--- a/web/txml.xlsx
+++ b/web/txml.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="195">
   <si>
     <t>&lt; 1</t>
   </si>
@@ -994,6 +994,9 @@
   </si>
   <si>
     <t>CD4 status for TX_RTT</t>
+  </si>
+  <si>
+    <t>Total Patients Restarting ART and CD4 Count Done</t>
   </si>
 </sst>
 </file>
@@ -3964,6 +3967,57 @@
     <xf numFmtId="1" fontId="32" fillId="6" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="34" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="4" borderId="70" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3985,15 +4039,6 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4006,410 +4051,20 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="75" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -4422,6 +4077,12 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="75" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="4" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4431,17 +4092,359 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="4" borderId="70" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5598,12 +5601,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" s="62" customFormat="1" ht="45" customHeight="1">
-      <c r="B1" s="248" t="s">
+      <c r="B1" s="265" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
+      <c r="C1" s="266"/>
+      <c r="D1" s="266"/>
+      <c r="E1" s="266"/>
       <c r="F1" s="63"/>
     </row>
     <row r="2" spans="2:6" s="64" customFormat="1" ht="45" customHeight="1">
@@ -5624,16 +5627,16 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="45" customHeight="1" thickBot="1">
-      <c r="B3" s="256" t="s">
+      <c r="B3" s="270" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="251"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="252"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="269"/>
     </row>
     <row r="4" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B4" s="264" t="s">
+      <c r="B4" s="257" t="s">
         <v>112</v>
       </c>
       <c r="C4" s="72" t="s">
@@ -5650,7 +5653,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B5" s="265"/>
+      <c r="B5" s="258"/>
       <c r="C5" s="72" t="s">
         <v>62</v>
       </c>
@@ -5665,7 +5668,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B6" s="265"/>
+      <c r="B6" s="258"/>
       <c r="C6" s="72" t="s">
         <v>63</v>
       </c>
@@ -5680,7 +5683,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B7" s="265"/>
+      <c r="B7" s="258"/>
       <c r="C7" s="72" t="s">
         <v>64</v>
       </c>
@@ -5695,7 +5698,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B8" s="265"/>
+      <c r="B8" s="258"/>
       <c r="C8" s="72" t="s">
         <v>65</v>
       </c>
@@ -5710,7 +5713,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B9" s="266"/>
+      <c r="B9" s="259"/>
       <c r="C9" s="72" t="s">
         <v>66</v>
       </c>
@@ -5725,7 +5728,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B10" s="267" t="s">
+      <c r="B10" s="260" t="s">
         <v>130</v>
       </c>
       <c r="C10" s="75" t="s">
@@ -5740,7 +5743,7 @@
       <c r="F10" s="74"/>
     </row>
     <row r="11" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B11" s="268"/>
+      <c r="B11" s="261"/>
       <c r="C11" s="75" t="s">
         <v>128</v>
       </c>
@@ -5753,7 +5756,7 @@
       <c r="F11" s="74"/>
     </row>
     <row r="12" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B12" s="269"/>
+      <c r="B12" s="262"/>
       <c r="C12" s="75" t="s">
         <v>129</v>
       </c>
@@ -5792,7 +5795,7 @@
       <c r="F14" s="74"/>
     </row>
     <row r="15" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B15" s="257" t="s">
+      <c r="B15" s="271" t="s">
         <v>193</v>
       </c>
       <c r="C15" s="224" t="s">
@@ -5805,7 +5808,7 @@
       <c r="F15" s="74"/>
     </row>
     <row r="16" spans="2:6" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B16" s="258"/>
+      <c r="B16" s="272"/>
       <c r="C16" s="224" t="s">
         <v>183</v>
       </c>
@@ -5816,7 +5819,7 @@
       <c r="F16" s="74"/>
     </row>
     <row r="17" spans="2:34" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B17" s="258"/>
+      <c r="B17" s="272"/>
       <c r="C17" s="224" t="s">
         <v>184</v>
       </c>
@@ -5827,7 +5830,7 @@
       <c r="F17" s="74"/>
     </row>
     <row r="18" spans="2:34" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B18" s="258"/>
+      <c r="B18" s="272"/>
       <c r="C18" s="224" t="s">
         <v>185</v>
       </c>
@@ -5838,7 +5841,7 @@
       <c r="F18" s="74"/>
     </row>
     <row r="19" spans="2:34" s="71" customFormat="1" ht="45" customHeight="1">
-      <c r="B19" s="259"/>
+      <c r="B19" s="273"/>
       <c r="C19" s="224" t="s">
         <v>191</v>
       </c>
@@ -5849,16 +5852,16 @@
       <c r="F19" s="74"/>
     </row>
     <row r="20" spans="2:34" ht="45" customHeight="1" thickBot="1">
-      <c r="B20" s="260" t="s">
+      <c r="B20" s="253" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="260"/>
-      <c r="D20" s="260"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="260"/>
+      <c r="C20" s="253"/>
+      <c r="D20" s="253"/>
+      <c r="E20" s="253"/>
+      <c r="F20" s="253"/>
     </row>
     <row r="21" spans="2:34" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="254" t="s">
         <v>107</v>
       </c>
       <c r="C21" s="112" t="s">
@@ -5894,14 +5897,14 @@
       <c r="AA21" s="96"/>
       <c r="AB21" s="97"/>
       <c r="AC21" s="98"/>
-      <c r="AD21" s="246"/>
+      <c r="AD21" s="263"/>
       <c r="AE21" s="99"/>
-      <c r="AF21" s="247"/>
+      <c r="AF21" s="264"/>
       <c r="AG21" s="95"/>
       <c r="AH21" s="3"/>
     </row>
     <row r="22" spans="2:34" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B22" s="262"/>
+      <c r="B22" s="255"/>
       <c r="C22" s="113" t="s">
         <v>165</v>
       </c>
@@ -5935,14 +5938,14 @@
       <c r="AA22" s="100"/>
       <c r="AB22" s="97"/>
       <c r="AC22" s="98"/>
-      <c r="AD22" s="246"/>
+      <c r="AD22" s="263"/>
       <c r="AE22" s="99"/>
-      <c r="AF22" s="247"/>
+      <c r="AF22" s="264"/>
       <c r="AG22" s="95"/>
       <c r="AH22" s="4"/>
     </row>
     <row r="23" spans="2:34" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B23" s="262"/>
+      <c r="B23" s="255"/>
       <c r="C23" s="112" t="s">
         <v>166</v>
       </c>
@@ -5974,14 +5977,14 @@
       <c r="AA23" s="101"/>
       <c r="AB23" s="97"/>
       <c r="AC23" s="98"/>
-      <c r="AD23" s="246"/>
+      <c r="AD23" s="263"/>
       <c r="AE23" s="99"/>
-      <c r="AF23" s="247"/>
+      <c r="AF23" s="264"/>
       <c r="AG23" s="95"/>
       <c r="AH23" s="4"/>
     </row>
     <row r="24" spans="2:34" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B24" s="262"/>
+      <c r="B24" s="255"/>
       <c r="C24" s="114" t="s">
         <v>167</v>
       </c>
@@ -6013,14 +6016,14 @@
       <c r="AA24" s="101"/>
       <c r="AB24" s="97"/>
       <c r="AC24" s="98"/>
-      <c r="AD24" s="246"/>
+      <c r="AD24" s="263"/>
       <c r="AE24" s="99"/>
-      <c r="AF24" s="247"/>
+      <c r="AF24" s="264"/>
       <c r="AG24" s="95"/>
       <c r="AH24" s="4"/>
     </row>
     <row r="25" spans="2:34" s="1" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B25" s="262"/>
+      <c r="B25" s="255"/>
       <c r="C25" s="114" t="s">
         <v>144</v>
       </c>
@@ -6052,14 +6055,14 @@
       <c r="AA25" s="101"/>
       <c r="AB25" s="97"/>
       <c r="AC25" s="98"/>
-      <c r="AD25" s="246"/>
+      <c r="AD25" s="263"/>
       <c r="AE25" s="99"/>
-      <c r="AF25" s="247"/>
+      <c r="AF25" s="264"/>
       <c r="AG25" s="95"/>
       <c r="AH25" s="4"/>
     </row>
     <row r="26" spans="2:34" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B26" s="262"/>
+      <c r="B26" s="255"/>
       <c r="C26" s="112" t="s">
         <v>168</v>
       </c>
@@ -6091,14 +6094,14 @@
       <c r="AA26" s="102"/>
       <c r="AB26" s="97"/>
       <c r="AC26" s="98"/>
-      <c r="AD26" s="246"/>
+      <c r="AD26" s="263"/>
       <c r="AE26" s="99"/>
-      <c r="AF26" s="247"/>
+      <c r="AF26" s="264"/>
       <c r="AG26" s="95"/>
       <c r="AH26" s="3"/>
     </row>
     <row r="27" spans="2:34" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B27" s="262"/>
+      <c r="B27" s="255"/>
       <c r="C27" s="112" t="s">
         <v>169</v>
       </c>
@@ -6132,14 +6135,14 @@
       <c r="AA27" s="96"/>
       <c r="AB27" s="97"/>
       <c r="AC27" s="98"/>
-      <c r="AD27" s="246"/>
+      <c r="AD27" s="263"/>
       <c r="AE27" s="99"/>
-      <c r="AF27" s="247"/>
+      <c r="AF27" s="264"/>
       <c r="AG27" s="95"/>
       <c r="AH27" s="3"/>
     </row>
     <row r="28" spans="2:34" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1">
-      <c r="B28" s="263"/>
+      <c r="B28" s="256"/>
       <c r="C28" s="112" t="s">
         <v>170</v>
       </c>
@@ -6171,23 +6174,23 @@
       <c r="AA28" s="102"/>
       <c r="AB28" s="97"/>
       <c r="AC28" s="98"/>
-      <c r="AD28" s="246"/>
+      <c r="AD28" s="263"/>
       <c r="AE28" s="99"/>
-      <c r="AF28" s="247"/>
+      <c r="AF28" s="264"/>
       <c r="AG28" s="95"/>
       <c r="AH28" s="3"/>
     </row>
     <row r="29" spans="2:34" ht="45" customHeight="1" thickBot="1">
-      <c r="B29" s="250" t="s">
+      <c r="B29" s="267" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="251"/>
-      <c r="D29" s="251"/>
-      <c r="E29" s="251"/>
-      <c r="F29" s="252"/>
+      <c r="C29" s="268"/>
+      <c r="D29" s="268"/>
+      <c r="E29" s="268"/>
+      <c r="F29" s="269"/>
     </row>
     <row r="30" spans="2:34" ht="45" customHeight="1">
-      <c r="B30" s="253" t="s">
+      <c r="B30" s="250" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="90" t="s">
@@ -6204,7 +6207,7 @@
       </c>
     </row>
     <row r="31" spans="2:34" ht="45" customHeight="1">
-      <c r="B31" s="254"/>
+      <c r="B31" s="251"/>
       <c r="C31" s="75" t="s">
         <v>111</v>
       </c>
@@ -6219,7 +6222,7 @@
       </c>
     </row>
     <row r="32" spans="2:34" ht="45" customHeight="1">
-      <c r="B32" s="254"/>
+      <c r="B32" s="251"/>
       <c r="C32" s="75" t="s">
         <v>110</v>
       </c>
@@ -6234,7 +6237,7 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="45" customHeight="1">
-      <c r="B33" s="254"/>
+      <c r="B33" s="251"/>
       <c r="C33" s="90" t="s">
         <v>74</v>
       </c>
@@ -6249,7 +6252,7 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="45" customHeight="1">
-      <c r="B34" s="254"/>
+      <c r="B34" s="251"/>
       <c r="C34" s="90" t="s">
         <v>76</v>
       </c>
@@ -6264,7 +6267,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" ht="45" customHeight="1" thickBot="1">
-      <c r="B35" s="255"/>
+      <c r="B35" s="252"/>
       <c r="C35" s="92" t="s">
         <v>86</v>
       </c>
@@ -6275,7 +6278,7 @@
       <c r="F35" s="84"/>
     </row>
     <row r="36" spans="2:6" ht="45" customHeight="1">
-      <c r="B36" s="253" t="s">
+      <c r="B36" s="250" t="s">
         <v>156</v>
       </c>
       <c r="C36" s="109" t="s">
@@ -6292,7 +6295,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" ht="45" customHeight="1">
-      <c r="B37" s="254"/>
+      <c r="B37" s="251"/>
       <c r="C37" s="110" t="s">
         <v>93</v>
       </c>
@@ -6307,7 +6310,7 @@
       </c>
     </row>
     <row r="38" spans="2:6" ht="45" customHeight="1">
-      <c r="B38" s="254"/>
+      <c r="B38" s="251"/>
       <c r="C38" s="110" t="s">
         <v>51</v>
       </c>
@@ -6322,7 +6325,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" ht="45" customHeight="1">
-      <c r="B39" s="254"/>
+      <c r="B39" s="251"/>
       <c r="C39" s="110" t="s">
         <v>46</v>
       </c>
@@ -6335,7 +6338,7 @@
       <c r="F39" s="81"/>
     </row>
     <row r="40" spans="2:6" ht="45" customHeight="1">
-      <c r="B40" s="254"/>
+      <c r="B40" s="251"/>
       <c r="C40" s="110" t="s">
         <v>94</v>
       </c>
@@ -6350,7 +6353,7 @@
       </c>
     </row>
     <row r="41" spans="2:6" ht="45" customHeight="1">
-      <c r="B41" s="254"/>
+      <c r="B41" s="251"/>
       <c r="C41" s="110" t="s">
         <v>47</v>
       </c>
@@ -6365,7 +6368,7 @@
       </c>
     </row>
     <row r="42" spans="2:6" ht="45" customHeight="1" thickBot="1">
-      <c r="B42" s="255"/>
+      <c r="B42" s="252"/>
       <c r="C42" s="111" t="s">
         <v>48</v>
       </c>
@@ -6382,11 +6385,6 @@
   </sheetData>
   <autoFilter ref="B2:F42"/>
   <mergeCells count="12">
-    <mergeCell ref="B36:B42"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:B28"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B10:B12"/>
     <mergeCell ref="AD21:AD28"/>
     <mergeCell ref="AF21:AF28"/>
     <mergeCell ref="B1:E1"/>
@@ -6394,6 +6392,11 @@
     <mergeCell ref="B30:B35"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B15:B19"/>
+    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:B28"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B10:B12"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D21:D28">
@@ -6447,112 +6450,112 @@
       <c r="A1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="273" t="s">
+      <c r="B1" s="390" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="274"/>
-      <c r="D1" s="278" t="s">
+      <c r="C1" s="391"/>
+      <c r="D1" s="380" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="279"/>
-      <c r="F1" s="292" t="s">
+      <c r="E1" s="381"/>
+      <c r="F1" s="366" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="293"/>
-      <c r="H1" s="278" t="s">
+      <c r="G1" s="367"/>
+      <c r="H1" s="380" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="292" t="s">
+      <c r="I1" s="381"/>
+      <c r="J1" s="381"/>
+      <c r="K1" s="366" t="s">
         <v>89</v>
       </c>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
-      <c r="N1" s="292"/>
-      <c r="O1" s="292"/>
-      <c r="P1" s="292"/>
-      <c r="Q1" s="292"/>
-      <c r="R1" s="279" t="s">
+      <c r="L1" s="366"/>
+      <c r="M1" s="366"/>
+      <c r="N1" s="366"/>
+      <c r="O1" s="366"/>
+      <c r="P1" s="366"/>
+      <c r="Q1" s="366"/>
+      <c r="R1" s="381" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="279"/>
-      <c r="T1" s="292" t="s">
+      <c r="S1" s="381"/>
+      <c r="T1" s="366" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="292"/>
-      <c r="V1" s="293"/>
-      <c r="W1" s="278" t="s">
+      <c r="U1" s="366"/>
+      <c r="V1" s="367"/>
+      <c r="W1" s="380" t="s">
         <v>56</v>
       </c>
-      <c r="X1" s="279"/>
+      <c r="X1" s="381"/>
       <c r="Y1" s="6" t="s">
         <v>91</v>
       </c>
       <c r="Z1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="AA1" s="280">
+      <c r="AA1" s="394">
         <v>2020</v>
       </c>
-      <c r="AB1" s="280"/>
-      <c r="AC1" s="280"/>
-      <c r="AD1" s="280"/>
-      <c r="AE1" s="280"/>
-      <c r="AF1" s="280"/>
-      <c r="AG1" s="280"/>
-      <c r="AH1" s="280"/>
-      <c r="AI1" s="280"/>
-      <c r="AJ1" s="281"/>
-      <c r="AK1" s="270" t="s">
+      <c r="AB1" s="394"/>
+      <c r="AC1" s="394"/>
+      <c r="AD1" s="394"/>
+      <c r="AE1" s="394"/>
+      <c r="AF1" s="394"/>
+      <c r="AG1" s="394"/>
+      <c r="AH1" s="394"/>
+      <c r="AI1" s="394"/>
+      <c r="AJ1" s="395"/>
+      <c r="AK1" s="388" t="s">
         <v>58</v>
       </c>
-      <c r="AL1" s="271"/>
-      <c r="AM1" s="271"/>
-      <c r="AN1" s="271"/>
+      <c r="AL1" s="389"/>
+      <c r="AM1" s="389"/>
+      <c r="AN1" s="389"/>
       <c r="AO1" s="8"/>
       <c r="AP1" s="9"/>
     </row>
     <row r="2" spans="1:42" s="12" customFormat="1" ht="21.4" hidden="1" thickBot="1">
-      <c r="A2" s="272" t="s">
+      <c r="A2" s="278" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="272"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="272"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="272"/>
-      <c r="M2" s="272"/>
-      <c r="N2" s="272"/>
-      <c r="O2" s="272"/>
-      <c r="P2" s="272"/>
-      <c r="Q2" s="272"/>
-      <c r="R2" s="272"/>
-      <c r="S2" s="272"/>
-      <c r="T2" s="272"/>
-      <c r="U2" s="272"/>
-      <c r="V2" s="272"/>
-      <c r="W2" s="272"/>
-      <c r="X2" s="272"/>
-      <c r="Y2" s="272"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="272"/>
-      <c r="AB2" s="272"/>
-      <c r="AC2" s="272"/>
-      <c r="AD2" s="272"/>
-      <c r="AE2" s="272"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="272"/>
-      <c r="AH2" s="272"/>
-      <c r="AI2" s="272"/>
-      <c r="AJ2" s="272"/>
-      <c r="AK2" s="272"/>
+      <c r="B2" s="278"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="278"/>
+      <c r="K2" s="278"/>
+      <c r="L2" s="278"/>
+      <c r="M2" s="278"/>
+      <c r="N2" s="278"/>
+      <c r="O2" s="278"/>
+      <c r="P2" s="278"/>
+      <c r="Q2" s="278"/>
+      <c r="R2" s="278"/>
+      <c r="S2" s="278"/>
+      <c r="T2" s="278"/>
+      <c r="U2" s="278"/>
+      <c r="V2" s="278"/>
+      <c r="W2" s="278"/>
+      <c r="X2" s="278"/>
+      <c r="Y2" s="278"/>
+      <c r="Z2" s="278"/>
+      <c r="AA2" s="278"/>
+      <c r="AB2" s="278"/>
+      <c r="AC2" s="278"/>
+      <c r="AD2" s="278"/>
+      <c r="AE2" s="278"/>
+      <c r="AF2" s="278"/>
+      <c r="AG2" s="278"/>
+      <c r="AH2" s="278"/>
+      <c r="AI2" s="278"/>
+      <c r="AJ2" s="278"/>
+      <c r="AK2" s="278"/>
       <c r="AL2" s="11"/>
       <c r="AO2" s="8"/>
       <c r="AP2" s="13"/>
@@ -6587,139 +6590,139 @@
       <c r="AP3" s="13"/>
     </row>
     <row r="4" spans="1:42" s="22" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A4" s="290" t="s">
+      <c r="A4" s="386" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="291"/>
-      <c r="C4" s="291"/>
-      <c r="D4" s="288" t="s">
+      <c r="B4" s="387"/>
+      <c r="C4" s="387"/>
+      <c r="D4" s="384" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="288"/>
-      <c r="F4" s="289"/>
-      <c r="G4" s="289"/>
-      <c r="H4" s="289"/>
-      <c r="I4" s="289"/>
-      <c r="J4" s="289"/>
-      <c r="K4" s="289"/>
-      <c r="L4" s="289"/>
-      <c r="M4" s="289"/>
-      <c r="N4" s="289"/>
-      <c r="O4" s="289"/>
-      <c r="P4" s="289"/>
-      <c r="Q4" s="289"/>
-      <c r="R4" s="289"/>
-      <c r="S4" s="289"/>
-      <c r="T4" s="289"/>
-      <c r="U4" s="289"/>
-      <c r="V4" s="289"/>
-      <c r="W4" s="282" t="s">
+      <c r="E4" s="384"/>
+      <c r="F4" s="385"/>
+      <c r="G4" s="385"/>
+      <c r="H4" s="385"/>
+      <c r="I4" s="385"/>
+      <c r="J4" s="385"/>
+      <c r="K4" s="385"/>
+      <c r="L4" s="385"/>
+      <c r="M4" s="385"/>
+      <c r="N4" s="385"/>
+      <c r="O4" s="385"/>
+      <c r="P4" s="385"/>
+      <c r="Q4" s="385"/>
+      <c r="R4" s="385"/>
+      <c r="S4" s="385"/>
+      <c r="T4" s="385"/>
+      <c r="U4" s="385"/>
+      <c r="V4" s="385"/>
+      <c r="W4" s="396" t="s">
         <v>123</v>
       </c>
-      <c r="X4" s="283"/>
-      <c r="Y4" s="283"/>
-      <c r="Z4" s="283"/>
-      <c r="AA4" s="283"/>
-      <c r="AB4" s="283"/>
-      <c r="AC4" s="283"/>
-      <c r="AD4" s="283"/>
-      <c r="AE4" s="283"/>
-      <c r="AF4" s="283"/>
-      <c r="AG4" s="283"/>
-      <c r="AH4" s="283"/>
-      <c r="AI4" s="283"/>
-      <c r="AJ4" s="283"/>
-      <c r="AK4" s="283"/>
-      <c r="AL4" s="283"/>
-      <c r="AM4" s="283"/>
-      <c r="AN4" s="284"/>
+      <c r="X4" s="397"/>
+      <c r="Y4" s="397"/>
+      <c r="Z4" s="397"/>
+      <c r="AA4" s="397"/>
+      <c r="AB4" s="397"/>
+      <c r="AC4" s="397"/>
+      <c r="AD4" s="397"/>
+      <c r="AE4" s="397"/>
+      <c r="AF4" s="397"/>
+      <c r="AG4" s="397"/>
+      <c r="AH4" s="397"/>
+      <c r="AI4" s="397"/>
+      <c r="AJ4" s="397"/>
+      <c r="AK4" s="397"/>
+      <c r="AL4" s="397"/>
+      <c r="AM4" s="397"/>
+      <c r="AN4" s="398"/>
       <c r="AO4" s="50"/>
       <c r="AP4" s="21"/>
     </row>
     <row r="5" spans="1:42" s="27" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A5" s="309" t="s">
+      <c r="A5" s="382" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="286" t="s">
+      <c r="B5" s="399" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="392" t="s">
+      <c r="C5" s="282" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="275" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="275"/>
-      <c r="F5" s="275" t="s">
+      <c r="D5" s="274" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="275"/>
-      <c r="H5" s="275" t="s">
+      <c r="G5" s="274"/>
+      <c r="H5" s="274" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="275"/>
-      <c r="J5" s="275" t="s">
+      <c r="I5" s="274"/>
+      <c r="J5" s="274" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="275"/>
-      <c r="L5" s="275" t="s">
+      <c r="K5" s="274"/>
+      <c r="L5" s="274" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="275"/>
-      <c r="N5" s="275" t="s">
+      <c r="M5" s="274"/>
+      <c r="N5" s="274" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="275"/>
-      <c r="P5" s="275" t="s">
+      <c r="O5" s="274"/>
+      <c r="P5" s="274" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="275"/>
-      <c r="R5" s="275" t="s">
+      <c r="Q5" s="274"/>
+      <c r="R5" s="274" t="s">
         <v>7</v>
       </c>
-      <c r="S5" s="275"/>
-      <c r="T5" s="275" t="s">
+      <c r="S5" s="274"/>
+      <c r="T5" s="274" t="s">
         <v>8</v>
       </c>
-      <c r="U5" s="275"/>
-      <c r="V5" s="275" t="s">
+      <c r="U5" s="274"/>
+      <c r="V5" s="274" t="s">
         <v>13</v>
       </c>
-      <c r="W5" s="275"/>
-      <c r="X5" s="275" t="s">
+      <c r="W5" s="274"/>
+      <c r="X5" s="274" t="s">
         <v>14</v>
       </c>
-      <c r="Y5" s="275"/>
-      <c r="Z5" s="275" t="s">
+      <c r="Y5" s="274"/>
+      <c r="Z5" s="274" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="285"/>
-      <c r="AB5" s="275" t="s">
+      <c r="AA5" s="275"/>
+      <c r="AB5" s="274" t="s">
         <v>177</v>
       </c>
-      <c r="AC5" s="285"/>
-      <c r="AD5" s="275" t="s">
+      <c r="AC5" s="275"/>
+      <c r="AD5" s="274" t="s">
         <v>178</v>
       </c>
-      <c r="AE5" s="285"/>
-      <c r="AF5" s="275" t="s">
+      <c r="AE5" s="275"/>
+      <c r="AF5" s="274" t="s">
         <v>179</v>
       </c>
-      <c r="AG5" s="285"/>
-      <c r="AH5" s="275" t="s">
+      <c r="AG5" s="275"/>
+      <c r="AH5" s="274" t="s">
         <v>180</v>
       </c>
-      <c r="AI5" s="285"/>
-      <c r="AJ5" s="296" t="s">
+      <c r="AI5" s="275"/>
+      <c r="AJ5" s="370" t="s">
         <v>12</v>
       </c>
-      <c r="AK5" s="294" t="s">
+      <c r="AK5" s="368" t="s">
         <v>53</v>
       </c>
       <c r="AL5" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AM5" s="276" t="s">
+      <c r="AM5" s="392" t="s">
         <v>60</v>
       </c>
       <c r="AN5" s="24" t="s">
@@ -6729,9 +6732,9 @@
       <c r="AP5" s="26"/>
     </row>
     <row r="6" spans="1:42" s="27" customFormat="1" ht="27" customHeight="1" thickBot="1">
-      <c r="A6" s="310"/>
-      <c r="B6" s="287"/>
-      <c r="C6" s="393"/>
+      <c r="A6" s="383"/>
+      <c r="B6" s="400"/>
+      <c r="C6" s="283"/>
       <c r="D6" s="28" t="s">
         <v>10</v>
       </c>
@@ -6828,13 +6831,13 @@
       <c r="AI6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AJ6" s="297"/>
-      <c r="AK6" s="295"/>
+      <c r="AJ6" s="371"/>
+      <c r="AK6" s="369"/>
       <c r="AL6" s="29" t="str">
         <f>IF(LEN(A54)-LEN(SUBSTITUTE(A54,"*",""))&gt;0," Total Errors are "&amp;(LEN(A54)-LEN(SUBSTITUTE(A54,"*",""))),"")</f>
         <v/>
       </c>
-      <c r="AM6" s="277"/>
+      <c r="AM6" s="393"/>
       <c r="AN6" s="30" t="str">
         <f>IF(LEN(A76)-LEN(SUBSTITUTE(A76,"*",""))&gt;0," Total Warnings are "&amp;(LEN(A76)-LEN(SUBSTITUTE(A76,"*",""))),"")</f>
         <v/>
@@ -6843,109 +6846,109 @@
       <c r="AP6" s="26"/>
     </row>
     <row r="7" spans="1:42" ht="25.9" thickBot="1">
-      <c r="A7" s="306" t="s">
+      <c r="A7" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="307"/>
-      <c r="C7" s="307"/>
-      <c r="D7" s="307"/>
-      <c r="E7" s="307"/>
-      <c r="F7" s="307"/>
-      <c r="G7" s="307"/>
-      <c r="H7" s="307"/>
-      <c r="I7" s="307"/>
-      <c r="J7" s="307"/>
-      <c r="K7" s="307"/>
-      <c r="L7" s="307"/>
-      <c r="M7" s="307"/>
-      <c r="N7" s="307"/>
-      <c r="O7" s="307"/>
-      <c r="P7" s="307"/>
-      <c r="Q7" s="307"/>
-      <c r="R7" s="307"/>
-      <c r="S7" s="307"/>
-      <c r="T7" s="307"/>
-      <c r="U7" s="307"/>
-      <c r="V7" s="307"/>
-      <c r="W7" s="307"/>
-      <c r="X7" s="307"/>
-      <c r="Y7" s="307"/>
-      <c r="Z7" s="307"/>
-      <c r="AA7" s="307"/>
-      <c r="AB7" s="307"/>
-      <c r="AC7" s="307"/>
-      <c r="AD7" s="307"/>
-      <c r="AE7" s="307"/>
-      <c r="AF7" s="307"/>
-      <c r="AG7" s="307"/>
-      <c r="AH7" s="307"/>
-      <c r="AI7" s="307"/>
-      <c r="AJ7" s="307"/>
-      <c r="AK7" s="307"/>
-      <c r="AL7" s="307"/>
-      <c r="AM7" s="307"/>
-      <c r="AN7" s="308"/>
+      <c r="B7" s="378"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="378"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
+      <c r="G7" s="378"/>
+      <c r="H7" s="378"/>
+      <c r="I7" s="378"/>
+      <c r="J7" s="378"/>
+      <c r="K7" s="378"/>
+      <c r="L7" s="378"/>
+      <c r="M7" s="378"/>
+      <c r="N7" s="378"/>
+      <c r="O7" s="378"/>
+      <c r="P7" s="378"/>
+      <c r="Q7" s="378"/>
+      <c r="R7" s="378"/>
+      <c r="S7" s="378"/>
+      <c r="T7" s="378"/>
+      <c r="U7" s="378"/>
+      <c r="V7" s="378"/>
+      <c r="W7" s="378"/>
+      <c r="X7" s="378"/>
+      <c r="Y7" s="378"/>
+      <c r="Z7" s="378"/>
+      <c r="AA7" s="378"/>
+      <c r="AB7" s="378"/>
+      <c r="AC7" s="378"/>
+      <c r="AD7" s="378"/>
+      <c r="AE7" s="378"/>
+      <c r="AF7" s="378"/>
+      <c r="AG7" s="378"/>
+      <c r="AH7" s="378"/>
+      <c r="AI7" s="378"/>
+      <c r="AJ7" s="378"/>
+      <c r="AK7" s="378"/>
+      <c r="AL7" s="378"/>
+      <c r="AM7" s="378"/>
+      <c r="AN7" s="379"/>
       <c r="AO7" s="33"/>
       <c r="AP7" s="34"/>
     </row>
     <row r="8" spans="1:42" hidden="1">
-      <c r="A8" s="313" t="s">
+      <c r="A8" s="311" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="311" t="s">
+      <c r="B8" s="309" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="395" t="s">
+      <c r="C8" s="287" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="394" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="301"/>
-      <c r="F8" s="300" t="s">
+      <c r="D8" s="286" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="285"/>
+      <c r="F8" s="284" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="301"/>
-      <c r="H8" s="300" t="s">
+      <c r="G8" s="285"/>
+      <c r="H8" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="301"/>
-      <c r="J8" s="300" t="s">
+      <c r="I8" s="285"/>
+      <c r="J8" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="301"/>
-      <c r="L8" s="300" t="s">
+      <c r="K8" s="285"/>
+      <c r="L8" s="284" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="301"/>
-      <c r="N8" s="300" t="s">
+      <c r="M8" s="285"/>
+      <c r="N8" s="284" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="301"/>
-      <c r="P8" s="300" t="s">
+      <c r="O8" s="285"/>
+      <c r="P8" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="Q8" s="301"/>
-      <c r="R8" s="300" t="s">
+      <c r="Q8" s="285"/>
+      <c r="R8" s="284" t="s">
         <v>7</v>
       </c>
-      <c r="S8" s="301"/>
-      <c r="T8" s="300" t="s">
+      <c r="S8" s="285"/>
+      <c r="T8" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="U8" s="301"/>
-      <c r="V8" s="300" t="s">
+      <c r="U8" s="285"/>
+      <c r="V8" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="W8" s="301"/>
-      <c r="X8" s="300" t="s">
+      <c r="W8" s="285"/>
+      <c r="X8" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="Y8" s="301"/>
-      <c r="Z8" s="300" t="s">
+      <c r="Y8" s="285"/>
+      <c r="Z8" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="301"/>
+      <c r="AA8" s="285"/>
       <c r="AB8" s="120"/>
       <c r="AC8" s="120"/>
       <c r="AD8" s="120"/>
@@ -6954,28 +6957,28 @@
       <c r="AG8" s="120"/>
       <c r="AH8" s="120"/>
       <c r="AI8" s="120"/>
-      <c r="AJ8" s="304" t="s">
+      <c r="AJ8" s="375" t="s">
         <v>12</v>
       </c>
-      <c r="AK8" s="359" t="s">
+      <c r="AK8" s="358" t="s">
         <v>53</v>
       </c>
-      <c r="AL8" s="356" t="s">
+      <c r="AL8" s="354" t="s">
         <v>59</v>
       </c>
-      <c r="AM8" s="302" t="s">
+      <c r="AM8" s="356" t="s">
         <v>60</v>
       </c>
-      <c r="AN8" s="302" t="s">
+      <c r="AN8" s="356" t="s">
         <v>60</v>
       </c>
       <c r="AO8" s="33"/>
       <c r="AP8" s="34"/>
     </row>
     <row r="9" spans="1:42" ht="21.4" hidden="1" thickBot="1">
-      <c r="A9" s="314"/>
-      <c r="B9" s="312"/>
-      <c r="C9" s="396"/>
+      <c r="A9" s="312"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="288"/>
       <c r="D9" s="39" t="s">
         <v>10</v>
       </c>
@@ -7056,16 +7059,16 @@
       <c r="AG9" s="121"/>
       <c r="AH9" s="121"/>
       <c r="AI9" s="121"/>
-      <c r="AJ9" s="305"/>
-      <c r="AK9" s="360"/>
-      <c r="AL9" s="357"/>
-      <c r="AM9" s="358"/>
-      <c r="AN9" s="303"/>
+      <c r="AJ9" s="376"/>
+      <c r="AK9" s="359"/>
+      <c r="AL9" s="355"/>
+      <c r="AM9" s="357"/>
+      <c r="AN9" s="374"/>
       <c r="AO9" s="33"/>
       <c r="AP9" s="34"/>
     </row>
     <row r="10" spans="1:42" ht="30" customHeight="1">
-      <c r="A10" s="364" t="s">
+      <c r="A10" s="361" t="s">
         <v>131</v>
       </c>
       <c r="B10" s="123" t="s">
@@ -7120,12 +7123,12 @@
         <f>CONCATENATE(IF(D29&lt;&gt;SUM(D16,D17,D18)," * Total TX_RTT By Population Type "&amp;D8&amp;" "&amp;D9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(E29&lt;&gt;SUM(E16,E17,E18)," * Total TX_RTT By Population Type "&amp;D8&amp;" "&amp;E9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(F29&lt;&gt;SUM(F16,F17,F18)," * Total TX_RTT By Population Type "&amp;F8&amp;" "&amp;F9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(G29&lt;&gt;SUM(G16,G17,G18)," * Total TX_RTT By Population Type "&amp;F8&amp;" "&amp;G9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(H29&lt;&gt;SUM(H16,H17,H18)," * Total TX_RTT By Population Type "&amp;H8&amp;" "&amp;H9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(I29&lt;&gt;SUM(I16,I17,I18)," * Total TX_RTT By Population Type "&amp;H8&amp;" "&amp;I9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(J29&lt;&gt;SUM(J16,J17,J18)," * Total TX_RTT By Population Type "&amp;J8&amp;" "&amp;J9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(K29&lt;&gt;SUM(K16,K17,K18)," * Total TX_RTT By Population Type "&amp;J8&amp;" "&amp;K9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(L29&lt;&gt;SUM(L16,L17,L18)," * Total TX_RTT By Population Type "&amp;L8&amp;" "&amp;L9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(M29&lt;&gt;SUM(M16,M17,M18)," * Total TX_RTT By Population Type "&amp;L8&amp;" "&amp;M9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(N29&lt;&gt;SUM(N16,N17,N18)," * Total TX_RTT By Population Type "&amp;N8&amp;" "&amp;N9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(O29&lt;&gt;SUM(O16,O17,O18)," * Total TX_RTT By Population Type "&amp;N8&amp;" "&amp;O9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(P29&lt;&gt;SUM(P16,P17,P18)," * Total TX_RTT By Population Type "&amp;P8&amp;" "&amp;P9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(Q29&lt;&gt;SUM(Q16,Q17,Q18)," * Total TX_RTT By Population Type "&amp;P8&amp;" "&amp;Q9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(R29&lt;&gt;SUM(R16,R17,R18)," * Total TX_RTT By Population Type "&amp;R8&amp;" "&amp;R9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(S29&lt;&gt;SUM(S16,S17,S18)," * Total TX_RTT By Population Type "&amp;R8&amp;" "&amp;S9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(T29&lt;&gt;SUM(T16,T17,T18)," * Total TX_RTT By Population Type "&amp;T8&amp;" "&amp;T9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(U29&lt;&gt;SUM(U16,U17,U18)," * Total TX_RTT By Population Type "&amp;T8&amp;" "&amp;U9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(V29&lt;&gt;SUM(V16,V17,V18)," * Total TX_RTT By Population Type "&amp;V8&amp;" "&amp;V9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(W29&lt;&gt;SUM(W16,W17,W18)," * Total TX_RTT By Population Type "&amp;V8&amp;" "&amp;W9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(X29&lt;&gt;SUM(X16,X17,X18)," * Total TX_RTT By Population Type "&amp;X8&amp;" "&amp;X9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(Y29&lt;&gt;SUM(Y16,Y17,Y18)," * Total TX_RTT By Population Type "&amp;X8&amp;" "&amp;Y9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(Z29&lt;&gt;SUM(Z16,Z17,Z18)," * Total TX_RTT By Population Type "&amp;Z8&amp;" "&amp;Z9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""),IF(AA29&lt;&gt;SUM(AA16,AA17,AA18)," * Total TX_RTT By Population Type "&amp;Z8&amp;" "&amp;AA9&amp;" is Not equal to Total TX_RTT By Duration of Treatment"&amp;CHAR(10),""))</f>
         <v/>
       </c>
-      <c r="AL10" s="374" t="str">
+      <c r="AL10" s="294" t="str">
         <f>CONCATENATE(AK36,AK40,AK42,AK43,AK44,AK45,AK46,AK47,AK48,AK49,AK10,AK27,AK28,AK29,AK32,AK33,AK34,AK11,AK12,AK13,AK14,AK15,AK16,AK17,AK18,AK19,AK20,AK30,AK31,AK37,AK38,AK41,AK21)</f>
         <v/>
       </c>
       <c r="AM10" s="41"/>
-      <c r="AN10" s="298" t="str">
+      <c r="AN10" s="372" t="str">
         <f>CONCATENATE(AM36,AM40,AM42,AM43,AM44,AM45,AM46,AM47,AM48,AM49)</f>
         <v/>
       </c>
@@ -7133,7 +7136,7 @@
       <c r="AP10" s="34"/>
     </row>
     <row r="11" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A11" s="365"/>
+      <c r="A11" s="362"/>
       <c r="B11" s="132" t="s">
         <v>62</v>
       </c>
@@ -7183,14 +7186,14 @@
         <v>0</v>
       </c>
       <c r="AK11" s="40"/>
-      <c r="AL11" s="375"/>
+      <c r="AL11" s="295"/>
       <c r="AM11" s="41"/>
-      <c r="AN11" s="299"/>
+      <c r="AN11" s="373"/>
       <c r="AO11" s="33"/>
       <c r="AP11" s="34"/>
     </row>
     <row r="12" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A12" s="365"/>
+      <c r="A12" s="362"/>
       <c r="B12" s="132" t="s">
         <v>63</v>
       </c>
@@ -7240,14 +7243,14 @@
         <v>0</v>
       </c>
       <c r="AK12" s="40"/>
-      <c r="AL12" s="375"/>
+      <c r="AL12" s="295"/>
       <c r="AM12" s="41"/>
-      <c r="AN12" s="299"/>
+      <c r="AN12" s="373"/>
       <c r="AO12" s="33"/>
       <c r="AP12" s="34"/>
     </row>
     <row r="13" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A13" s="365"/>
+      <c r="A13" s="362"/>
       <c r="B13" s="132" t="s">
         <v>64</v>
       </c>
@@ -7297,14 +7300,14 @@
         <v>0</v>
       </c>
       <c r="AK13" s="40"/>
-      <c r="AL13" s="375"/>
+      <c r="AL13" s="295"/>
       <c r="AM13" s="41"/>
-      <c r="AN13" s="299"/>
+      <c r="AN13" s="373"/>
       <c r="AO13" s="33"/>
       <c r="AP13" s="34"/>
     </row>
     <row r="14" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A14" s="365"/>
+      <c r="A14" s="362"/>
       <c r="B14" s="132" t="s">
         <v>65</v>
       </c>
@@ -7354,14 +7357,14 @@
         <v>0</v>
       </c>
       <c r="AK14" s="40"/>
-      <c r="AL14" s="375"/>
+      <c r="AL14" s="295"/>
       <c r="AM14" s="41"/>
-      <c r="AN14" s="299"/>
+      <c r="AN14" s="373"/>
       <c r="AO14" s="33"/>
       <c r="AP14" s="34"/>
     </row>
     <row r="15" spans="1:42" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A15" s="366"/>
+      <c r="A15" s="363"/>
       <c r="B15" s="141" t="s">
         <v>66</v>
       </c>
@@ -7411,14 +7414,14 @@
         <v>0</v>
       </c>
       <c r="AK15" s="40"/>
-      <c r="AL15" s="375"/>
+      <c r="AL15" s="295"/>
       <c r="AM15" s="41"/>
-      <c r="AN15" s="299"/>
+      <c r="AN15" s="373"/>
       <c r="AO15" s="33"/>
       <c r="AP15" s="34"/>
     </row>
     <row r="16" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A16" s="367" t="s">
+      <c r="A16" s="364" t="s">
         <v>130</v>
       </c>
       <c r="B16" s="132" t="s">
@@ -7470,14 +7473,14 @@
         <v>0</v>
       </c>
       <c r="AK16" s="40"/>
-      <c r="AL16" s="375"/>
+      <c r="AL16" s="295"/>
       <c r="AM16" s="41"/>
-      <c r="AN16" s="299"/>
+      <c r="AN16" s="373"/>
       <c r="AO16" s="33"/>
       <c r="AP16" s="34"/>
     </row>
     <row r="17" spans="1:42" ht="38.25" customHeight="1">
-      <c r="A17" s="368"/>
+      <c r="A17" s="365"/>
       <c r="B17" s="132" t="s">
         <v>128</v>
       </c>
@@ -7527,14 +7530,14 @@
         <v>0</v>
       </c>
       <c r="AK17" s="40"/>
-      <c r="AL17" s="375"/>
+      <c r="AL17" s="295"/>
       <c r="AM17" s="41"/>
-      <c r="AN17" s="299"/>
+      <c r="AN17" s="373"/>
       <c r="AO17" s="33"/>
       <c r="AP17" s="34"/>
     </row>
     <row r="18" spans="1:42" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A18" s="368"/>
+      <c r="A18" s="365"/>
       <c r="B18" s="152" t="s">
         <v>129</v>
       </c>
@@ -7584,9 +7587,9 @@
         <v>0</v>
       </c>
       <c r="AK18" s="40"/>
-      <c r="AL18" s="375"/>
+      <c r="AL18" s="295"/>
       <c r="AM18" s="41"/>
-      <c r="AN18" s="299"/>
+      <c r="AN18" s="373"/>
       <c r="AO18" s="33"/>
       <c r="AP18" s="34"/>
     </row>
@@ -7643,9 +7646,9 @@
         <v>0</v>
       </c>
       <c r="AK19" s="37"/>
-      <c r="AL19" s="375"/>
+      <c r="AL19" s="295"/>
       <c r="AM19" s="38"/>
-      <c r="AN19" s="299"/>
+      <c r="AN19" s="373"/>
       <c r="AO19" s="51"/>
       <c r="AP19" s="34"/>
     </row>
@@ -7702,18 +7705,18 @@
         <v>0</v>
       </c>
       <c r="AK20" s="37"/>
-      <c r="AL20" s="375"/>
+      <c r="AL20" s="295"/>
       <c r="AM20" s="38"/>
-      <c r="AN20" s="299"/>
+      <c r="AN20" s="373"/>
       <c r="AO20" s="51"/>
       <c r="AP20" s="34"/>
     </row>
     <row r="21" spans="1:42" s="122" customFormat="1" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A21" s="384" t="s">
+      <c r="A21" s="306" t="s">
         <v>193</v>
       </c>
       <c r="B21" s="226" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C21" s="231" t="s">
         <v>186</v>
@@ -7854,24 +7857,24 @@
         <f>CONCATENATE(IF(D21&lt;&gt;SUM(D16,D17,D18)," * Total TX_RTT Done for CD_4 "&amp;D8&amp;" "&amp;D9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(E21&lt;&gt;SUM(E16,E17,E18)," * Total TX_RTT Done for CD_4 "&amp;D8&amp;" "&amp;E9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(F21&lt;&gt;SUM(F16,F17,F18)," * Total TX_RTT Done for CD_4 "&amp;F8&amp;" "&amp;F9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(G21&lt;&gt;SUM(G16,G17,G18)," * Total TX_RTT Done for CD_4 "&amp;F8&amp;" "&amp;G9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(H21&lt;&gt;SUM(H16,H17,H18)," * Total TX_RTT Done for CD_4 "&amp;H8&amp;" "&amp;H9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(I21&lt;&gt;SUM(I16,I17,I18)," * Total TX_RTT Done for CD_4 "&amp;H8&amp;" "&amp;I9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(J21&lt;&gt;SUM(J16,J17,J18)," * Total TX_RTT Done for CD_4 "&amp;J8&amp;" "&amp;J9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(K21&lt;&gt;SUM(K16,K17,K18)," * Total TX_RTT Done for CD_4 "&amp;J8&amp;" "&amp;K9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(L21&lt;&gt;SUM(L16,L17,L18)," * Total TX_RTT Done for CD_4 "&amp;L8&amp;" "&amp;L9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(M21&lt;&gt;SUM(M16,M17,M18)," * Total TX_RTT Done for CD_4 "&amp;L8&amp;" "&amp;M9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(N21&lt;&gt;SUM(N16,N17,N18)," * Total TX_RTT Done for CD_4 "&amp;N8&amp;" "&amp;N9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(O21&lt;&gt;SUM(O16,O17,O18)," * Total TX_RTT Done for CD_4 "&amp;N8&amp;" "&amp;O9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(P21&lt;&gt;SUM(P16,P17,P18)," * Total TX_RTT Done for CD_4 "&amp;P8&amp;" "&amp;P9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(Q21&lt;&gt;SUM(Q16,Q17,Q18)," * Total TX_RTT Done for CD_4 "&amp;P8&amp;" "&amp;Q9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(R21&lt;&gt;SUM(R16,R17,R18)," * Total TX_RTT Done for CD_4 "&amp;R8&amp;" "&amp;R9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(S21&lt;&gt;SUM(S16,S17,S18)," * Total TX_RTT Done for CD_4 "&amp;R8&amp;" "&amp;S9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(T21&lt;&gt;SUM(T16,T17,T18)," * Total TX_RTT Done for CD_4 "&amp;T8&amp;" "&amp;T9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(U21&lt;&gt;SUM(U16,U17,U18)," * Total TX_RTT Done for CD_4 "&amp;T8&amp;" "&amp;U9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(V21&lt;&gt;SUM(V16,V17,V18)," * Total TX_RTT Done for CD_4 "&amp;V8&amp;" "&amp;V9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(W21&lt;&gt;SUM(W16,W17,W18)," * Total TX_RTT Done for CD_4 "&amp;V8&amp;" "&amp;W9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(X21&lt;&gt;SUM(X16,X17,X18)," * Total TX_RTT Done for CD_4 "&amp;X8&amp;" "&amp;X9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(Y21&lt;&gt;SUM(Y16,Y17,Y18)," * Total TX_RTT Done for CD_4 "&amp;X8&amp;" "&amp;Y9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(Z21&lt;&gt;SUM(Z16,Z17,Z18)," * Total TX_RTT Done for CD_4 "&amp;Z8&amp;" "&amp;Z9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""),IF(AA21&lt;&gt;SUM(AA16,AA17,AA18)," * Total TX_RTT Done for CD_4 "&amp;Z8&amp;" "&amp;AA9&amp;" Should be equal to  Total TX_RTT"&amp;CHAR(10),""))</f>
         <v/>
       </c>
-      <c r="AL21" s="375"/>
+      <c r="AL21" s="295"/>
       <c r="AM21" s="53"/>
-      <c r="AN21" s="299"/>
+      <c r="AN21" s="373"/>
       <c r="AO21" s="33"/>
       <c r="AP21" s="34"/>
     </row>
     <row r="22" spans="1:42" s="122" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A22" s="385"/>
+      <c r="A22" s="307"/>
       <c r="B22" s="132" t="s">
         <v>183</v>
       </c>
       <c r="C22" s="231" t="s">
         <v>187</v>
       </c>
-      <c r="D22" s="397"/>
-      <c r="E22" s="398"/>
-      <c r="F22" s="398"/>
-      <c r="G22" s="398"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="247"/>
+      <c r="F22" s="247"/>
+      <c r="G22" s="247"/>
       <c r="H22" s="134"/>
       <c r="I22" s="134"/>
       <c r="J22" s="134"/>
@@ -7911,24 +7914,24 @@
         <v>0</v>
       </c>
       <c r="AK22" s="40"/>
-      <c r="AL22" s="375"/>
+      <c r="AL22" s="295"/>
       <c r="AM22" s="53"/>
-      <c r="AN22" s="299"/>
+      <c r="AN22" s="373"/>
       <c r="AO22" s="33"/>
       <c r="AP22" s="34"/>
     </row>
     <row r="23" spans="1:42" s="122" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A23" s="385"/>
+      <c r="A23" s="307"/>
       <c r="B23" s="132" t="s">
         <v>184</v>
       </c>
       <c r="C23" s="233" t="s">
         <v>188</v>
       </c>
-      <c r="D23" s="399"/>
-      <c r="E23" s="400"/>
-      <c r="F23" s="400"/>
-      <c r="G23" s="400"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="249"/>
+      <c r="F23" s="249"/>
+      <c r="G23" s="249"/>
       <c r="H23" s="154"/>
       <c r="I23" s="154"/>
       <c r="J23" s="154"/>
@@ -7968,14 +7971,14 @@
         <v>0</v>
       </c>
       <c r="AK23" s="40"/>
-      <c r="AL23" s="375"/>
+      <c r="AL23" s="295"/>
       <c r="AM23" s="53"/>
-      <c r="AN23" s="299"/>
+      <c r="AN23" s="373"/>
       <c r="AO23" s="33"/>
       <c r="AP23" s="34"/>
     </row>
     <row r="24" spans="1:42" s="122" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A24" s="385"/>
+      <c r="A24" s="307"/>
       <c r="B24" s="132" t="s">
         <v>185</v>
       </c>
@@ -8025,14 +8028,14 @@
         <v>0</v>
       </c>
       <c r="AK24" s="37"/>
-      <c r="AL24" s="375"/>
+      <c r="AL24" s="295"/>
       <c r="AM24" s="38"/>
-      <c r="AN24" s="299"/>
+      <c r="AN24" s="373"/>
       <c r="AO24" s="51"/>
       <c r="AP24" s="34"/>
     </row>
     <row r="25" spans="1:42" s="229" customFormat="1" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A25" s="386"/>
+      <c r="A25" s="308"/>
       <c r="B25" s="243" t="s">
         <v>191</v>
       </c>
@@ -8082,60 +8085,60 @@
         <v>0</v>
       </c>
       <c r="AK25" s="37"/>
-      <c r="AL25" s="375"/>
+      <c r="AL25" s="295"/>
       <c r="AM25" s="38"/>
-      <c r="AN25" s="299"/>
+      <c r="AN25" s="373"/>
       <c r="AO25" s="51"/>
       <c r="AP25" s="34"/>
     </row>
     <row r="26" spans="1:42" ht="33.4" customHeight="1" thickBot="1">
-      <c r="A26" s="380" t="s">
+      <c r="A26" s="300" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="381"/>
-      <c r="C26" s="381"/>
-      <c r="D26" s="381"/>
-      <c r="E26" s="381"/>
-      <c r="F26" s="381"/>
-      <c r="G26" s="381"/>
-      <c r="H26" s="381"/>
-      <c r="I26" s="381"/>
-      <c r="J26" s="381"/>
-      <c r="K26" s="381"/>
-      <c r="L26" s="381"/>
-      <c r="M26" s="381"/>
-      <c r="N26" s="381"/>
-      <c r="O26" s="381"/>
-      <c r="P26" s="381"/>
-      <c r="Q26" s="381"/>
-      <c r="R26" s="381"/>
-      <c r="S26" s="381"/>
-      <c r="T26" s="381"/>
-      <c r="U26" s="381"/>
-      <c r="V26" s="381"/>
-      <c r="W26" s="381"/>
-      <c r="X26" s="381"/>
-      <c r="Y26" s="381"/>
-      <c r="Z26" s="382"/>
-      <c r="AA26" s="382"/>
-      <c r="AB26" s="382"/>
-      <c r="AC26" s="382"/>
-      <c r="AD26" s="382"/>
-      <c r="AE26" s="382"/>
-      <c r="AF26" s="382"/>
-      <c r="AG26" s="382"/>
-      <c r="AH26" s="382"/>
-      <c r="AI26" s="382"/>
-      <c r="AJ26" s="382"/>
+      <c r="B26" s="301"/>
+      <c r="C26" s="301"/>
+      <c r="D26" s="301"/>
+      <c r="E26" s="301"/>
+      <c r="F26" s="301"/>
+      <c r="G26" s="301"/>
+      <c r="H26" s="301"/>
+      <c r="I26" s="301"/>
+      <c r="J26" s="301"/>
+      <c r="K26" s="301"/>
+      <c r="L26" s="301"/>
+      <c r="M26" s="301"/>
+      <c r="N26" s="301"/>
+      <c r="O26" s="301"/>
+      <c r="P26" s="301"/>
+      <c r="Q26" s="301"/>
+      <c r="R26" s="301"/>
+      <c r="S26" s="301"/>
+      <c r="T26" s="301"/>
+      <c r="U26" s="301"/>
+      <c r="V26" s="301"/>
+      <c r="W26" s="301"/>
+      <c r="X26" s="301"/>
+      <c r="Y26" s="301"/>
+      <c r="Z26" s="302"/>
+      <c r="AA26" s="302"/>
+      <c r="AB26" s="302"/>
+      <c r="AC26" s="302"/>
+      <c r="AD26" s="302"/>
+      <c r="AE26" s="302"/>
+      <c r="AF26" s="302"/>
+      <c r="AG26" s="302"/>
+      <c r="AH26" s="302"/>
+      <c r="AI26" s="302"/>
+      <c r="AJ26" s="302"/>
       <c r="AK26" s="60"/>
-      <c r="AL26" s="375"/>
+      <c r="AL26" s="295"/>
       <c r="AM26" s="60"/>
-      <c r="AN26" s="299"/>
+      <c r="AN26" s="373"/>
       <c r="AO26" s="33"/>
       <c r="AP26" s="34"/>
     </row>
     <row r="27" spans="1:42" ht="41.25" customHeight="1">
-      <c r="A27" s="377" t="s">
+      <c r="A27" s="297" t="s">
         <v>172</v>
       </c>
       <c r="B27" s="115" t="s">
@@ -8187,14 +8190,14 @@
         <v>0</v>
       </c>
       <c r="AK27" s="31"/>
-      <c r="AL27" s="375"/>
+      <c r="AL27" s="295"/>
       <c r="AM27" s="32"/>
-      <c r="AN27" s="299"/>
+      <c r="AN27" s="373"/>
       <c r="AO27" s="33"/>
       <c r="AP27" s="34"/>
     </row>
     <row r="28" spans="1:42" s="36" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A28" s="378"/>
+      <c r="A28" s="298"/>
       <c r="B28" s="116" t="s">
         <v>158</v>
       </c>
@@ -8244,14 +8247,14 @@
         <v>0</v>
       </c>
       <c r="AK28" s="31"/>
-      <c r="AL28" s="375"/>
+      <c r="AL28" s="295"/>
       <c r="AM28" s="32"/>
-      <c r="AN28" s="299"/>
+      <c r="AN28" s="373"/>
       <c r="AO28" s="33"/>
       <c r="AP28" s="34"/>
     </row>
     <row r="29" spans="1:42" s="36" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A29" s="378"/>
+      <c r="A29" s="298"/>
       <c r="B29" s="116" t="s">
         <v>159</v>
       </c>
@@ -8391,14 +8394,14 @@
         <v>0</v>
       </c>
       <c r="AK29" s="31"/>
-      <c r="AL29" s="375"/>
+      <c r="AL29" s="295"/>
       <c r="AM29" s="32"/>
-      <c r="AN29" s="299"/>
+      <c r="AN29" s="373"/>
       <c r="AO29" s="33"/>
       <c r="AP29" s="34"/>
     </row>
     <row r="30" spans="1:42" s="36" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A30" s="378"/>
+      <c r="A30" s="298"/>
       <c r="B30" s="116" t="s">
         <v>173</v>
       </c>
@@ -8538,14 +8541,14 @@
         <v>0</v>
       </c>
       <c r="AK30" s="37"/>
-      <c r="AL30" s="375"/>
+      <c r="AL30" s="295"/>
       <c r="AM30" s="38"/>
-      <c r="AN30" s="299"/>
+      <c r="AN30" s="373"/>
       <c r="AO30" s="33"/>
       <c r="AP30" s="34"/>
     </row>
     <row r="31" spans="1:42" s="36" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A31" s="378"/>
+      <c r="A31" s="298"/>
       <c r="B31" s="116" t="s">
         <v>171</v>
       </c>
@@ -8685,14 +8688,14 @@
         <v>0</v>
       </c>
       <c r="AK31" s="37"/>
-      <c r="AL31" s="375"/>
+      <c r="AL31" s="295"/>
       <c r="AM31" s="38"/>
-      <c r="AN31" s="299"/>
+      <c r="AN31" s="373"/>
       <c r="AO31" s="33"/>
       <c r="AP31" s="34"/>
     </row>
     <row r="32" spans="1:42" ht="41.25" customHeight="1">
-      <c r="A32" s="378"/>
+      <c r="A32" s="298"/>
       <c r="B32" s="116" t="s">
         <v>146</v>
       </c>
@@ -8835,17 +8838,17 @@
         <f>CONCATENATE(IF(AJ34&gt;0,IF(AJ34&lt;&gt;AJ42,CONCATENATE("Accounted Patients Under LTFU [",AJ42,"] is not equal to expected patients to account for [",AJ34,"] "),""),""))</f>
         <v/>
       </c>
-      <c r="AL32" s="375"/>
+      <c r="AL32" s="295"/>
       <c r="AM32" s="38" t="str">
         <f>CONCATENATE(IF(SUM(AJ10:AJ15)&gt;AJ34,IF(AJ34&lt;0,CONCATENATE("You seem to have acounted for more patients under LTFU returning to Care [",SUM(AJ10:AJ15),"] than what you should account for [",AJ34,"] "),""),""))</f>
         <v/>
       </c>
-      <c r="AN32" s="299"/>
+      <c r="AN32" s="373"/>
       <c r="AO32" s="33"/>
       <c r="AP32" s="34"/>
     </row>
     <row r="33" spans="1:42" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A33" s="378"/>
+      <c r="A33" s="298"/>
       <c r="B33" s="117" t="s">
         <v>157</v>
       </c>
@@ -8895,14 +8898,14 @@
         <v>0</v>
       </c>
       <c r="AK33" s="31"/>
-      <c r="AL33" s="375"/>
+      <c r="AL33" s="295"/>
       <c r="AM33" s="32"/>
-      <c r="AN33" s="299"/>
+      <c r="AN33" s="373"/>
       <c r="AO33" s="33"/>
       <c r="AP33" s="34"/>
     </row>
     <row r="34" spans="1:42" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A34" s="379"/>
+      <c r="A34" s="299"/>
       <c r="B34" s="118" t="s">
         <v>147</v>
       </c>
@@ -9042,63 +9045,63 @@
         <v>0</v>
       </c>
       <c r="AK34" s="37"/>
-      <c r="AL34" s="375"/>
+      <c r="AL34" s="295"/>
       <c r="AM34" s="38" t="str">
         <f>CONCATENATE(IF(SUM(AJ10:AJ15)&gt;AJ34,IF(AJ34&gt;0,"You seem to have Gains that have not been accounted for under LTFU returning to Care",""),""))</f>
         <v/>
       </c>
-      <c r="AN34" s="299"/>
+      <c r="AN34" s="373"/>
       <c r="AO34" s="33"/>
       <c r="AP34" s="34"/>
     </row>
     <row r="35" spans="1:42" s="47" customFormat="1" ht="31.15" customHeight="1" thickBot="1">
-      <c r="A35" s="369" t="s">
+      <c r="A35" s="289" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="370"/>
-      <c r="C35" s="370"/>
-      <c r="D35" s="371"/>
-      <c r="E35" s="371"/>
-      <c r="F35" s="371"/>
-      <c r="G35" s="371"/>
-      <c r="H35" s="371"/>
-      <c r="I35" s="371"/>
-      <c r="J35" s="371"/>
-      <c r="K35" s="371"/>
-      <c r="L35" s="371"/>
-      <c r="M35" s="371"/>
-      <c r="N35" s="371"/>
-      <c r="O35" s="371"/>
-      <c r="P35" s="371"/>
-      <c r="Q35" s="371"/>
-      <c r="R35" s="371"/>
-      <c r="S35" s="371"/>
-      <c r="T35" s="371"/>
-      <c r="U35" s="371"/>
-      <c r="V35" s="371"/>
-      <c r="W35" s="371"/>
-      <c r="X35" s="371"/>
-      <c r="Y35" s="371"/>
-      <c r="Z35" s="371"/>
-      <c r="AA35" s="371"/>
-      <c r="AB35" s="372"/>
-      <c r="AC35" s="372"/>
-      <c r="AD35" s="372"/>
-      <c r="AE35" s="372"/>
-      <c r="AF35" s="372"/>
-      <c r="AG35" s="372"/>
-      <c r="AH35" s="372"/>
-      <c r="AI35" s="372"/>
-      <c r="AJ35" s="373"/>
+      <c r="B35" s="290"/>
+      <c r="C35" s="290"/>
+      <c r="D35" s="291"/>
+      <c r="E35" s="291"/>
+      <c r="F35" s="291"/>
+      <c r="G35" s="291"/>
+      <c r="H35" s="291"/>
+      <c r="I35" s="291"/>
+      <c r="J35" s="291"/>
+      <c r="K35" s="291"/>
+      <c r="L35" s="291"/>
+      <c r="M35" s="291"/>
+      <c r="N35" s="291"/>
+      <c r="O35" s="291"/>
+      <c r="P35" s="291"/>
+      <c r="Q35" s="291"/>
+      <c r="R35" s="291"/>
+      <c r="S35" s="291"/>
+      <c r="T35" s="291"/>
+      <c r="U35" s="291"/>
+      <c r="V35" s="291"/>
+      <c r="W35" s="291"/>
+      <c r="X35" s="291"/>
+      <c r="Y35" s="291"/>
+      <c r="Z35" s="291"/>
+      <c r="AA35" s="291"/>
+      <c r="AB35" s="292"/>
+      <c r="AC35" s="292"/>
+      <c r="AD35" s="292"/>
+      <c r="AE35" s="292"/>
+      <c r="AF35" s="292"/>
+      <c r="AG35" s="292"/>
+      <c r="AH35" s="292"/>
+      <c r="AI35" s="292"/>
+      <c r="AJ35" s="293"/>
       <c r="AK35" s="40"/>
-      <c r="AL35" s="375"/>
+      <c r="AL35" s="295"/>
       <c r="AM35" s="53"/>
-      <c r="AN35" s="299"/>
+      <c r="AN35" s="373"/>
       <c r="AO35" s="58"/>
       <c r="AP35" s="59"/>
     </row>
     <row r="36" spans="1:42" ht="33.950000000000003" customHeight="1">
-      <c r="A36" s="383" t="s">
+      <c r="A36" s="303" t="s">
         <v>113</v>
       </c>
       <c r="B36" s="54" t="s">
@@ -9153,14 +9156,14 @@
         <f>CONCATENATE(IF(D36&lt;SUM(D43,D44,D45,D46,D47,D48,D49)," * Total Died  for Age "&amp;D8&amp;" "&amp;D9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(E36&lt;SUM(E43,E44,E45,E46,E47,E48,E49)," * Total Died  for Age "&amp;D8&amp;" "&amp;E9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(F36&lt;SUM(F43,F44,F45,F46,F47,F48,F49)," * Total Died  for Age "&amp;F8&amp;" "&amp;F9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(G36&lt;SUM(G43,G44,G45,G46,G47,G48,G49)," * Total Died  for Age "&amp;F8&amp;" "&amp;G9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(H36&lt;SUM(H43,H44,H45,H46,H47,H48,H49)," * Total Died  for Age "&amp;H8&amp;" "&amp;H9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(I36&lt;SUM(I43,I44,I45,I46,I47,I48,I49)," * Total Died  for Age "&amp;H8&amp;" "&amp;I9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(J36&lt;SUM(J43,J44,J45,J46,J47,J48,J49)," * Total Died  for Age "&amp;J8&amp;" "&amp;J9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(K36&lt;SUM(K43,K44,K45,K46,K47,K48,K49)," * Total Died  for Age "&amp;J8&amp;" "&amp;K9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(L36&lt;SUM(L43,L44,L45,L46,L47,L48,L49)," * Total Died  for Age "&amp;L8&amp;" "&amp;L9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(M36&lt;SUM(M43,M44,M45,M46,M47,M48,M49)," * Total Died  for Age "&amp;L8&amp;" "&amp;M9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(N36&lt;SUM(N43,N44,N45,N46,N47,N48,N49)," * Total Died  for Age "&amp;N8&amp;" "&amp;N9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(O36&lt;SUM(O43,O44,O45,O46,O47,O48,O49)," * Total Died  for Age "&amp;N8&amp;" "&amp;O9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(P36&lt;SUM(P43,P44,P45,P46,P47,P48,P49)," * Total Died  for Age "&amp;P8&amp;" "&amp;P9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(Q36&lt;SUM(Q43,Q44,Q45,Q46,Q47,Q48,Q49)," * Total Died  for Age "&amp;P8&amp;" "&amp;Q9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(R36&lt;SUM(R43,R44,R45,R46,R47,R48,R49)," * Total Died  for Age "&amp;R8&amp;" "&amp;R9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(S36&lt;SUM(S43,S44,S45,S46,S47,S48,S49)," * Total Died  for Age "&amp;R8&amp;" "&amp;S9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(T36&lt;SUM(T43,T44,T45,T46,T47,T48,T49)," * Total Died  for Age "&amp;T8&amp;" "&amp;T9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(U36&lt;SUM(U43,U44,U45,U46,U47,U48,U49)," * Total Died  for Age "&amp;T8&amp;" "&amp;U9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(V36&lt;SUM(V43,V44,V45,V46,V47,V48,V49)," * Total Died  for Age "&amp;V8&amp;" "&amp;V9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(W36&lt;SUM(W43,W44,W45,W46,W47,W48,W49)," * Total Died  for Age "&amp;V8&amp;" "&amp;W9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(X36&lt;SUM(X43,X44,X45,X46,X47,X48,X49)," * Total Died  for Age "&amp;X8&amp;" "&amp;X9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(Y36&lt;SUM(Y43,Y44,Y45,Y46,Y47,Y48,Y49)," * Total Died  for Age "&amp;X8&amp;" "&amp;Y9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(Z36&lt;SUM(Z43,Z44,Z45,Z46,Z47,Z48,Z49)," * Total Died  for Age "&amp;Z8&amp;" "&amp;Z9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""),IF(AA36&lt;SUM(AA43,AA44,AA45,AA46,AA47,AA48,AA49)," * Total Died  for Age "&amp;Z8&amp;" "&amp;AA9&amp;" is less than sum of Total Causes of Death F08-05 to F08-11"&amp;CHAR(10),""))</f>
         <v/>
       </c>
-      <c r="AL36" s="375"/>
+      <c r="AL36" s="295"/>
       <c r="AM36" s="32"/>
-      <c r="AN36" s="299"/>
+      <c r="AN36" s="373"/>
       <c r="AO36" s="33"/>
       <c r="AP36" s="34"/>
     </row>
     <row r="37" spans="1:42" s="44" customFormat="1" ht="33.950000000000003" customHeight="1">
-      <c r="A37" s="362"/>
+      <c r="A37" s="304"/>
       <c r="B37" s="42" t="s">
         <v>138</v>
       </c>
@@ -9210,14 +9213,14 @@
         <v>0</v>
       </c>
       <c r="AK37" s="31"/>
-      <c r="AL37" s="375"/>
+      <c r="AL37" s="295"/>
       <c r="AM37" s="43"/>
-      <c r="AN37" s="299"/>
+      <c r="AN37" s="373"/>
       <c r="AO37" s="33"/>
       <c r="AP37" s="34"/>
     </row>
     <row r="38" spans="1:42" ht="33.950000000000003" customHeight="1">
-      <c r="A38" s="362"/>
+      <c r="A38" s="304"/>
       <c r="B38" s="42" t="s">
         <v>136</v>
       </c>
@@ -9267,14 +9270,14 @@
         <v>0</v>
       </c>
       <c r="AK38" s="31"/>
-      <c r="AL38" s="375"/>
+      <c r="AL38" s="295"/>
       <c r="AM38" s="32"/>
-      <c r="AN38" s="299"/>
+      <c r="AN38" s="373"/>
       <c r="AO38" s="33"/>
       <c r="AP38" s="34"/>
     </row>
     <row r="39" spans="1:42" ht="33.950000000000003" customHeight="1">
-      <c r="A39" s="362"/>
+      <c r="A39" s="304"/>
       <c r="B39" s="42" t="s">
         <v>137</v>
       </c>
@@ -9324,14 +9327,14 @@
         <v>0</v>
       </c>
       <c r="AK39" s="31"/>
-      <c r="AL39" s="375"/>
+      <c r="AL39" s="295"/>
       <c r="AM39" s="32"/>
-      <c r="AN39" s="299"/>
+      <c r="AN39" s="373"/>
       <c r="AO39" s="33"/>
       <c r="AP39" s="34"/>
     </row>
     <row r="40" spans="1:42" ht="33.950000000000003" customHeight="1">
-      <c r="A40" s="362"/>
+      <c r="A40" s="304"/>
       <c r="B40" s="42" t="s">
         <v>96</v>
       </c>
@@ -9381,14 +9384,14 @@
         <v>0</v>
       </c>
       <c r="AK40" s="31"/>
-      <c r="AL40" s="375"/>
+      <c r="AL40" s="295"/>
       <c r="AM40" s="32"/>
-      <c r="AN40" s="299"/>
+      <c r="AN40" s="373"/>
       <c r="AO40" s="33"/>
       <c r="AP40" s="34"/>
     </row>
     <row r="41" spans="1:42" ht="33.950000000000003" customHeight="1" thickBot="1">
-      <c r="A41" s="362"/>
+      <c r="A41" s="304"/>
       <c r="B41" s="42" t="s">
         <v>76</v>
       </c>
@@ -9438,14 +9441,14 @@
         <v>0</v>
       </c>
       <c r="AK41" s="31"/>
-      <c r="AL41" s="375"/>
+      <c r="AL41" s="295"/>
       <c r="AM41" s="32"/>
-      <c r="AN41" s="299"/>
+      <c r="AN41" s="373"/>
       <c r="AO41" s="33"/>
       <c r="AP41" s="34"/>
     </row>
     <row r="42" spans="1:42" ht="33.950000000000003" customHeight="1" thickBot="1">
-      <c r="A42" s="363"/>
+      <c r="A42" s="305"/>
       <c r="B42" s="207" t="s">
         <v>114</v>
       </c>
@@ -9585,14 +9588,14 @@
         <v>0</v>
       </c>
       <c r="AK42" s="31"/>
-      <c r="AL42" s="375"/>
+      <c r="AL42" s="295"/>
       <c r="AM42" s="32"/>
-      <c r="AN42" s="299"/>
+      <c r="AN42" s="373"/>
       <c r="AO42" s="33"/>
       <c r="AP42" s="34"/>
     </row>
     <row r="43" spans="1:42" ht="33" customHeight="1">
-      <c r="A43" s="361" t="s">
+      <c r="A43" s="360" t="s">
         <v>139</v>
       </c>
       <c r="B43" s="55" t="s">
@@ -9644,14 +9647,14 @@
         <v>0</v>
       </c>
       <c r="AK43" s="31"/>
-      <c r="AL43" s="375"/>
+      <c r="AL43" s="295"/>
       <c r="AM43" s="32"/>
-      <c r="AN43" s="299"/>
+      <c r="AN43" s="373"/>
       <c r="AO43" s="33"/>
       <c r="AP43" s="34"/>
     </row>
     <row r="44" spans="1:42" ht="33" customHeight="1">
-      <c r="A44" s="362"/>
+      <c r="A44" s="304"/>
       <c r="B44" s="56" t="s">
         <v>93</v>
       </c>
@@ -9701,14 +9704,14 @@
         <v>0</v>
       </c>
       <c r="AK44" s="31"/>
-      <c r="AL44" s="375"/>
+      <c r="AL44" s="295"/>
       <c r="AM44" s="32"/>
-      <c r="AN44" s="299"/>
+      <c r="AN44" s="373"/>
       <c r="AO44" s="33"/>
       <c r="AP44" s="34"/>
     </row>
     <row r="45" spans="1:42" ht="33" customHeight="1">
-      <c r="A45" s="362"/>
+      <c r="A45" s="304"/>
       <c r="B45" s="56" t="s">
         <v>97</v>
       </c>
@@ -9758,14 +9761,14 @@
         <v>0</v>
       </c>
       <c r="AK45" s="31"/>
-      <c r="AL45" s="375"/>
+      <c r="AL45" s="295"/>
       <c r="AM45" s="32"/>
-      <c r="AN45" s="299"/>
+      <c r="AN45" s="373"/>
       <c r="AO45" s="33"/>
       <c r="AP45" s="34"/>
     </row>
     <row r="46" spans="1:42" s="44" customFormat="1" ht="33" customHeight="1">
-      <c r="A46" s="362"/>
+      <c r="A46" s="304"/>
       <c r="B46" s="221" t="s">
         <v>46</v>
       </c>
@@ -9815,14 +9818,14 @@
         <v>0</v>
       </c>
       <c r="AK46" s="31"/>
-      <c r="AL46" s="375"/>
+      <c r="AL46" s="295"/>
       <c r="AM46" s="43"/>
-      <c r="AN46" s="299"/>
+      <c r="AN46" s="373"/>
       <c r="AO46" s="33"/>
       <c r="AP46" s="34"/>
     </row>
     <row r="47" spans="1:42" ht="33" customHeight="1">
-      <c r="A47" s="362"/>
+      <c r="A47" s="304"/>
       <c r="B47" s="56" t="s">
         <v>94</v>
       </c>
@@ -9872,14 +9875,14 @@
         <v>0</v>
       </c>
       <c r="AK47" s="31"/>
-      <c r="AL47" s="375"/>
+      <c r="AL47" s="295"/>
       <c r="AM47" s="32"/>
-      <c r="AN47" s="299"/>
+      <c r="AN47" s="373"/>
       <c r="AO47" s="33"/>
       <c r="AP47" s="34"/>
     </row>
     <row r="48" spans="1:42" ht="33" customHeight="1">
-      <c r="A48" s="362"/>
+      <c r="A48" s="304"/>
       <c r="B48" s="56" t="s">
         <v>47</v>
       </c>
@@ -9929,14 +9932,14 @@
         <v>0</v>
       </c>
       <c r="AK48" s="31"/>
-      <c r="AL48" s="375"/>
+      <c r="AL48" s="295"/>
       <c r="AM48" s="32"/>
-      <c r="AN48" s="299"/>
+      <c r="AN48" s="373"/>
       <c r="AO48" s="33"/>
       <c r="AP48" s="34"/>
     </row>
     <row r="49" spans="1:42" ht="33" customHeight="1" thickBot="1">
-      <c r="A49" s="363"/>
+      <c r="A49" s="305"/>
       <c r="B49" s="57" t="s">
         <v>48</v>
       </c>
@@ -9986,9 +9989,9 @@
         <v>0</v>
       </c>
       <c r="AK49" s="31"/>
-      <c r="AL49" s="376"/>
+      <c r="AL49" s="296"/>
       <c r="AM49" s="32"/>
-      <c r="AN49" s="299"/>
+      <c r="AN49" s="373"/>
       <c r="AO49" s="33"/>
       <c r="AP49" s="34"/>
     </row>
@@ -10021,2247 +10024,2306 @@
       <c r="M52" s="12"/>
     </row>
     <row r="53" spans="1:42" ht="21.4" thickBot="1">
-      <c r="A53" s="387"/>
-      <c r="B53" s="388"/>
-      <c r="C53" s="272"/>
-      <c r="D53" s="389"/>
-      <c r="E53" s="389"/>
-      <c r="F53" s="389"/>
-      <c r="G53" s="389"/>
-      <c r="H53" s="389"/>
-      <c r="I53" s="389"/>
-      <c r="J53" s="389"/>
-      <c r="K53" s="389"/>
-      <c r="L53" s="389"/>
-      <c r="M53" s="389"/>
-      <c r="N53" s="389"/>
-      <c r="O53" s="389"/>
-      <c r="P53" s="389"/>
-      <c r="Q53" s="389"/>
-      <c r="R53" s="389"/>
-      <c r="S53" s="389"/>
-      <c r="T53" s="389"/>
-      <c r="U53" s="389"/>
-      <c r="V53" s="389"/>
-      <c r="W53" s="389"/>
-      <c r="X53" s="389"/>
-      <c r="Y53" s="389"/>
-      <c r="Z53" s="389"/>
-      <c r="AA53" s="389"/>
-      <c r="AB53" s="389"/>
-      <c r="AC53" s="389"/>
-      <c r="AD53" s="389"/>
-      <c r="AE53" s="389"/>
-      <c r="AF53" s="389"/>
-      <c r="AG53" s="389"/>
-      <c r="AH53" s="389"/>
-      <c r="AI53" s="389"/>
-      <c r="AJ53" s="389"/>
-      <c r="AK53" s="390"/>
-      <c r="AL53" s="391"/>
-      <c r="AM53" s="389"/>
-      <c r="AN53" s="389"/>
+      <c r="A53" s="276"/>
+      <c r="B53" s="277"/>
+      <c r="C53" s="278"/>
+      <c r="D53" s="279"/>
+      <c r="E53" s="279"/>
+      <c r="F53" s="279"/>
+      <c r="G53" s="279"/>
+      <c r="H53" s="279"/>
+      <c r="I53" s="279"/>
+      <c r="J53" s="279"/>
+      <c r="K53" s="279"/>
+      <c r="L53" s="279"/>
+      <c r="M53" s="279"/>
+      <c r="N53" s="279"/>
+      <c r="O53" s="279"/>
+      <c r="P53" s="279"/>
+      <c r="Q53" s="279"/>
+      <c r="R53" s="279"/>
+      <c r="S53" s="279"/>
+      <c r="T53" s="279"/>
+      <c r="U53" s="279"/>
+      <c r="V53" s="279"/>
+      <c r="W53" s="279"/>
+      <c r="X53" s="279"/>
+      <c r="Y53" s="279"/>
+      <c r="Z53" s="279"/>
+      <c r="AA53" s="279"/>
+      <c r="AB53" s="279"/>
+      <c r="AC53" s="279"/>
+      <c r="AD53" s="279"/>
+      <c r="AE53" s="279"/>
+      <c r="AF53" s="279"/>
+      <c r="AG53" s="279"/>
+      <c r="AH53" s="279"/>
+      <c r="AI53" s="279"/>
+      <c r="AJ53" s="279"/>
+      <c r="AK53" s="280"/>
+      <c r="AL53" s="281"/>
+      <c r="AM53" s="279"/>
+      <c r="AN53" s="279"/>
     </row>
     <row r="54" spans="1:42" ht="30.75" customHeight="1">
-      <c r="A54" s="338" t="str">
+      <c r="A54" s="336" t="str">
         <f>CONCATENATE(AL10,AL27)</f>
         <v/>
       </c>
-      <c r="B54" s="339"/>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
-      <c r="G54" s="339"/>
-      <c r="H54" s="339"/>
-      <c r="I54" s="339"/>
-      <c r="J54" s="339"/>
-      <c r="K54" s="339"/>
-      <c r="L54" s="340"/>
-      <c r="M54" s="347" t="str">
+      <c r="B54" s="337"/>
+      <c r="C54" s="337"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
+      <c r="G54" s="337"/>
+      <c r="H54" s="337"/>
+      <c r="I54" s="337"/>
+      <c r="J54" s="337"/>
+      <c r="K54" s="337"/>
+      <c r="L54" s="338"/>
+      <c r="M54" s="345" t="str">
         <f>IF(LEN(A54)&lt;=0,"","Please ensure you solve the errors appearing on the left . However, In the cases where the errors are valid and can be explained ( We expect this to be very rare cases), Please delete this message and type the  justification for the error here)")</f>
         <v/>
       </c>
-      <c r="N54" s="348"/>
-      <c r="O54" s="348"/>
-      <c r="P54" s="348"/>
-      <c r="Q54" s="348"/>
-      <c r="R54" s="348"/>
-      <c r="S54" s="348"/>
-      <c r="T54" s="348"/>
-      <c r="U54" s="348"/>
-      <c r="V54" s="348"/>
-      <c r="W54" s="348"/>
-      <c r="X54" s="348"/>
-      <c r="Y54" s="348"/>
-      <c r="Z54" s="348"/>
-      <c r="AA54" s="348"/>
-      <c r="AB54" s="348"/>
-      <c r="AC54" s="348"/>
-      <c r="AD54" s="348"/>
-      <c r="AE54" s="348"/>
-      <c r="AF54" s="348"/>
-      <c r="AG54" s="348"/>
-      <c r="AH54" s="348"/>
-      <c r="AI54" s="348"/>
-      <c r="AJ54" s="348"/>
-      <c r="AK54" s="348"/>
-      <c r="AL54" s="348"/>
-      <c r="AM54" s="348"/>
-      <c r="AN54" s="349"/>
+      <c r="N54" s="346"/>
+      <c r="O54" s="346"/>
+      <c r="P54" s="346"/>
+      <c r="Q54" s="346"/>
+      <c r="R54" s="346"/>
+      <c r="S54" s="346"/>
+      <c r="T54" s="346"/>
+      <c r="U54" s="346"/>
+      <c r="V54" s="346"/>
+      <c r="W54" s="346"/>
+      <c r="X54" s="346"/>
+      <c r="Y54" s="346"/>
+      <c r="Z54" s="346"/>
+      <c r="AA54" s="346"/>
+      <c r="AB54" s="346"/>
+      <c r="AC54" s="346"/>
+      <c r="AD54" s="346"/>
+      <c r="AE54" s="346"/>
+      <c r="AF54" s="346"/>
+      <c r="AG54" s="346"/>
+      <c r="AH54" s="346"/>
+      <c r="AI54" s="346"/>
+      <c r="AJ54" s="346"/>
+      <c r="AK54" s="346"/>
+      <c r="AL54" s="346"/>
+      <c r="AM54" s="346"/>
+      <c r="AN54" s="347"/>
     </row>
     <row r="55" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A55" s="341"/>
-      <c r="B55" s="342"/>
-      <c r="C55" s="342"/>
-      <c r="D55" s="342"/>
-      <c r="E55" s="342"/>
-      <c r="F55" s="342"/>
-      <c r="G55" s="342"/>
-      <c r="H55" s="342"/>
-      <c r="I55" s="342"/>
-      <c r="J55" s="342"/>
-      <c r="K55" s="342"/>
-      <c r="L55" s="343"/>
-      <c r="M55" s="350"/>
-      <c r="N55" s="351"/>
-      <c r="O55" s="351"/>
-      <c r="P55" s="351"/>
-      <c r="Q55" s="351"/>
-      <c r="R55" s="351"/>
-      <c r="S55" s="351"/>
-      <c r="T55" s="351"/>
-      <c r="U55" s="351"/>
-      <c r="V55" s="351"/>
-      <c r="W55" s="351"/>
-      <c r="X55" s="351"/>
-      <c r="Y55" s="351"/>
-      <c r="Z55" s="351"/>
-      <c r="AA55" s="351"/>
-      <c r="AB55" s="351"/>
-      <c r="AC55" s="351"/>
-      <c r="AD55" s="351"/>
-      <c r="AE55" s="351"/>
-      <c r="AF55" s="351"/>
-      <c r="AG55" s="351"/>
-      <c r="AH55" s="351"/>
-      <c r="AI55" s="351"/>
-      <c r="AJ55" s="351"/>
-      <c r="AK55" s="351"/>
-      <c r="AL55" s="351"/>
-      <c r="AM55" s="351"/>
-      <c r="AN55" s="352"/>
+      <c r="A55" s="339"/>
+      <c r="B55" s="340"/>
+      <c r="C55" s="340"/>
+      <c r="D55" s="340"/>
+      <c r="E55" s="340"/>
+      <c r="F55" s="340"/>
+      <c r="G55" s="340"/>
+      <c r="H55" s="340"/>
+      <c r="I55" s="340"/>
+      <c r="J55" s="340"/>
+      <c r="K55" s="340"/>
+      <c r="L55" s="341"/>
+      <c r="M55" s="348"/>
+      <c r="N55" s="349"/>
+      <c r="O55" s="349"/>
+      <c r="P55" s="349"/>
+      <c r="Q55" s="349"/>
+      <c r="R55" s="349"/>
+      <c r="S55" s="349"/>
+      <c r="T55" s="349"/>
+      <c r="U55" s="349"/>
+      <c r="V55" s="349"/>
+      <c r="W55" s="349"/>
+      <c r="X55" s="349"/>
+      <c r="Y55" s="349"/>
+      <c r="Z55" s="349"/>
+      <c r="AA55" s="349"/>
+      <c r="AB55" s="349"/>
+      <c r="AC55" s="349"/>
+      <c r="AD55" s="349"/>
+      <c r="AE55" s="349"/>
+      <c r="AF55" s="349"/>
+      <c r="AG55" s="349"/>
+      <c r="AH55" s="349"/>
+      <c r="AI55" s="349"/>
+      <c r="AJ55" s="349"/>
+      <c r="AK55" s="349"/>
+      <c r="AL55" s="349"/>
+      <c r="AM55" s="349"/>
+      <c r="AN55" s="350"/>
     </row>
     <row r="56" spans="1:42" ht="30.75" customHeight="1">
-      <c r="A56" s="341"/>
-      <c r="B56" s="342"/>
-      <c r="C56" s="342"/>
-      <c r="D56" s="342"/>
-      <c r="E56" s="342"/>
-      <c r="F56" s="342"/>
-      <c r="G56" s="342"/>
-      <c r="H56" s="342"/>
-      <c r="I56" s="342"/>
-      <c r="J56" s="342"/>
-      <c r="K56" s="342"/>
-      <c r="L56" s="343"/>
-      <c r="M56" s="350"/>
-      <c r="N56" s="351"/>
-      <c r="O56" s="351"/>
-      <c r="P56" s="351"/>
-      <c r="Q56" s="351"/>
-      <c r="R56" s="351"/>
-      <c r="S56" s="351"/>
-      <c r="T56" s="351"/>
-      <c r="U56" s="351"/>
-      <c r="V56" s="351"/>
-      <c r="W56" s="351"/>
-      <c r="X56" s="351"/>
-      <c r="Y56" s="351"/>
-      <c r="Z56" s="351"/>
-      <c r="AA56" s="351"/>
-      <c r="AB56" s="351"/>
-      <c r="AC56" s="351"/>
-      <c r="AD56" s="351"/>
-      <c r="AE56" s="351"/>
-      <c r="AF56" s="351"/>
-      <c r="AG56" s="351"/>
-      <c r="AH56" s="351"/>
-      <c r="AI56" s="351"/>
-      <c r="AJ56" s="351"/>
-      <c r="AK56" s="351"/>
-      <c r="AL56" s="351"/>
-      <c r="AM56" s="351"/>
-      <c r="AN56" s="352"/>
+      <c r="A56" s="339"/>
+      <c r="B56" s="340"/>
+      <c r="C56" s="340"/>
+      <c r="D56" s="340"/>
+      <c r="E56" s="340"/>
+      <c r="F56" s="340"/>
+      <c r="G56" s="340"/>
+      <c r="H56" s="340"/>
+      <c r="I56" s="340"/>
+      <c r="J56" s="340"/>
+      <c r="K56" s="340"/>
+      <c r="L56" s="341"/>
+      <c r="M56" s="348"/>
+      <c r="N56" s="349"/>
+      <c r="O56" s="349"/>
+      <c r="P56" s="349"/>
+      <c r="Q56" s="349"/>
+      <c r="R56" s="349"/>
+      <c r="S56" s="349"/>
+      <c r="T56" s="349"/>
+      <c r="U56" s="349"/>
+      <c r="V56" s="349"/>
+      <c r="W56" s="349"/>
+      <c r="X56" s="349"/>
+      <c r="Y56" s="349"/>
+      <c r="Z56" s="349"/>
+      <c r="AA56" s="349"/>
+      <c r="AB56" s="349"/>
+      <c r="AC56" s="349"/>
+      <c r="AD56" s="349"/>
+      <c r="AE56" s="349"/>
+      <c r="AF56" s="349"/>
+      <c r="AG56" s="349"/>
+      <c r="AH56" s="349"/>
+      <c r="AI56" s="349"/>
+      <c r="AJ56" s="349"/>
+      <c r="AK56" s="349"/>
+      <c r="AL56" s="349"/>
+      <c r="AM56" s="349"/>
+      <c r="AN56" s="350"/>
     </row>
     <row r="57" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A57" s="341"/>
-      <c r="B57" s="342"/>
-      <c r="C57" s="342"/>
-      <c r="D57" s="342"/>
-      <c r="E57" s="342"/>
-      <c r="F57" s="342"/>
-      <c r="G57" s="342"/>
-      <c r="H57" s="342"/>
-      <c r="I57" s="342"/>
-      <c r="J57" s="342"/>
-      <c r="K57" s="342"/>
-      <c r="L57" s="343"/>
-      <c r="M57" s="350"/>
-      <c r="N57" s="351"/>
-      <c r="O57" s="351"/>
-      <c r="P57" s="351"/>
-      <c r="Q57" s="351"/>
-      <c r="R57" s="351"/>
-      <c r="S57" s="351"/>
-      <c r="T57" s="351"/>
-      <c r="U57" s="351"/>
-      <c r="V57" s="351"/>
-      <c r="W57" s="351"/>
-      <c r="X57" s="351"/>
-      <c r="Y57" s="351"/>
-      <c r="Z57" s="351"/>
-      <c r="AA57" s="351"/>
-      <c r="AB57" s="351"/>
-      <c r="AC57" s="351"/>
-      <c r="AD57" s="351"/>
-      <c r="AE57" s="351"/>
-      <c r="AF57" s="351"/>
-      <c r="AG57" s="351"/>
-      <c r="AH57" s="351"/>
-      <c r="AI57" s="351"/>
-      <c r="AJ57" s="351"/>
-      <c r="AK57" s="351"/>
-      <c r="AL57" s="351"/>
-      <c r="AM57" s="351"/>
-      <c r="AN57" s="352"/>
+      <c r="A57" s="339"/>
+      <c r="B57" s="340"/>
+      <c r="C57" s="340"/>
+      <c r="D57" s="340"/>
+      <c r="E57" s="340"/>
+      <c r="F57" s="340"/>
+      <c r="G57" s="340"/>
+      <c r="H57" s="340"/>
+      <c r="I57" s="340"/>
+      <c r="J57" s="340"/>
+      <c r="K57" s="340"/>
+      <c r="L57" s="341"/>
+      <c r="M57" s="348"/>
+      <c r="N57" s="349"/>
+      <c r="O57" s="349"/>
+      <c r="P57" s="349"/>
+      <c r="Q57" s="349"/>
+      <c r="R57" s="349"/>
+      <c r="S57" s="349"/>
+      <c r="T57" s="349"/>
+      <c r="U57" s="349"/>
+      <c r="V57" s="349"/>
+      <c r="W57" s="349"/>
+      <c r="X57" s="349"/>
+      <c r="Y57" s="349"/>
+      <c r="Z57" s="349"/>
+      <c r="AA57" s="349"/>
+      <c r="AB57" s="349"/>
+      <c r="AC57" s="349"/>
+      <c r="AD57" s="349"/>
+      <c r="AE57" s="349"/>
+      <c r="AF57" s="349"/>
+      <c r="AG57" s="349"/>
+      <c r="AH57" s="349"/>
+      <c r="AI57" s="349"/>
+      <c r="AJ57" s="349"/>
+      <c r="AK57" s="349"/>
+      <c r="AL57" s="349"/>
+      <c r="AM57" s="349"/>
+      <c r="AN57" s="350"/>
     </row>
     <row r="58" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A58" s="341"/>
-      <c r="B58" s="342"/>
-      <c r="C58" s="342"/>
-      <c r="D58" s="342"/>
-      <c r="E58" s="342"/>
-      <c r="F58" s="342"/>
-      <c r="G58" s="342"/>
-      <c r="H58" s="342"/>
-      <c r="I58" s="342"/>
-      <c r="J58" s="342"/>
-      <c r="K58" s="342"/>
-      <c r="L58" s="343"/>
-      <c r="M58" s="350"/>
-      <c r="N58" s="351"/>
-      <c r="O58" s="351"/>
-      <c r="P58" s="351"/>
-      <c r="Q58" s="351"/>
-      <c r="R58" s="351"/>
-      <c r="S58" s="351"/>
-      <c r="T58" s="351"/>
-      <c r="U58" s="351"/>
-      <c r="V58" s="351"/>
-      <c r="W58" s="351"/>
-      <c r="X58" s="351"/>
-      <c r="Y58" s="351"/>
-      <c r="Z58" s="351"/>
-      <c r="AA58" s="351"/>
-      <c r="AB58" s="351"/>
-      <c r="AC58" s="351"/>
-      <c r="AD58" s="351"/>
-      <c r="AE58" s="351"/>
-      <c r="AF58" s="351"/>
-      <c r="AG58" s="351"/>
-      <c r="AH58" s="351"/>
-      <c r="AI58" s="351"/>
-      <c r="AJ58" s="351"/>
-      <c r="AK58" s="351"/>
-      <c r="AL58" s="351"/>
-      <c r="AM58" s="351"/>
-      <c r="AN58" s="352"/>
+      <c r="A58" s="339"/>
+      <c r="B58" s="340"/>
+      <c r="C58" s="340"/>
+      <c r="D58" s="340"/>
+      <c r="E58" s="340"/>
+      <c r="F58" s="340"/>
+      <c r="G58" s="340"/>
+      <c r="H58" s="340"/>
+      <c r="I58" s="340"/>
+      <c r="J58" s="340"/>
+      <c r="K58" s="340"/>
+      <c r="L58" s="341"/>
+      <c r="M58" s="348"/>
+      <c r="N58" s="349"/>
+      <c r="O58" s="349"/>
+      <c r="P58" s="349"/>
+      <c r="Q58" s="349"/>
+      <c r="R58" s="349"/>
+      <c r="S58" s="349"/>
+      <c r="T58" s="349"/>
+      <c r="U58" s="349"/>
+      <c r="V58" s="349"/>
+      <c r="W58" s="349"/>
+      <c r="X58" s="349"/>
+      <c r="Y58" s="349"/>
+      <c r="Z58" s="349"/>
+      <c r="AA58" s="349"/>
+      <c r="AB58" s="349"/>
+      <c r="AC58" s="349"/>
+      <c r="AD58" s="349"/>
+      <c r="AE58" s="349"/>
+      <c r="AF58" s="349"/>
+      <c r="AG58" s="349"/>
+      <c r="AH58" s="349"/>
+      <c r="AI58" s="349"/>
+      <c r="AJ58" s="349"/>
+      <c r="AK58" s="349"/>
+      <c r="AL58" s="349"/>
+      <c r="AM58" s="349"/>
+      <c r="AN58" s="350"/>
     </row>
     <row r="59" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A59" s="341"/>
-      <c r="B59" s="342"/>
-      <c r="C59" s="342"/>
-      <c r="D59" s="342"/>
-      <c r="E59" s="342"/>
-      <c r="F59" s="342"/>
-      <c r="G59" s="342"/>
-      <c r="H59" s="342"/>
-      <c r="I59" s="342"/>
-      <c r="J59" s="342"/>
-      <c r="K59" s="342"/>
-      <c r="L59" s="343"/>
-      <c r="M59" s="350"/>
-      <c r="N59" s="351"/>
-      <c r="O59" s="351"/>
-      <c r="P59" s="351"/>
-      <c r="Q59" s="351"/>
-      <c r="R59" s="351"/>
-      <c r="S59" s="351"/>
-      <c r="T59" s="351"/>
-      <c r="U59" s="351"/>
-      <c r="V59" s="351"/>
-      <c r="W59" s="351"/>
-      <c r="X59" s="351"/>
-      <c r="Y59" s="351"/>
-      <c r="Z59" s="351"/>
-      <c r="AA59" s="351"/>
-      <c r="AB59" s="351"/>
-      <c r="AC59" s="351"/>
-      <c r="AD59" s="351"/>
-      <c r="AE59" s="351"/>
-      <c r="AF59" s="351"/>
-      <c r="AG59" s="351"/>
-      <c r="AH59" s="351"/>
-      <c r="AI59" s="351"/>
-      <c r="AJ59" s="351"/>
-      <c r="AK59" s="351"/>
-      <c r="AL59" s="351"/>
-      <c r="AM59" s="351"/>
-      <c r="AN59" s="352"/>
+      <c r="A59" s="339"/>
+      <c r="B59" s="340"/>
+      <c r="C59" s="340"/>
+      <c r="D59" s="340"/>
+      <c r="E59" s="340"/>
+      <c r="F59" s="340"/>
+      <c r="G59" s="340"/>
+      <c r="H59" s="340"/>
+      <c r="I59" s="340"/>
+      <c r="J59" s="340"/>
+      <c r="K59" s="340"/>
+      <c r="L59" s="341"/>
+      <c r="M59" s="348"/>
+      <c r="N59" s="349"/>
+      <c r="O59" s="349"/>
+      <c r="P59" s="349"/>
+      <c r="Q59" s="349"/>
+      <c r="R59" s="349"/>
+      <c r="S59" s="349"/>
+      <c r="T59" s="349"/>
+      <c r="U59" s="349"/>
+      <c r="V59" s="349"/>
+      <c r="W59" s="349"/>
+      <c r="X59" s="349"/>
+      <c r="Y59" s="349"/>
+      <c r="Z59" s="349"/>
+      <c r="AA59" s="349"/>
+      <c r="AB59" s="349"/>
+      <c r="AC59" s="349"/>
+      <c r="AD59" s="349"/>
+      <c r="AE59" s="349"/>
+      <c r="AF59" s="349"/>
+      <c r="AG59" s="349"/>
+      <c r="AH59" s="349"/>
+      <c r="AI59" s="349"/>
+      <c r="AJ59" s="349"/>
+      <c r="AK59" s="349"/>
+      <c r="AL59" s="349"/>
+      <c r="AM59" s="349"/>
+      <c r="AN59" s="350"/>
     </row>
     <row r="60" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A60" s="341"/>
-      <c r="B60" s="342"/>
-      <c r="C60" s="342"/>
-      <c r="D60" s="342"/>
-      <c r="E60" s="342"/>
-      <c r="F60" s="342"/>
-      <c r="G60" s="342"/>
-      <c r="H60" s="342"/>
-      <c r="I60" s="342"/>
-      <c r="J60" s="342"/>
-      <c r="K60" s="342"/>
-      <c r="L60" s="343"/>
-      <c r="M60" s="350"/>
-      <c r="N60" s="351"/>
-      <c r="O60" s="351"/>
-      <c r="P60" s="351"/>
-      <c r="Q60" s="351"/>
-      <c r="R60" s="351"/>
-      <c r="S60" s="351"/>
-      <c r="T60" s="351"/>
-      <c r="U60" s="351"/>
-      <c r="V60" s="351"/>
-      <c r="W60" s="351"/>
-      <c r="X60" s="351"/>
-      <c r="Y60" s="351"/>
-      <c r="Z60" s="351"/>
-      <c r="AA60" s="351"/>
-      <c r="AB60" s="351"/>
-      <c r="AC60" s="351"/>
-      <c r="AD60" s="351"/>
-      <c r="AE60" s="351"/>
-      <c r="AF60" s="351"/>
-      <c r="AG60" s="351"/>
-      <c r="AH60" s="351"/>
-      <c r="AI60" s="351"/>
-      <c r="AJ60" s="351"/>
-      <c r="AK60" s="351"/>
-      <c r="AL60" s="351"/>
-      <c r="AM60" s="351"/>
-      <c r="AN60" s="352"/>
+      <c r="A60" s="339"/>
+      <c r="B60" s="340"/>
+      <c r="C60" s="340"/>
+      <c r="D60" s="340"/>
+      <c r="E60" s="340"/>
+      <c r="F60" s="340"/>
+      <c r="G60" s="340"/>
+      <c r="H60" s="340"/>
+      <c r="I60" s="340"/>
+      <c r="J60" s="340"/>
+      <c r="K60" s="340"/>
+      <c r="L60" s="341"/>
+      <c r="M60" s="348"/>
+      <c r="N60" s="349"/>
+      <c r="O60" s="349"/>
+      <c r="P60" s="349"/>
+      <c r="Q60" s="349"/>
+      <c r="R60" s="349"/>
+      <c r="S60" s="349"/>
+      <c r="T60" s="349"/>
+      <c r="U60" s="349"/>
+      <c r="V60" s="349"/>
+      <c r="W60" s="349"/>
+      <c r="X60" s="349"/>
+      <c r="Y60" s="349"/>
+      <c r="Z60" s="349"/>
+      <c r="AA60" s="349"/>
+      <c r="AB60" s="349"/>
+      <c r="AC60" s="349"/>
+      <c r="AD60" s="349"/>
+      <c r="AE60" s="349"/>
+      <c r="AF60" s="349"/>
+      <c r="AG60" s="349"/>
+      <c r="AH60" s="349"/>
+      <c r="AI60" s="349"/>
+      <c r="AJ60" s="349"/>
+      <c r="AK60" s="349"/>
+      <c r="AL60" s="349"/>
+      <c r="AM60" s="349"/>
+      <c r="AN60" s="350"/>
     </row>
     <row r="61" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A61" s="341"/>
-      <c r="B61" s="342"/>
-      <c r="C61" s="342"/>
-      <c r="D61" s="342"/>
-      <c r="E61" s="342"/>
-      <c r="F61" s="342"/>
-      <c r="G61" s="342"/>
-      <c r="H61" s="342"/>
-      <c r="I61" s="342"/>
-      <c r="J61" s="342"/>
-      <c r="K61" s="342"/>
-      <c r="L61" s="343"/>
-      <c r="M61" s="350"/>
-      <c r="N61" s="351"/>
-      <c r="O61" s="351"/>
-      <c r="P61" s="351"/>
-      <c r="Q61" s="351"/>
-      <c r="R61" s="351"/>
-      <c r="S61" s="351"/>
-      <c r="T61" s="351"/>
-      <c r="U61" s="351"/>
-      <c r="V61" s="351"/>
-      <c r="W61" s="351"/>
-      <c r="X61" s="351"/>
-      <c r="Y61" s="351"/>
-      <c r="Z61" s="351"/>
-      <c r="AA61" s="351"/>
-      <c r="AB61" s="351"/>
-      <c r="AC61" s="351"/>
-      <c r="AD61" s="351"/>
-      <c r="AE61" s="351"/>
-      <c r="AF61" s="351"/>
-      <c r="AG61" s="351"/>
-      <c r="AH61" s="351"/>
-      <c r="AI61" s="351"/>
-      <c r="AJ61" s="351"/>
-      <c r="AK61" s="351"/>
-      <c r="AL61" s="351"/>
-      <c r="AM61" s="351"/>
-      <c r="AN61" s="352"/>
+      <c r="A61" s="339"/>
+      <c r="B61" s="340"/>
+      <c r="C61" s="340"/>
+      <c r="D61" s="340"/>
+      <c r="E61" s="340"/>
+      <c r="F61" s="340"/>
+      <c r="G61" s="340"/>
+      <c r="H61" s="340"/>
+      <c r="I61" s="340"/>
+      <c r="J61" s="340"/>
+      <c r="K61" s="340"/>
+      <c r="L61" s="341"/>
+      <c r="M61" s="348"/>
+      <c r="N61" s="349"/>
+      <c r="O61" s="349"/>
+      <c r="P61" s="349"/>
+      <c r="Q61" s="349"/>
+      <c r="R61" s="349"/>
+      <c r="S61" s="349"/>
+      <c r="T61" s="349"/>
+      <c r="U61" s="349"/>
+      <c r="V61" s="349"/>
+      <c r="W61" s="349"/>
+      <c r="X61" s="349"/>
+      <c r="Y61" s="349"/>
+      <c r="Z61" s="349"/>
+      <c r="AA61" s="349"/>
+      <c r="AB61" s="349"/>
+      <c r="AC61" s="349"/>
+      <c r="AD61" s="349"/>
+      <c r="AE61" s="349"/>
+      <c r="AF61" s="349"/>
+      <c r="AG61" s="349"/>
+      <c r="AH61" s="349"/>
+      <c r="AI61" s="349"/>
+      <c r="AJ61" s="349"/>
+      <c r="AK61" s="349"/>
+      <c r="AL61" s="349"/>
+      <c r="AM61" s="349"/>
+      <c r="AN61" s="350"/>
     </row>
     <row r="62" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A62" s="341"/>
-      <c r="B62" s="342"/>
-      <c r="C62" s="342"/>
-      <c r="D62" s="342"/>
-      <c r="E62" s="342"/>
-      <c r="F62" s="342"/>
-      <c r="G62" s="342"/>
-      <c r="H62" s="342"/>
-      <c r="I62" s="342"/>
-      <c r="J62" s="342"/>
-      <c r="K62" s="342"/>
-      <c r="L62" s="343"/>
-      <c r="M62" s="350"/>
-      <c r="N62" s="351"/>
-      <c r="O62" s="351"/>
-      <c r="P62" s="351"/>
-      <c r="Q62" s="351"/>
-      <c r="R62" s="351"/>
-      <c r="S62" s="351"/>
-      <c r="T62" s="351"/>
-      <c r="U62" s="351"/>
-      <c r="V62" s="351"/>
-      <c r="W62" s="351"/>
-      <c r="X62" s="351"/>
-      <c r="Y62" s="351"/>
-      <c r="Z62" s="351"/>
-      <c r="AA62" s="351"/>
-      <c r="AB62" s="351"/>
-      <c r="AC62" s="351"/>
-      <c r="AD62" s="351"/>
-      <c r="AE62" s="351"/>
-      <c r="AF62" s="351"/>
-      <c r="AG62" s="351"/>
-      <c r="AH62" s="351"/>
-      <c r="AI62" s="351"/>
-      <c r="AJ62" s="351"/>
-      <c r="AK62" s="351"/>
-      <c r="AL62" s="351"/>
-      <c r="AM62" s="351"/>
-      <c r="AN62" s="352"/>
+      <c r="A62" s="339"/>
+      <c r="B62" s="340"/>
+      <c r="C62" s="340"/>
+      <c r="D62" s="340"/>
+      <c r="E62" s="340"/>
+      <c r="F62" s="340"/>
+      <c r="G62" s="340"/>
+      <c r="H62" s="340"/>
+      <c r="I62" s="340"/>
+      <c r="J62" s="340"/>
+      <c r="K62" s="340"/>
+      <c r="L62" s="341"/>
+      <c r="M62" s="348"/>
+      <c r="N62" s="349"/>
+      <c r="O62" s="349"/>
+      <c r="P62" s="349"/>
+      <c r="Q62" s="349"/>
+      <c r="R62" s="349"/>
+      <c r="S62" s="349"/>
+      <c r="T62" s="349"/>
+      <c r="U62" s="349"/>
+      <c r="V62" s="349"/>
+      <c r="W62" s="349"/>
+      <c r="X62" s="349"/>
+      <c r="Y62" s="349"/>
+      <c r="Z62" s="349"/>
+      <c r="AA62" s="349"/>
+      <c r="AB62" s="349"/>
+      <c r="AC62" s="349"/>
+      <c r="AD62" s="349"/>
+      <c r="AE62" s="349"/>
+      <c r="AF62" s="349"/>
+      <c r="AG62" s="349"/>
+      <c r="AH62" s="349"/>
+      <c r="AI62" s="349"/>
+      <c r="AJ62" s="349"/>
+      <c r="AK62" s="349"/>
+      <c r="AL62" s="349"/>
+      <c r="AM62" s="349"/>
+      <c r="AN62" s="350"/>
     </row>
     <row r="63" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A63" s="341"/>
-      <c r="B63" s="342"/>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-      <c r="G63" s="342"/>
-      <c r="H63" s="342"/>
-      <c r="I63" s="342"/>
-      <c r="J63" s="342"/>
-      <c r="K63" s="342"/>
-      <c r="L63" s="343"/>
-      <c r="M63" s="350"/>
-      <c r="N63" s="351"/>
-      <c r="O63" s="351"/>
-      <c r="P63" s="351"/>
-      <c r="Q63" s="351"/>
-      <c r="R63" s="351"/>
-      <c r="S63" s="351"/>
-      <c r="T63" s="351"/>
-      <c r="U63" s="351"/>
-      <c r="V63" s="351"/>
-      <c r="W63" s="351"/>
-      <c r="X63" s="351"/>
-      <c r="Y63" s="351"/>
-      <c r="Z63" s="351"/>
-      <c r="AA63" s="351"/>
-      <c r="AB63" s="351"/>
-      <c r="AC63" s="351"/>
-      <c r="AD63" s="351"/>
-      <c r="AE63" s="351"/>
-      <c r="AF63" s="351"/>
-      <c r="AG63" s="351"/>
-      <c r="AH63" s="351"/>
-      <c r="AI63" s="351"/>
-      <c r="AJ63" s="351"/>
-      <c r="AK63" s="351"/>
-      <c r="AL63" s="351"/>
-      <c r="AM63" s="351"/>
-      <c r="AN63" s="352"/>
+      <c r="A63" s="339"/>
+      <c r="B63" s="340"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+      <c r="G63" s="340"/>
+      <c r="H63" s="340"/>
+      <c r="I63" s="340"/>
+      <c r="J63" s="340"/>
+      <c r="K63" s="340"/>
+      <c r="L63" s="341"/>
+      <c r="M63" s="348"/>
+      <c r="N63" s="349"/>
+      <c r="O63" s="349"/>
+      <c r="P63" s="349"/>
+      <c r="Q63" s="349"/>
+      <c r="R63" s="349"/>
+      <c r="S63" s="349"/>
+      <c r="T63" s="349"/>
+      <c r="U63" s="349"/>
+      <c r="V63" s="349"/>
+      <c r="W63" s="349"/>
+      <c r="X63" s="349"/>
+      <c r="Y63" s="349"/>
+      <c r="Z63" s="349"/>
+      <c r="AA63" s="349"/>
+      <c r="AB63" s="349"/>
+      <c r="AC63" s="349"/>
+      <c r="AD63" s="349"/>
+      <c r="AE63" s="349"/>
+      <c r="AF63" s="349"/>
+      <c r="AG63" s="349"/>
+      <c r="AH63" s="349"/>
+      <c r="AI63" s="349"/>
+      <c r="AJ63" s="349"/>
+      <c r="AK63" s="349"/>
+      <c r="AL63" s="349"/>
+      <c r="AM63" s="349"/>
+      <c r="AN63" s="350"/>
     </row>
     <row r="64" spans="1:42" ht="25.5" customHeight="1">
-      <c r="A64" s="341"/>
-      <c r="B64" s="342"/>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
-      <c r="G64" s="342"/>
-      <c r="H64" s="342"/>
-      <c r="I64" s="342"/>
-      <c r="J64" s="342"/>
-      <c r="K64" s="342"/>
-      <c r="L64" s="343"/>
-      <c r="M64" s="350"/>
-      <c r="N64" s="351"/>
-      <c r="O64" s="351"/>
-      <c r="P64" s="351"/>
-      <c r="Q64" s="351"/>
-      <c r="R64" s="351"/>
-      <c r="S64" s="351"/>
-      <c r="T64" s="351"/>
-      <c r="U64" s="351"/>
-      <c r="V64" s="351"/>
-      <c r="W64" s="351"/>
-      <c r="X64" s="351"/>
-      <c r="Y64" s="351"/>
-      <c r="Z64" s="351"/>
-      <c r="AA64" s="351"/>
-      <c r="AB64" s="351"/>
-      <c r="AC64" s="351"/>
-      <c r="AD64" s="351"/>
-      <c r="AE64" s="351"/>
-      <c r="AF64" s="351"/>
-      <c r="AG64" s="351"/>
-      <c r="AH64" s="351"/>
-      <c r="AI64" s="351"/>
-      <c r="AJ64" s="351"/>
-      <c r="AK64" s="351"/>
-      <c r="AL64" s="351"/>
-      <c r="AM64" s="351"/>
-      <c r="AN64" s="352"/>
+      <c r="A64" s="339"/>
+      <c r="B64" s="340"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
+      <c r="G64" s="340"/>
+      <c r="H64" s="340"/>
+      <c r="I64" s="340"/>
+      <c r="J64" s="340"/>
+      <c r="K64" s="340"/>
+      <c r="L64" s="341"/>
+      <c r="M64" s="348"/>
+      <c r="N64" s="349"/>
+      <c r="O64" s="349"/>
+      <c r="P64" s="349"/>
+      <c r="Q64" s="349"/>
+      <c r="R64" s="349"/>
+      <c r="S64" s="349"/>
+      <c r="T64" s="349"/>
+      <c r="U64" s="349"/>
+      <c r="V64" s="349"/>
+      <c r="W64" s="349"/>
+      <c r="X64" s="349"/>
+      <c r="Y64" s="349"/>
+      <c r="Z64" s="349"/>
+      <c r="AA64" s="349"/>
+      <c r="AB64" s="349"/>
+      <c r="AC64" s="349"/>
+      <c r="AD64" s="349"/>
+      <c r="AE64" s="349"/>
+      <c r="AF64" s="349"/>
+      <c r="AG64" s="349"/>
+      <c r="AH64" s="349"/>
+      <c r="AI64" s="349"/>
+      <c r="AJ64" s="349"/>
+      <c r="AK64" s="349"/>
+      <c r="AL64" s="349"/>
+      <c r="AM64" s="349"/>
+      <c r="AN64" s="350"/>
     </row>
     <row r="65" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A65" s="341"/>
-      <c r="B65" s="342"/>
-      <c r="C65" s="342"/>
-      <c r="D65" s="342"/>
-      <c r="E65" s="342"/>
-      <c r="F65" s="342"/>
-      <c r="G65" s="342"/>
-      <c r="H65" s="342"/>
-      <c r="I65" s="342"/>
-      <c r="J65" s="342"/>
-      <c r="K65" s="342"/>
-      <c r="L65" s="343"/>
-      <c r="M65" s="350"/>
-      <c r="N65" s="351"/>
-      <c r="O65" s="351"/>
-      <c r="P65" s="351"/>
-      <c r="Q65" s="351"/>
-      <c r="R65" s="351"/>
-      <c r="S65" s="351"/>
-      <c r="T65" s="351"/>
-      <c r="U65" s="351"/>
-      <c r="V65" s="351"/>
-      <c r="W65" s="351"/>
-      <c r="X65" s="351"/>
-      <c r="Y65" s="351"/>
-      <c r="Z65" s="351"/>
-      <c r="AA65" s="351"/>
-      <c r="AB65" s="351"/>
-      <c r="AC65" s="351"/>
-      <c r="AD65" s="351"/>
-      <c r="AE65" s="351"/>
-      <c r="AF65" s="351"/>
-      <c r="AG65" s="351"/>
-      <c r="AH65" s="351"/>
-      <c r="AI65" s="351"/>
-      <c r="AJ65" s="351"/>
-      <c r="AK65" s="351"/>
-      <c r="AL65" s="351"/>
-      <c r="AM65" s="351"/>
-      <c r="AN65" s="352"/>
+      <c r="A65" s="339"/>
+      <c r="B65" s="340"/>
+      <c r="C65" s="340"/>
+      <c r="D65" s="340"/>
+      <c r="E65" s="340"/>
+      <c r="F65" s="340"/>
+      <c r="G65" s="340"/>
+      <c r="H65" s="340"/>
+      <c r="I65" s="340"/>
+      <c r="J65" s="340"/>
+      <c r="K65" s="340"/>
+      <c r="L65" s="341"/>
+      <c r="M65" s="348"/>
+      <c r="N65" s="349"/>
+      <c r="O65" s="349"/>
+      <c r="P65" s="349"/>
+      <c r="Q65" s="349"/>
+      <c r="R65" s="349"/>
+      <c r="S65" s="349"/>
+      <c r="T65" s="349"/>
+      <c r="U65" s="349"/>
+      <c r="V65" s="349"/>
+      <c r="W65" s="349"/>
+      <c r="X65" s="349"/>
+      <c r="Y65" s="349"/>
+      <c r="Z65" s="349"/>
+      <c r="AA65" s="349"/>
+      <c r="AB65" s="349"/>
+      <c r="AC65" s="349"/>
+      <c r="AD65" s="349"/>
+      <c r="AE65" s="349"/>
+      <c r="AF65" s="349"/>
+      <c r="AG65" s="349"/>
+      <c r="AH65" s="349"/>
+      <c r="AI65" s="349"/>
+      <c r="AJ65" s="349"/>
+      <c r="AK65" s="349"/>
+      <c r="AL65" s="349"/>
+      <c r="AM65" s="349"/>
+      <c r="AN65" s="350"/>
     </row>
     <row r="66" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A66" s="341"/>
-      <c r="B66" s="342"/>
-      <c r="C66" s="342"/>
-      <c r="D66" s="342"/>
-      <c r="E66" s="342"/>
-      <c r="F66" s="342"/>
-      <c r="G66" s="342"/>
-      <c r="H66" s="342"/>
-      <c r="I66" s="342"/>
-      <c r="J66" s="342"/>
-      <c r="K66" s="342"/>
-      <c r="L66" s="343"/>
-      <c r="M66" s="350"/>
-      <c r="N66" s="351"/>
-      <c r="O66" s="351"/>
-      <c r="P66" s="351"/>
-      <c r="Q66" s="351"/>
-      <c r="R66" s="351"/>
-      <c r="S66" s="351"/>
-      <c r="T66" s="351"/>
-      <c r="U66" s="351"/>
-      <c r="V66" s="351"/>
-      <c r="W66" s="351"/>
-      <c r="X66" s="351"/>
-      <c r="Y66" s="351"/>
-      <c r="Z66" s="351"/>
-      <c r="AA66" s="351"/>
-      <c r="AB66" s="351"/>
-      <c r="AC66" s="351"/>
-      <c r="AD66" s="351"/>
-      <c r="AE66" s="351"/>
-      <c r="AF66" s="351"/>
-      <c r="AG66" s="351"/>
-      <c r="AH66" s="351"/>
-      <c r="AI66" s="351"/>
-      <c r="AJ66" s="351"/>
-      <c r="AK66" s="351"/>
-      <c r="AL66" s="351"/>
-      <c r="AM66" s="351"/>
-      <c r="AN66" s="352"/>
+      <c r="A66" s="339"/>
+      <c r="B66" s="340"/>
+      <c r="C66" s="340"/>
+      <c r="D66" s="340"/>
+      <c r="E66" s="340"/>
+      <c r="F66" s="340"/>
+      <c r="G66" s="340"/>
+      <c r="H66" s="340"/>
+      <c r="I66" s="340"/>
+      <c r="J66" s="340"/>
+      <c r="K66" s="340"/>
+      <c r="L66" s="341"/>
+      <c r="M66" s="348"/>
+      <c r="N66" s="349"/>
+      <c r="O66" s="349"/>
+      <c r="P66" s="349"/>
+      <c r="Q66" s="349"/>
+      <c r="R66" s="349"/>
+      <c r="S66" s="349"/>
+      <c r="T66" s="349"/>
+      <c r="U66" s="349"/>
+      <c r="V66" s="349"/>
+      <c r="W66" s="349"/>
+      <c r="X66" s="349"/>
+      <c r="Y66" s="349"/>
+      <c r="Z66" s="349"/>
+      <c r="AA66" s="349"/>
+      <c r="AB66" s="349"/>
+      <c r="AC66" s="349"/>
+      <c r="AD66" s="349"/>
+      <c r="AE66" s="349"/>
+      <c r="AF66" s="349"/>
+      <c r="AG66" s="349"/>
+      <c r="AH66" s="349"/>
+      <c r="AI66" s="349"/>
+      <c r="AJ66" s="349"/>
+      <c r="AK66" s="349"/>
+      <c r="AL66" s="349"/>
+      <c r="AM66" s="349"/>
+      <c r="AN66" s="350"/>
     </row>
     <row r="67" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A67" s="341"/>
-      <c r="B67" s="342"/>
-      <c r="C67" s="342"/>
-      <c r="D67" s="342"/>
-      <c r="E67" s="342"/>
-      <c r="F67" s="342"/>
-      <c r="G67" s="342"/>
-      <c r="H67" s="342"/>
-      <c r="I67" s="342"/>
-      <c r="J67" s="342"/>
-      <c r="K67" s="342"/>
-      <c r="L67" s="343"/>
-      <c r="M67" s="350"/>
-      <c r="N67" s="351"/>
-      <c r="O67" s="351"/>
-      <c r="P67" s="351"/>
-      <c r="Q67" s="351"/>
-      <c r="R67" s="351"/>
-      <c r="S67" s="351"/>
-      <c r="T67" s="351"/>
-      <c r="U67" s="351"/>
-      <c r="V67" s="351"/>
-      <c r="W67" s="351"/>
-      <c r="X67" s="351"/>
-      <c r="Y67" s="351"/>
-      <c r="Z67" s="351"/>
-      <c r="AA67" s="351"/>
-      <c r="AB67" s="351"/>
-      <c r="AC67" s="351"/>
-      <c r="AD67" s="351"/>
-      <c r="AE67" s="351"/>
-      <c r="AF67" s="351"/>
-      <c r="AG67" s="351"/>
-      <c r="AH67" s="351"/>
-      <c r="AI67" s="351"/>
-      <c r="AJ67" s="351"/>
-      <c r="AK67" s="351"/>
-      <c r="AL67" s="351"/>
-      <c r="AM67" s="351"/>
-      <c r="AN67" s="352"/>
+      <c r="A67" s="339"/>
+      <c r="B67" s="340"/>
+      <c r="C67" s="340"/>
+      <c r="D67" s="340"/>
+      <c r="E67" s="340"/>
+      <c r="F67" s="340"/>
+      <c r="G67" s="340"/>
+      <c r="H67" s="340"/>
+      <c r="I67" s="340"/>
+      <c r="J67" s="340"/>
+      <c r="K67" s="340"/>
+      <c r="L67" s="341"/>
+      <c r="M67" s="348"/>
+      <c r="N67" s="349"/>
+      <c r="O67" s="349"/>
+      <c r="P67" s="349"/>
+      <c r="Q67" s="349"/>
+      <c r="R67" s="349"/>
+      <c r="S67" s="349"/>
+      <c r="T67" s="349"/>
+      <c r="U67" s="349"/>
+      <c r="V67" s="349"/>
+      <c r="W67" s="349"/>
+      <c r="X67" s="349"/>
+      <c r="Y67" s="349"/>
+      <c r="Z67" s="349"/>
+      <c r="AA67" s="349"/>
+      <c r="AB67" s="349"/>
+      <c r="AC67" s="349"/>
+      <c r="AD67" s="349"/>
+      <c r="AE67" s="349"/>
+      <c r="AF67" s="349"/>
+      <c r="AG67" s="349"/>
+      <c r="AH67" s="349"/>
+      <c r="AI67" s="349"/>
+      <c r="AJ67" s="349"/>
+      <c r="AK67" s="349"/>
+      <c r="AL67" s="349"/>
+      <c r="AM67" s="349"/>
+      <c r="AN67" s="350"/>
     </row>
     <row r="68" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A68" s="341"/>
-      <c r="B68" s="342"/>
-      <c r="C68" s="342"/>
-      <c r="D68" s="342"/>
-      <c r="E68" s="342"/>
-      <c r="F68" s="342"/>
-      <c r="G68" s="342"/>
-      <c r="H68" s="342"/>
-      <c r="I68" s="342"/>
-      <c r="J68" s="342"/>
-      <c r="K68" s="342"/>
-      <c r="L68" s="343"/>
-      <c r="M68" s="350"/>
-      <c r="N68" s="351"/>
-      <c r="O68" s="351"/>
-      <c r="P68" s="351"/>
-      <c r="Q68" s="351"/>
-      <c r="R68" s="351"/>
-      <c r="S68" s="351"/>
-      <c r="T68" s="351"/>
-      <c r="U68" s="351"/>
-      <c r="V68" s="351"/>
-      <c r="W68" s="351"/>
-      <c r="X68" s="351"/>
-      <c r="Y68" s="351"/>
-      <c r="Z68" s="351"/>
-      <c r="AA68" s="351"/>
-      <c r="AB68" s="351"/>
-      <c r="AC68" s="351"/>
-      <c r="AD68" s="351"/>
-      <c r="AE68" s="351"/>
-      <c r="AF68" s="351"/>
-      <c r="AG68" s="351"/>
-      <c r="AH68" s="351"/>
-      <c r="AI68" s="351"/>
-      <c r="AJ68" s="351"/>
-      <c r="AK68" s="351"/>
-      <c r="AL68" s="351"/>
-      <c r="AM68" s="351"/>
-      <c r="AN68" s="352"/>
+      <c r="A68" s="339"/>
+      <c r="B68" s="340"/>
+      <c r="C68" s="340"/>
+      <c r="D68" s="340"/>
+      <c r="E68" s="340"/>
+      <c r="F68" s="340"/>
+      <c r="G68" s="340"/>
+      <c r="H68" s="340"/>
+      <c r="I68" s="340"/>
+      <c r="J68" s="340"/>
+      <c r="K68" s="340"/>
+      <c r="L68" s="341"/>
+      <c r="M68" s="348"/>
+      <c r="N68" s="349"/>
+      <c r="O68" s="349"/>
+      <c r="P68" s="349"/>
+      <c r="Q68" s="349"/>
+      <c r="R68" s="349"/>
+      <c r="S68" s="349"/>
+      <c r="T68" s="349"/>
+      <c r="U68" s="349"/>
+      <c r="V68" s="349"/>
+      <c r="W68" s="349"/>
+      <c r="X68" s="349"/>
+      <c r="Y68" s="349"/>
+      <c r="Z68" s="349"/>
+      <c r="AA68" s="349"/>
+      <c r="AB68" s="349"/>
+      <c r="AC68" s="349"/>
+      <c r="AD68" s="349"/>
+      <c r="AE68" s="349"/>
+      <c r="AF68" s="349"/>
+      <c r="AG68" s="349"/>
+      <c r="AH68" s="349"/>
+      <c r="AI68" s="349"/>
+      <c r="AJ68" s="349"/>
+      <c r="AK68" s="349"/>
+      <c r="AL68" s="349"/>
+      <c r="AM68" s="349"/>
+      <c r="AN68" s="350"/>
     </row>
     <row r="69" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A69" s="341"/>
-      <c r="B69" s="342"/>
-      <c r="C69" s="342"/>
-      <c r="D69" s="342"/>
-      <c r="E69" s="342"/>
-      <c r="F69" s="342"/>
-      <c r="G69" s="342"/>
-      <c r="H69" s="342"/>
-      <c r="I69" s="342"/>
-      <c r="J69" s="342"/>
-      <c r="K69" s="342"/>
-      <c r="L69" s="343"/>
-      <c r="M69" s="350"/>
-      <c r="N69" s="351"/>
-      <c r="O69" s="351"/>
-      <c r="P69" s="351"/>
-      <c r="Q69" s="351"/>
-      <c r="R69" s="351"/>
-      <c r="S69" s="351"/>
-      <c r="T69" s="351"/>
-      <c r="U69" s="351"/>
-      <c r="V69" s="351"/>
-      <c r="W69" s="351"/>
-      <c r="X69" s="351"/>
-      <c r="Y69" s="351"/>
-      <c r="Z69" s="351"/>
-      <c r="AA69" s="351"/>
-      <c r="AB69" s="351"/>
-      <c r="AC69" s="351"/>
-      <c r="AD69" s="351"/>
-      <c r="AE69" s="351"/>
-      <c r="AF69" s="351"/>
-      <c r="AG69" s="351"/>
-      <c r="AH69" s="351"/>
-      <c r="AI69" s="351"/>
-      <c r="AJ69" s="351"/>
-      <c r="AK69" s="351"/>
-      <c r="AL69" s="351"/>
-      <c r="AM69" s="351"/>
-      <c r="AN69" s="352"/>
+      <c r="A69" s="339"/>
+      <c r="B69" s="340"/>
+      <c r="C69" s="340"/>
+      <c r="D69" s="340"/>
+      <c r="E69" s="340"/>
+      <c r="F69" s="340"/>
+      <c r="G69" s="340"/>
+      <c r="H69" s="340"/>
+      <c r="I69" s="340"/>
+      <c r="J69" s="340"/>
+      <c r="K69" s="340"/>
+      <c r="L69" s="341"/>
+      <c r="M69" s="348"/>
+      <c r="N69" s="349"/>
+      <c r="O69" s="349"/>
+      <c r="P69" s="349"/>
+      <c r="Q69" s="349"/>
+      <c r="R69" s="349"/>
+      <c r="S69" s="349"/>
+      <c r="T69" s="349"/>
+      <c r="U69" s="349"/>
+      <c r="V69" s="349"/>
+      <c r="W69" s="349"/>
+      <c r="X69" s="349"/>
+      <c r="Y69" s="349"/>
+      <c r="Z69" s="349"/>
+      <c r="AA69" s="349"/>
+      <c r="AB69" s="349"/>
+      <c r="AC69" s="349"/>
+      <c r="AD69" s="349"/>
+      <c r="AE69" s="349"/>
+      <c r="AF69" s="349"/>
+      <c r="AG69" s="349"/>
+      <c r="AH69" s="349"/>
+      <c r="AI69" s="349"/>
+      <c r="AJ69" s="349"/>
+      <c r="AK69" s="349"/>
+      <c r="AL69" s="349"/>
+      <c r="AM69" s="349"/>
+      <c r="AN69" s="350"/>
     </row>
     <row r="70" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A70" s="341"/>
-      <c r="B70" s="342"/>
-      <c r="C70" s="342"/>
-      <c r="D70" s="342"/>
-      <c r="E70" s="342"/>
-      <c r="F70" s="342"/>
-      <c r="G70" s="342"/>
-      <c r="H70" s="342"/>
-      <c r="I70" s="342"/>
-      <c r="J70" s="342"/>
-      <c r="K70" s="342"/>
-      <c r="L70" s="343"/>
-      <c r="M70" s="350"/>
-      <c r="N70" s="351"/>
-      <c r="O70" s="351"/>
-      <c r="P70" s="351"/>
-      <c r="Q70" s="351"/>
-      <c r="R70" s="351"/>
-      <c r="S70" s="351"/>
-      <c r="T70" s="351"/>
-      <c r="U70" s="351"/>
-      <c r="V70" s="351"/>
-      <c r="W70" s="351"/>
-      <c r="X70" s="351"/>
-      <c r="Y70" s="351"/>
-      <c r="Z70" s="351"/>
-      <c r="AA70" s="351"/>
-      <c r="AB70" s="351"/>
-      <c r="AC70" s="351"/>
-      <c r="AD70" s="351"/>
-      <c r="AE70" s="351"/>
-      <c r="AF70" s="351"/>
-      <c r="AG70" s="351"/>
-      <c r="AH70" s="351"/>
-      <c r="AI70" s="351"/>
-      <c r="AJ70" s="351"/>
-      <c r="AK70" s="351"/>
-      <c r="AL70" s="351"/>
-      <c r="AM70" s="351"/>
-      <c r="AN70" s="352"/>
+      <c r="A70" s="339"/>
+      <c r="B70" s="340"/>
+      <c r="C70" s="340"/>
+      <c r="D70" s="340"/>
+      <c r="E70" s="340"/>
+      <c r="F70" s="340"/>
+      <c r="G70" s="340"/>
+      <c r="H70" s="340"/>
+      <c r="I70" s="340"/>
+      <c r="J70" s="340"/>
+      <c r="K70" s="340"/>
+      <c r="L70" s="341"/>
+      <c r="M70" s="348"/>
+      <c r="N70" s="349"/>
+      <c r="O70" s="349"/>
+      <c r="P70" s="349"/>
+      <c r="Q70" s="349"/>
+      <c r="R70" s="349"/>
+      <c r="S70" s="349"/>
+      <c r="T70" s="349"/>
+      <c r="U70" s="349"/>
+      <c r="V70" s="349"/>
+      <c r="W70" s="349"/>
+      <c r="X70" s="349"/>
+      <c r="Y70" s="349"/>
+      <c r="Z70" s="349"/>
+      <c r="AA70" s="349"/>
+      <c r="AB70" s="349"/>
+      <c r="AC70" s="349"/>
+      <c r="AD70" s="349"/>
+      <c r="AE70" s="349"/>
+      <c r="AF70" s="349"/>
+      <c r="AG70" s="349"/>
+      <c r="AH70" s="349"/>
+      <c r="AI70" s="349"/>
+      <c r="AJ70" s="349"/>
+      <c r="AK70" s="349"/>
+      <c r="AL70" s="349"/>
+      <c r="AM70" s="349"/>
+      <c r="AN70" s="350"/>
     </row>
     <row r="71" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A71" s="341"/>
-      <c r="B71" s="342"/>
-      <c r="C71" s="342"/>
-      <c r="D71" s="342"/>
-      <c r="E71" s="342"/>
-      <c r="F71" s="342"/>
-      <c r="G71" s="342"/>
-      <c r="H71" s="342"/>
-      <c r="I71" s="342"/>
-      <c r="J71" s="342"/>
-      <c r="K71" s="342"/>
-      <c r="L71" s="343"/>
-      <c r="M71" s="350"/>
-      <c r="N71" s="351"/>
-      <c r="O71" s="351"/>
-      <c r="P71" s="351"/>
-      <c r="Q71" s="351"/>
-      <c r="R71" s="351"/>
-      <c r="S71" s="351"/>
-      <c r="T71" s="351"/>
-      <c r="U71" s="351"/>
-      <c r="V71" s="351"/>
-      <c r="W71" s="351"/>
-      <c r="X71" s="351"/>
-      <c r="Y71" s="351"/>
-      <c r="Z71" s="351"/>
-      <c r="AA71" s="351"/>
-      <c r="AB71" s="351"/>
-      <c r="AC71" s="351"/>
-      <c r="AD71" s="351"/>
-      <c r="AE71" s="351"/>
-      <c r="AF71" s="351"/>
-      <c r="AG71" s="351"/>
-      <c r="AH71" s="351"/>
-      <c r="AI71" s="351"/>
-      <c r="AJ71" s="351"/>
-      <c r="AK71" s="351"/>
-      <c r="AL71" s="351"/>
-      <c r="AM71" s="351"/>
-      <c r="AN71" s="352"/>
+      <c r="A71" s="339"/>
+      <c r="B71" s="340"/>
+      <c r="C71" s="340"/>
+      <c r="D71" s="340"/>
+      <c r="E71" s="340"/>
+      <c r="F71" s="340"/>
+      <c r="G71" s="340"/>
+      <c r="H71" s="340"/>
+      <c r="I71" s="340"/>
+      <c r="J71" s="340"/>
+      <c r="K71" s="340"/>
+      <c r="L71" s="341"/>
+      <c r="M71" s="348"/>
+      <c r="N71" s="349"/>
+      <c r="O71" s="349"/>
+      <c r="P71" s="349"/>
+      <c r="Q71" s="349"/>
+      <c r="R71" s="349"/>
+      <c r="S71" s="349"/>
+      <c r="T71" s="349"/>
+      <c r="U71" s="349"/>
+      <c r="V71" s="349"/>
+      <c r="W71" s="349"/>
+      <c r="X71" s="349"/>
+      <c r="Y71" s="349"/>
+      <c r="Z71" s="349"/>
+      <c r="AA71" s="349"/>
+      <c r="AB71" s="349"/>
+      <c r="AC71" s="349"/>
+      <c r="AD71" s="349"/>
+      <c r="AE71" s="349"/>
+      <c r="AF71" s="349"/>
+      <c r="AG71" s="349"/>
+      <c r="AH71" s="349"/>
+      <c r="AI71" s="349"/>
+      <c r="AJ71" s="349"/>
+      <c r="AK71" s="349"/>
+      <c r="AL71" s="349"/>
+      <c r="AM71" s="349"/>
+      <c r="AN71" s="350"/>
     </row>
     <row r="72" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A72" s="341"/>
-      <c r="B72" s="342"/>
-      <c r="C72" s="342"/>
-      <c r="D72" s="342"/>
-      <c r="E72" s="342"/>
-      <c r="F72" s="342"/>
-      <c r="G72" s="342"/>
-      <c r="H72" s="342"/>
-      <c r="I72" s="342"/>
-      <c r="J72" s="342"/>
-      <c r="K72" s="342"/>
-      <c r="L72" s="343"/>
-      <c r="M72" s="350"/>
-      <c r="N72" s="351"/>
-      <c r="O72" s="351"/>
-      <c r="P72" s="351"/>
-      <c r="Q72" s="351"/>
-      <c r="R72" s="351"/>
-      <c r="S72" s="351"/>
-      <c r="T72" s="351"/>
-      <c r="U72" s="351"/>
-      <c r="V72" s="351"/>
-      <c r="W72" s="351"/>
-      <c r="X72" s="351"/>
-      <c r="Y72" s="351"/>
-      <c r="Z72" s="351"/>
-      <c r="AA72" s="351"/>
-      <c r="AB72" s="351"/>
-      <c r="AC72" s="351"/>
-      <c r="AD72" s="351"/>
-      <c r="AE72" s="351"/>
-      <c r="AF72" s="351"/>
-      <c r="AG72" s="351"/>
-      <c r="AH72" s="351"/>
-      <c r="AI72" s="351"/>
-      <c r="AJ72" s="351"/>
-      <c r="AK72" s="351"/>
-      <c r="AL72" s="351"/>
-      <c r="AM72" s="351"/>
-      <c r="AN72" s="352"/>
+      <c r="A72" s="339"/>
+      <c r="B72" s="340"/>
+      <c r="C72" s="340"/>
+      <c r="D72" s="340"/>
+      <c r="E72" s="340"/>
+      <c r="F72" s="340"/>
+      <c r="G72" s="340"/>
+      <c r="H72" s="340"/>
+      <c r="I72" s="340"/>
+      <c r="J72" s="340"/>
+      <c r="K72" s="340"/>
+      <c r="L72" s="341"/>
+      <c r="M72" s="348"/>
+      <c r="N72" s="349"/>
+      <c r="O72" s="349"/>
+      <c r="P72" s="349"/>
+      <c r="Q72" s="349"/>
+      <c r="R72" s="349"/>
+      <c r="S72" s="349"/>
+      <c r="T72" s="349"/>
+      <c r="U72" s="349"/>
+      <c r="V72" s="349"/>
+      <c r="W72" s="349"/>
+      <c r="X72" s="349"/>
+      <c r="Y72" s="349"/>
+      <c r="Z72" s="349"/>
+      <c r="AA72" s="349"/>
+      <c r="AB72" s="349"/>
+      <c r="AC72" s="349"/>
+      <c r="AD72" s="349"/>
+      <c r="AE72" s="349"/>
+      <c r="AF72" s="349"/>
+      <c r="AG72" s="349"/>
+      <c r="AH72" s="349"/>
+      <c r="AI72" s="349"/>
+      <c r="AJ72" s="349"/>
+      <c r="AK72" s="349"/>
+      <c r="AL72" s="349"/>
+      <c r="AM72" s="349"/>
+      <c r="AN72" s="350"/>
     </row>
     <row r="73" spans="1:40" ht="25.5" customHeight="1">
-      <c r="A73" s="341"/>
-      <c r="B73" s="342"/>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-      <c r="G73" s="342"/>
-      <c r="H73" s="342"/>
-      <c r="I73" s="342"/>
-      <c r="J73" s="342"/>
-      <c r="K73" s="342"/>
-      <c r="L73" s="343"/>
-      <c r="M73" s="350"/>
-      <c r="N73" s="351"/>
-      <c r="O73" s="351"/>
-      <c r="P73" s="351"/>
-      <c r="Q73" s="351"/>
-      <c r="R73" s="351"/>
-      <c r="S73" s="351"/>
-      <c r="T73" s="351"/>
-      <c r="U73" s="351"/>
-      <c r="V73" s="351"/>
-      <c r="W73" s="351"/>
-      <c r="X73" s="351"/>
-      <c r="Y73" s="351"/>
-      <c r="Z73" s="351"/>
-      <c r="AA73" s="351"/>
-      <c r="AB73" s="351"/>
-      <c r="AC73" s="351"/>
-      <c r="AD73" s="351"/>
-      <c r="AE73" s="351"/>
-      <c r="AF73" s="351"/>
-      <c r="AG73" s="351"/>
-      <c r="AH73" s="351"/>
-      <c r="AI73" s="351"/>
-      <c r="AJ73" s="351"/>
-      <c r="AK73" s="351"/>
-      <c r="AL73" s="351"/>
-      <c r="AM73" s="351"/>
-      <c r="AN73" s="352"/>
+      <c r="A73" s="339"/>
+      <c r="B73" s="340"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+      <c r="G73" s="340"/>
+      <c r="H73" s="340"/>
+      <c r="I73" s="340"/>
+      <c r="J73" s="340"/>
+      <c r="K73" s="340"/>
+      <c r="L73" s="341"/>
+      <c r="M73" s="348"/>
+      <c r="N73" s="349"/>
+      <c r="O73" s="349"/>
+      <c r="P73" s="349"/>
+      <c r="Q73" s="349"/>
+      <c r="R73" s="349"/>
+      <c r="S73" s="349"/>
+      <c r="T73" s="349"/>
+      <c r="U73" s="349"/>
+      <c r="V73" s="349"/>
+      <c r="W73" s="349"/>
+      <c r="X73" s="349"/>
+      <c r="Y73" s="349"/>
+      <c r="Z73" s="349"/>
+      <c r="AA73" s="349"/>
+      <c r="AB73" s="349"/>
+      <c r="AC73" s="349"/>
+      <c r="AD73" s="349"/>
+      <c r="AE73" s="349"/>
+      <c r="AF73" s="349"/>
+      <c r="AG73" s="349"/>
+      <c r="AH73" s="349"/>
+      <c r="AI73" s="349"/>
+      <c r="AJ73" s="349"/>
+      <c r="AK73" s="349"/>
+      <c r="AL73" s="349"/>
+      <c r="AM73" s="349"/>
+      <c r="AN73" s="350"/>
     </row>
     <row r="74" spans="1:40" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A74" s="344"/>
-      <c r="B74" s="345"/>
-      <c r="C74" s="345"/>
-      <c r="D74" s="345"/>
-      <c r="E74" s="345"/>
-      <c r="F74" s="345"/>
-      <c r="G74" s="345"/>
-      <c r="H74" s="345"/>
-      <c r="I74" s="345"/>
-      <c r="J74" s="345"/>
-      <c r="K74" s="345"/>
-      <c r="L74" s="346"/>
-      <c r="M74" s="353"/>
-      <c r="N74" s="354"/>
-      <c r="O74" s="354"/>
-      <c r="P74" s="354"/>
-      <c r="Q74" s="354"/>
-      <c r="R74" s="354"/>
-      <c r="S74" s="354"/>
-      <c r="T74" s="354"/>
-      <c r="U74" s="354"/>
-      <c r="V74" s="354"/>
-      <c r="W74" s="354"/>
-      <c r="X74" s="354"/>
-      <c r="Y74" s="354"/>
-      <c r="Z74" s="354"/>
-      <c r="AA74" s="354"/>
-      <c r="AB74" s="354"/>
-      <c r="AC74" s="354"/>
-      <c r="AD74" s="354"/>
-      <c r="AE74" s="354"/>
-      <c r="AF74" s="354"/>
-      <c r="AG74" s="354"/>
-      <c r="AH74" s="354"/>
-      <c r="AI74" s="354"/>
-      <c r="AJ74" s="354"/>
-      <c r="AK74" s="354"/>
-      <c r="AL74" s="354"/>
-      <c r="AM74" s="354"/>
-      <c r="AN74" s="355"/>
+      <c r="A74" s="342"/>
+      <c r="B74" s="343"/>
+      <c r="C74" s="343"/>
+      <c r="D74" s="343"/>
+      <c r="E74" s="343"/>
+      <c r="F74" s="343"/>
+      <c r="G74" s="343"/>
+      <c r="H74" s="343"/>
+      <c r="I74" s="343"/>
+      <c r="J74" s="343"/>
+      <c r="K74" s="343"/>
+      <c r="L74" s="344"/>
+      <c r="M74" s="351"/>
+      <c r="N74" s="352"/>
+      <c r="O74" s="352"/>
+      <c r="P74" s="352"/>
+      <c r="Q74" s="352"/>
+      <c r="R74" s="352"/>
+      <c r="S74" s="352"/>
+      <c r="T74" s="352"/>
+      <c r="U74" s="352"/>
+      <c r="V74" s="352"/>
+      <c r="W74" s="352"/>
+      <c r="X74" s="352"/>
+      <c r="Y74" s="352"/>
+      <c r="Z74" s="352"/>
+      <c r="AA74" s="352"/>
+      <c r="AB74" s="352"/>
+      <c r="AC74" s="352"/>
+      <c r="AD74" s="352"/>
+      <c r="AE74" s="352"/>
+      <c r="AF74" s="352"/>
+      <c r="AG74" s="352"/>
+      <c r="AH74" s="352"/>
+      <c r="AI74" s="352"/>
+      <c r="AJ74" s="352"/>
+      <c r="AK74" s="352"/>
+      <c r="AL74" s="352"/>
+      <c r="AM74" s="352"/>
+      <c r="AN74" s="353"/>
     </row>
     <row r="75" spans="1:40" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A75" s="333" t="s">
+      <c r="A75" s="331" t="s">
         <v>102</v>
       </c>
-      <c r="B75" s="334"/>
-      <c r="C75" s="334"/>
-      <c r="D75" s="334"/>
-      <c r="E75" s="334"/>
-      <c r="F75" s="334"/>
-      <c r="G75" s="334"/>
-      <c r="H75" s="334"/>
-      <c r="I75" s="334"/>
-      <c r="J75" s="334"/>
-      <c r="K75" s="334"/>
-      <c r="L75" s="335"/>
-      <c r="M75" s="336" t="s">
+      <c r="B75" s="332"/>
+      <c r="C75" s="332"/>
+      <c r="D75" s="332"/>
+      <c r="E75" s="332"/>
+      <c r="F75" s="332"/>
+      <c r="G75" s="332"/>
+      <c r="H75" s="332"/>
+      <c r="I75" s="332"/>
+      <c r="J75" s="332"/>
+      <c r="K75" s="332"/>
+      <c r="L75" s="333"/>
+      <c r="M75" s="334" t="s">
         <v>103</v>
       </c>
-      <c r="N75" s="336"/>
-      <c r="O75" s="336"/>
-      <c r="P75" s="336"/>
-      <c r="Q75" s="336"/>
-      <c r="R75" s="336"/>
-      <c r="S75" s="336"/>
-      <c r="T75" s="336"/>
-      <c r="U75" s="336"/>
-      <c r="V75" s="336"/>
-      <c r="W75" s="336"/>
-      <c r="X75" s="336"/>
-      <c r="Y75" s="336"/>
-      <c r="Z75" s="336"/>
-      <c r="AA75" s="336"/>
-      <c r="AB75" s="336"/>
-      <c r="AC75" s="336"/>
-      <c r="AD75" s="336"/>
-      <c r="AE75" s="336"/>
-      <c r="AF75" s="336"/>
-      <c r="AG75" s="336"/>
-      <c r="AH75" s="336"/>
-      <c r="AI75" s="336"/>
-      <c r="AJ75" s="336"/>
-      <c r="AK75" s="336"/>
-      <c r="AL75" s="336"/>
-      <c r="AM75" s="336"/>
-      <c r="AN75" s="337"/>
+      <c r="N75" s="334"/>
+      <c r="O75" s="334"/>
+      <c r="P75" s="334"/>
+      <c r="Q75" s="334"/>
+      <c r="R75" s="334"/>
+      <c r="S75" s="334"/>
+      <c r="T75" s="334"/>
+      <c r="U75" s="334"/>
+      <c r="V75" s="334"/>
+      <c r="W75" s="334"/>
+      <c r="X75" s="334"/>
+      <c r="Y75" s="334"/>
+      <c r="Z75" s="334"/>
+      <c r="AA75" s="334"/>
+      <c r="AB75" s="334"/>
+      <c r="AC75" s="334"/>
+      <c r="AD75" s="334"/>
+      <c r="AE75" s="334"/>
+      <c r="AF75" s="334"/>
+      <c r="AG75" s="334"/>
+      <c r="AH75" s="334"/>
+      <c r="AI75" s="334"/>
+      <c r="AJ75" s="334"/>
+      <c r="AK75" s="334"/>
+      <c r="AL75" s="334"/>
+      <c r="AM75" s="334"/>
+      <c r="AN75" s="335"/>
     </row>
     <row r="76" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A76" s="315" t="str">
+      <c r="A76" s="313" t="str">
         <f>CONCATENATE(AN10,AN27)</f>
         <v/>
       </c>
-      <c r="B76" s="316"/>
-      <c r="C76" s="316"/>
-      <c r="D76" s="316"/>
-      <c r="E76" s="316"/>
-      <c r="F76" s="316"/>
-      <c r="G76" s="316"/>
-      <c r="H76" s="316"/>
-      <c r="I76" s="316"/>
-      <c r="J76" s="316"/>
-      <c r="K76" s="316"/>
-      <c r="L76" s="317"/>
-      <c r="M76" s="324"/>
-      <c r="N76" s="325"/>
-      <c r="O76" s="325"/>
-      <c r="P76" s="325"/>
-      <c r="Q76" s="325"/>
-      <c r="R76" s="325"/>
-      <c r="S76" s="325"/>
-      <c r="T76" s="325"/>
-      <c r="U76" s="325"/>
-      <c r="V76" s="325"/>
-      <c r="W76" s="325"/>
-      <c r="X76" s="325"/>
-      <c r="Y76" s="325"/>
-      <c r="Z76" s="325"/>
-      <c r="AA76" s="325"/>
-      <c r="AB76" s="325"/>
-      <c r="AC76" s="325"/>
-      <c r="AD76" s="325"/>
-      <c r="AE76" s="325"/>
-      <c r="AF76" s="325"/>
-      <c r="AG76" s="325"/>
-      <c r="AH76" s="325"/>
-      <c r="AI76" s="325"/>
-      <c r="AJ76" s="325"/>
-      <c r="AK76" s="325"/>
-      <c r="AL76" s="325"/>
-      <c r="AM76" s="325"/>
-      <c r="AN76" s="326"/>
+      <c r="B76" s="314"/>
+      <c r="C76" s="314"/>
+      <c r="D76" s="314"/>
+      <c r="E76" s="314"/>
+      <c r="F76" s="314"/>
+      <c r="G76" s="314"/>
+      <c r="H76" s="314"/>
+      <c r="I76" s="314"/>
+      <c r="J76" s="314"/>
+      <c r="K76" s="314"/>
+      <c r="L76" s="315"/>
+      <c r="M76" s="322"/>
+      <c r="N76" s="323"/>
+      <c r="O76" s="323"/>
+      <c r="P76" s="323"/>
+      <c r="Q76" s="323"/>
+      <c r="R76" s="323"/>
+      <c r="S76" s="323"/>
+      <c r="T76" s="323"/>
+      <c r="U76" s="323"/>
+      <c r="V76" s="323"/>
+      <c r="W76" s="323"/>
+      <c r="X76" s="323"/>
+      <c r="Y76" s="323"/>
+      <c r="Z76" s="323"/>
+      <c r="AA76" s="323"/>
+      <c r="AB76" s="323"/>
+      <c r="AC76" s="323"/>
+      <c r="AD76" s="323"/>
+      <c r="AE76" s="323"/>
+      <c r="AF76" s="323"/>
+      <c r="AG76" s="323"/>
+      <c r="AH76" s="323"/>
+      <c r="AI76" s="323"/>
+      <c r="AJ76" s="323"/>
+      <c r="AK76" s="323"/>
+      <c r="AL76" s="323"/>
+      <c r="AM76" s="323"/>
+      <c r="AN76" s="324"/>
     </row>
     <row r="77" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A77" s="318"/>
-      <c r="B77" s="319"/>
-      <c r="C77" s="319"/>
-      <c r="D77" s="319"/>
-      <c r="E77" s="319"/>
-      <c r="F77" s="319"/>
-      <c r="G77" s="319"/>
-      <c r="H77" s="319"/>
-      <c r="I77" s="319"/>
-      <c r="J77" s="319"/>
-      <c r="K77" s="319"/>
-      <c r="L77" s="320"/>
-      <c r="M77" s="327"/>
-      <c r="N77" s="328"/>
-      <c r="O77" s="328"/>
-      <c r="P77" s="328"/>
-      <c r="Q77" s="328"/>
-      <c r="R77" s="328"/>
-      <c r="S77" s="328"/>
-      <c r="T77" s="328"/>
-      <c r="U77" s="328"/>
-      <c r="V77" s="328"/>
-      <c r="W77" s="328"/>
-      <c r="X77" s="328"/>
-      <c r="Y77" s="328"/>
-      <c r="Z77" s="328"/>
-      <c r="AA77" s="328"/>
-      <c r="AB77" s="328"/>
-      <c r="AC77" s="328"/>
-      <c r="AD77" s="328"/>
-      <c r="AE77" s="328"/>
-      <c r="AF77" s="328"/>
-      <c r="AG77" s="328"/>
-      <c r="AH77" s="328"/>
-      <c r="AI77" s="328"/>
-      <c r="AJ77" s="328"/>
-      <c r="AK77" s="328"/>
-      <c r="AL77" s="328"/>
-      <c r="AM77" s="328"/>
-      <c r="AN77" s="329"/>
+      <c r="A77" s="316"/>
+      <c r="B77" s="317"/>
+      <c r="C77" s="317"/>
+      <c r="D77" s="317"/>
+      <c r="E77" s="317"/>
+      <c r="F77" s="317"/>
+      <c r="G77" s="317"/>
+      <c r="H77" s="317"/>
+      <c r="I77" s="317"/>
+      <c r="J77" s="317"/>
+      <c r="K77" s="317"/>
+      <c r="L77" s="318"/>
+      <c r="M77" s="325"/>
+      <c r="N77" s="326"/>
+      <c r="O77" s="326"/>
+      <c r="P77" s="326"/>
+      <c r="Q77" s="326"/>
+      <c r="R77" s="326"/>
+      <c r="S77" s="326"/>
+      <c r="T77" s="326"/>
+      <c r="U77" s="326"/>
+      <c r="V77" s="326"/>
+      <c r="W77" s="326"/>
+      <c r="X77" s="326"/>
+      <c r="Y77" s="326"/>
+      <c r="Z77" s="326"/>
+      <c r="AA77" s="326"/>
+      <c r="AB77" s="326"/>
+      <c r="AC77" s="326"/>
+      <c r="AD77" s="326"/>
+      <c r="AE77" s="326"/>
+      <c r="AF77" s="326"/>
+      <c r="AG77" s="326"/>
+      <c r="AH77" s="326"/>
+      <c r="AI77" s="326"/>
+      <c r="AJ77" s="326"/>
+      <c r="AK77" s="326"/>
+      <c r="AL77" s="326"/>
+      <c r="AM77" s="326"/>
+      <c r="AN77" s="327"/>
     </row>
     <row r="78" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A78" s="318"/>
-      <c r="B78" s="319"/>
-      <c r="C78" s="319"/>
-      <c r="D78" s="319"/>
-      <c r="E78" s="319"/>
-      <c r="F78" s="319"/>
-      <c r="G78" s="319"/>
-      <c r="H78" s="319"/>
-      <c r="I78" s="319"/>
-      <c r="J78" s="319"/>
-      <c r="K78" s="319"/>
-      <c r="L78" s="320"/>
-      <c r="M78" s="327"/>
-      <c r="N78" s="328"/>
-      <c r="O78" s="328"/>
-      <c r="P78" s="328"/>
-      <c r="Q78" s="328"/>
-      <c r="R78" s="328"/>
-      <c r="S78" s="328"/>
-      <c r="T78" s="328"/>
-      <c r="U78" s="328"/>
-      <c r="V78" s="328"/>
-      <c r="W78" s="328"/>
-      <c r="X78" s="328"/>
-      <c r="Y78" s="328"/>
-      <c r="Z78" s="328"/>
-      <c r="AA78" s="328"/>
-      <c r="AB78" s="328"/>
-      <c r="AC78" s="328"/>
-      <c r="AD78" s="328"/>
-      <c r="AE78" s="328"/>
-      <c r="AF78" s="328"/>
-      <c r="AG78" s="328"/>
-      <c r="AH78" s="328"/>
-      <c r="AI78" s="328"/>
-      <c r="AJ78" s="328"/>
-      <c r="AK78" s="328"/>
-      <c r="AL78" s="328"/>
-      <c r="AM78" s="328"/>
-      <c r="AN78" s="329"/>
+      <c r="A78" s="316"/>
+      <c r="B78" s="317"/>
+      <c r="C78" s="317"/>
+      <c r="D78" s="317"/>
+      <c r="E78" s="317"/>
+      <c r="F78" s="317"/>
+      <c r="G78" s="317"/>
+      <c r="H78" s="317"/>
+      <c r="I78" s="317"/>
+      <c r="J78" s="317"/>
+      <c r="K78" s="317"/>
+      <c r="L78" s="318"/>
+      <c r="M78" s="325"/>
+      <c r="N78" s="326"/>
+      <c r="O78" s="326"/>
+      <c r="P78" s="326"/>
+      <c r="Q78" s="326"/>
+      <c r="R78" s="326"/>
+      <c r="S78" s="326"/>
+      <c r="T78" s="326"/>
+      <c r="U78" s="326"/>
+      <c r="V78" s="326"/>
+      <c r="W78" s="326"/>
+      <c r="X78" s="326"/>
+      <c r="Y78" s="326"/>
+      <c r="Z78" s="326"/>
+      <c r="AA78" s="326"/>
+      <c r="AB78" s="326"/>
+      <c r="AC78" s="326"/>
+      <c r="AD78" s="326"/>
+      <c r="AE78" s="326"/>
+      <c r="AF78" s="326"/>
+      <c r="AG78" s="326"/>
+      <c r="AH78" s="326"/>
+      <c r="AI78" s="326"/>
+      <c r="AJ78" s="326"/>
+      <c r="AK78" s="326"/>
+      <c r="AL78" s="326"/>
+      <c r="AM78" s="326"/>
+      <c r="AN78" s="327"/>
     </row>
     <row r="79" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A79" s="318"/>
-      <c r="B79" s="319"/>
-      <c r="C79" s="319"/>
-      <c r="D79" s="319"/>
-      <c r="E79" s="319"/>
-      <c r="F79" s="319"/>
-      <c r="G79" s="319"/>
-      <c r="H79" s="319"/>
-      <c r="I79" s="319"/>
-      <c r="J79" s="319"/>
-      <c r="K79" s="319"/>
-      <c r="L79" s="320"/>
-      <c r="M79" s="327"/>
-      <c r="N79" s="328"/>
-      <c r="O79" s="328"/>
-      <c r="P79" s="328"/>
-      <c r="Q79" s="328"/>
-      <c r="R79" s="328"/>
-      <c r="S79" s="328"/>
-      <c r="T79" s="328"/>
-      <c r="U79" s="328"/>
-      <c r="V79" s="328"/>
-      <c r="W79" s="328"/>
-      <c r="X79" s="328"/>
-      <c r="Y79" s="328"/>
-      <c r="Z79" s="328"/>
-      <c r="AA79" s="328"/>
-      <c r="AB79" s="328"/>
-      <c r="AC79" s="328"/>
-      <c r="AD79" s="328"/>
-      <c r="AE79" s="328"/>
-      <c r="AF79" s="328"/>
-      <c r="AG79" s="328"/>
-      <c r="AH79" s="328"/>
-      <c r="AI79" s="328"/>
-      <c r="AJ79" s="328"/>
-      <c r="AK79" s="328"/>
-      <c r="AL79" s="328"/>
-      <c r="AM79" s="328"/>
-      <c r="AN79" s="329"/>
+      <c r="A79" s="316"/>
+      <c r="B79" s="317"/>
+      <c r="C79" s="317"/>
+      <c r="D79" s="317"/>
+      <c r="E79" s="317"/>
+      <c r="F79" s="317"/>
+      <c r="G79" s="317"/>
+      <c r="H79" s="317"/>
+      <c r="I79" s="317"/>
+      <c r="J79" s="317"/>
+      <c r="K79" s="317"/>
+      <c r="L79" s="318"/>
+      <c r="M79" s="325"/>
+      <c r="N79" s="326"/>
+      <c r="O79" s="326"/>
+      <c r="P79" s="326"/>
+      <c r="Q79" s="326"/>
+      <c r="R79" s="326"/>
+      <c r="S79" s="326"/>
+      <c r="T79" s="326"/>
+      <c r="U79" s="326"/>
+      <c r="V79" s="326"/>
+      <c r="W79" s="326"/>
+      <c r="X79" s="326"/>
+      <c r="Y79" s="326"/>
+      <c r="Z79" s="326"/>
+      <c r="AA79" s="326"/>
+      <c r="AB79" s="326"/>
+      <c r="AC79" s="326"/>
+      <c r="AD79" s="326"/>
+      <c r="AE79" s="326"/>
+      <c r="AF79" s="326"/>
+      <c r="AG79" s="326"/>
+      <c r="AH79" s="326"/>
+      <c r="AI79" s="326"/>
+      <c r="AJ79" s="326"/>
+      <c r="AK79" s="326"/>
+      <c r="AL79" s="326"/>
+      <c r="AM79" s="326"/>
+      <c r="AN79" s="327"/>
     </row>
     <row r="80" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A80" s="318"/>
-      <c r="B80" s="319"/>
-      <c r="C80" s="319"/>
-      <c r="D80" s="319"/>
-      <c r="E80" s="319"/>
-      <c r="F80" s="319"/>
-      <c r="G80" s="319"/>
-      <c r="H80" s="319"/>
-      <c r="I80" s="319"/>
-      <c r="J80" s="319"/>
-      <c r="K80" s="319"/>
-      <c r="L80" s="320"/>
-      <c r="M80" s="327"/>
-      <c r="N80" s="328"/>
-      <c r="O80" s="328"/>
-      <c r="P80" s="328"/>
-      <c r="Q80" s="328"/>
-      <c r="R80" s="328"/>
-      <c r="S80" s="328"/>
-      <c r="T80" s="328"/>
-      <c r="U80" s="328"/>
-      <c r="V80" s="328"/>
-      <c r="W80" s="328"/>
-      <c r="X80" s="328"/>
-      <c r="Y80" s="328"/>
-      <c r="Z80" s="328"/>
-      <c r="AA80" s="328"/>
-      <c r="AB80" s="328"/>
-      <c r="AC80" s="328"/>
-      <c r="AD80" s="328"/>
-      <c r="AE80" s="328"/>
-      <c r="AF80" s="328"/>
-      <c r="AG80" s="328"/>
-      <c r="AH80" s="328"/>
-      <c r="AI80" s="328"/>
-      <c r="AJ80" s="328"/>
-      <c r="AK80" s="328"/>
-      <c r="AL80" s="328"/>
-      <c r="AM80" s="328"/>
-      <c r="AN80" s="329"/>
+      <c r="A80" s="316"/>
+      <c r="B80" s="317"/>
+      <c r="C80" s="317"/>
+      <c r="D80" s="317"/>
+      <c r="E80" s="317"/>
+      <c r="F80" s="317"/>
+      <c r="G80" s="317"/>
+      <c r="H80" s="317"/>
+      <c r="I80" s="317"/>
+      <c r="J80" s="317"/>
+      <c r="K80" s="317"/>
+      <c r="L80" s="318"/>
+      <c r="M80" s="325"/>
+      <c r="N80" s="326"/>
+      <c r="O80" s="326"/>
+      <c r="P80" s="326"/>
+      <c r="Q80" s="326"/>
+      <c r="R80" s="326"/>
+      <c r="S80" s="326"/>
+      <c r="T80" s="326"/>
+      <c r="U80" s="326"/>
+      <c r="V80" s="326"/>
+      <c r="W80" s="326"/>
+      <c r="X80" s="326"/>
+      <c r="Y80" s="326"/>
+      <c r="Z80" s="326"/>
+      <c r="AA80" s="326"/>
+      <c r="AB80" s="326"/>
+      <c r="AC80" s="326"/>
+      <c r="AD80" s="326"/>
+      <c r="AE80" s="326"/>
+      <c r="AF80" s="326"/>
+      <c r="AG80" s="326"/>
+      <c r="AH80" s="326"/>
+      <c r="AI80" s="326"/>
+      <c r="AJ80" s="326"/>
+      <c r="AK80" s="326"/>
+      <c r="AL80" s="326"/>
+      <c r="AM80" s="326"/>
+      <c r="AN80" s="327"/>
     </row>
     <row r="81" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A81" s="318"/>
-      <c r="B81" s="319"/>
-      <c r="C81" s="319"/>
-      <c r="D81" s="319"/>
-      <c r="E81" s="319"/>
-      <c r="F81" s="319"/>
-      <c r="G81" s="319"/>
-      <c r="H81" s="319"/>
-      <c r="I81" s="319"/>
-      <c r="J81" s="319"/>
-      <c r="K81" s="319"/>
-      <c r="L81" s="320"/>
-      <c r="M81" s="327"/>
-      <c r="N81" s="328"/>
-      <c r="O81" s="328"/>
-      <c r="P81" s="328"/>
-      <c r="Q81" s="328"/>
-      <c r="R81" s="328"/>
-      <c r="S81" s="328"/>
-      <c r="T81" s="328"/>
-      <c r="U81" s="328"/>
-      <c r="V81" s="328"/>
-      <c r="W81" s="328"/>
-      <c r="X81" s="328"/>
-      <c r="Y81" s="328"/>
-      <c r="Z81" s="328"/>
-      <c r="AA81" s="328"/>
-      <c r="AB81" s="328"/>
-      <c r="AC81" s="328"/>
-      <c r="AD81" s="328"/>
-      <c r="AE81" s="328"/>
-      <c r="AF81" s="328"/>
-      <c r="AG81" s="328"/>
-      <c r="AH81" s="328"/>
-      <c r="AI81" s="328"/>
-      <c r="AJ81" s="328"/>
-      <c r="AK81" s="328"/>
-      <c r="AL81" s="328"/>
-      <c r="AM81" s="328"/>
-      <c r="AN81" s="329"/>
+      <c r="A81" s="316"/>
+      <c r="B81" s="317"/>
+      <c r="C81" s="317"/>
+      <c r="D81" s="317"/>
+      <c r="E81" s="317"/>
+      <c r="F81" s="317"/>
+      <c r="G81" s="317"/>
+      <c r="H81" s="317"/>
+      <c r="I81" s="317"/>
+      <c r="J81" s="317"/>
+      <c r="K81" s="317"/>
+      <c r="L81" s="318"/>
+      <c r="M81" s="325"/>
+      <c r="N81" s="326"/>
+      <c r="O81" s="326"/>
+      <c r="P81" s="326"/>
+      <c r="Q81" s="326"/>
+      <c r="R81" s="326"/>
+      <c r="S81" s="326"/>
+      <c r="T81" s="326"/>
+      <c r="U81" s="326"/>
+      <c r="V81" s="326"/>
+      <c r="W81" s="326"/>
+      <c r="X81" s="326"/>
+      <c r="Y81" s="326"/>
+      <c r="Z81" s="326"/>
+      <c r="AA81" s="326"/>
+      <c r="AB81" s="326"/>
+      <c r="AC81" s="326"/>
+      <c r="AD81" s="326"/>
+      <c r="AE81" s="326"/>
+      <c r="AF81" s="326"/>
+      <c r="AG81" s="326"/>
+      <c r="AH81" s="326"/>
+      <c r="AI81" s="326"/>
+      <c r="AJ81" s="326"/>
+      <c r="AK81" s="326"/>
+      <c r="AL81" s="326"/>
+      <c r="AM81" s="326"/>
+      <c r="AN81" s="327"/>
     </row>
     <row r="82" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A82" s="318"/>
-      <c r="B82" s="319"/>
-      <c r="C82" s="319"/>
-      <c r="D82" s="319"/>
-      <c r="E82" s="319"/>
-      <c r="F82" s="319"/>
-      <c r="G82" s="319"/>
-      <c r="H82" s="319"/>
-      <c r="I82" s="319"/>
-      <c r="J82" s="319"/>
-      <c r="K82" s="319"/>
-      <c r="L82" s="320"/>
-      <c r="M82" s="327"/>
-      <c r="N82" s="328"/>
-      <c r="O82" s="328"/>
-      <c r="P82" s="328"/>
-      <c r="Q82" s="328"/>
-      <c r="R82" s="328"/>
-      <c r="S82" s="328"/>
-      <c r="T82" s="328"/>
-      <c r="U82" s="328"/>
-      <c r="V82" s="328"/>
-      <c r="W82" s="328"/>
-      <c r="X82" s="328"/>
-      <c r="Y82" s="328"/>
-      <c r="Z82" s="328"/>
-      <c r="AA82" s="328"/>
-      <c r="AB82" s="328"/>
-      <c r="AC82" s="328"/>
-      <c r="AD82" s="328"/>
-      <c r="AE82" s="328"/>
-      <c r="AF82" s="328"/>
-      <c r="AG82" s="328"/>
-      <c r="AH82" s="328"/>
-      <c r="AI82" s="328"/>
-      <c r="AJ82" s="328"/>
-      <c r="AK82" s="328"/>
-      <c r="AL82" s="328"/>
-      <c r="AM82" s="328"/>
-      <c r="AN82" s="329"/>
+      <c r="A82" s="316"/>
+      <c r="B82" s="317"/>
+      <c r="C82" s="317"/>
+      <c r="D82" s="317"/>
+      <c r="E82" s="317"/>
+      <c r="F82" s="317"/>
+      <c r="G82" s="317"/>
+      <c r="H82" s="317"/>
+      <c r="I82" s="317"/>
+      <c r="J82" s="317"/>
+      <c r="K82" s="317"/>
+      <c r="L82" s="318"/>
+      <c r="M82" s="325"/>
+      <c r="N82" s="326"/>
+      <c r="O82" s="326"/>
+      <c r="P82" s="326"/>
+      <c r="Q82" s="326"/>
+      <c r="R82" s="326"/>
+      <c r="S82" s="326"/>
+      <c r="T82" s="326"/>
+      <c r="U82" s="326"/>
+      <c r="V82" s="326"/>
+      <c r="W82" s="326"/>
+      <c r="X82" s="326"/>
+      <c r="Y82" s="326"/>
+      <c r="Z82" s="326"/>
+      <c r="AA82" s="326"/>
+      <c r="AB82" s="326"/>
+      <c r="AC82" s="326"/>
+      <c r="AD82" s="326"/>
+      <c r="AE82" s="326"/>
+      <c r="AF82" s="326"/>
+      <c r="AG82" s="326"/>
+      <c r="AH82" s="326"/>
+      <c r="AI82" s="326"/>
+      <c r="AJ82" s="326"/>
+      <c r="AK82" s="326"/>
+      <c r="AL82" s="326"/>
+      <c r="AM82" s="326"/>
+      <c r="AN82" s="327"/>
     </row>
     <row r="83" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A83" s="318"/>
-      <c r="B83" s="319"/>
-      <c r="C83" s="319"/>
-      <c r="D83" s="319"/>
-      <c r="E83" s="319"/>
-      <c r="F83" s="319"/>
-      <c r="G83" s="319"/>
-      <c r="H83" s="319"/>
-      <c r="I83" s="319"/>
-      <c r="J83" s="319"/>
-      <c r="K83" s="319"/>
-      <c r="L83" s="320"/>
-      <c r="M83" s="327"/>
-      <c r="N83" s="328"/>
-      <c r="O83" s="328"/>
-      <c r="P83" s="328"/>
-      <c r="Q83" s="328"/>
-      <c r="R83" s="328"/>
-      <c r="S83" s="328"/>
-      <c r="T83" s="328"/>
-      <c r="U83" s="328"/>
-      <c r="V83" s="328"/>
-      <c r="W83" s="328"/>
-      <c r="X83" s="328"/>
-      <c r="Y83" s="328"/>
-      <c r="Z83" s="328"/>
-      <c r="AA83" s="328"/>
-      <c r="AB83" s="328"/>
-      <c r="AC83" s="328"/>
-      <c r="AD83" s="328"/>
-      <c r="AE83" s="328"/>
-      <c r="AF83" s="328"/>
-      <c r="AG83" s="328"/>
-      <c r="AH83" s="328"/>
-      <c r="AI83" s="328"/>
-      <c r="AJ83" s="328"/>
-      <c r="AK83" s="328"/>
-      <c r="AL83" s="328"/>
-      <c r="AM83" s="328"/>
-      <c r="AN83" s="329"/>
+      <c r="A83" s="316"/>
+      <c r="B83" s="317"/>
+      <c r="C83" s="317"/>
+      <c r="D83" s="317"/>
+      <c r="E83" s="317"/>
+      <c r="F83" s="317"/>
+      <c r="G83" s="317"/>
+      <c r="H83" s="317"/>
+      <c r="I83" s="317"/>
+      <c r="J83" s="317"/>
+      <c r="K83" s="317"/>
+      <c r="L83" s="318"/>
+      <c r="M83" s="325"/>
+      <c r="N83" s="326"/>
+      <c r="O83" s="326"/>
+      <c r="P83" s="326"/>
+      <c r="Q83" s="326"/>
+      <c r="R83" s="326"/>
+      <c r="S83" s="326"/>
+      <c r="T83" s="326"/>
+      <c r="U83" s="326"/>
+      <c r="V83" s="326"/>
+      <c r="W83" s="326"/>
+      <c r="X83" s="326"/>
+      <c r="Y83" s="326"/>
+      <c r="Z83" s="326"/>
+      <c r="AA83" s="326"/>
+      <c r="AB83" s="326"/>
+      <c r="AC83" s="326"/>
+      <c r="AD83" s="326"/>
+      <c r="AE83" s="326"/>
+      <c r="AF83" s="326"/>
+      <c r="AG83" s="326"/>
+      <c r="AH83" s="326"/>
+      <c r="AI83" s="326"/>
+      <c r="AJ83" s="326"/>
+      <c r="AK83" s="326"/>
+      <c r="AL83" s="326"/>
+      <c r="AM83" s="326"/>
+      <c r="AN83" s="327"/>
     </row>
     <row r="84" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A84" s="318"/>
-      <c r="B84" s="319"/>
-      <c r="C84" s="319"/>
-      <c r="D84" s="319"/>
-      <c r="E84" s="319"/>
-      <c r="F84" s="319"/>
-      <c r="G84" s="319"/>
-      <c r="H84" s="319"/>
-      <c r="I84" s="319"/>
-      <c r="J84" s="319"/>
-      <c r="K84" s="319"/>
-      <c r="L84" s="320"/>
-      <c r="M84" s="327"/>
-      <c r="N84" s="328"/>
-      <c r="O84" s="328"/>
-      <c r="P84" s="328"/>
-      <c r="Q84" s="328"/>
-      <c r="R84" s="328"/>
-      <c r="S84" s="328"/>
-      <c r="T84" s="328"/>
-      <c r="U84" s="328"/>
-      <c r="V84" s="328"/>
-      <c r="W84" s="328"/>
-      <c r="X84" s="328"/>
-      <c r="Y84" s="328"/>
-      <c r="Z84" s="328"/>
-      <c r="AA84" s="328"/>
-      <c r="AB84" s="328"/>
-      <c r="AC84" s="328"/>
-      <c r="AD84" s="328"/>
-      <c r="AE84" s="328"/>
-      <c r="AF84" s="328"/>
-      <c r="AG84" s="328"/>
-      <c r="AH84" s="328"/>
-      <c r="AI84" s="328"/>
-      <c r="AJ84" s="328"/>
-      <c r="AK84" s="328"/>
-      <c r="AL84" s="328"/>
-      <c r="AM84" s="328"/>
-      <c r="AN84" s="329"/>
+      <c r="A84" s="316"/>
+      <c r="B84" s="317"/>
+      <c r="C84" s="317"/>
+      <c r="D84" s="317"/>
+      <c r="E84" s="317"/>
+      <c r="F84" s="317"/>
+      <c r="G84" s="317"/>
+      <c r="H84" s="317"/>
+      <c r="I84" s="317"/>
+      <c r="J84" s="317"/>
+      <c r="K84" s="317"/>
+      <c r="L84" s="318"/>
+      <c r="M84" s="325"/>
+      <c r="N84" s="326"/>
+      <c r="O84" s="326"/>
+      <c r="P84" s="326"/>
+      <c r="Q84" s="326"/>
+      <c r="R84" s="326"/>
+      <c r="S84" s="326"/>
+      <c r="T84" s="326"/>
+      <c r="U84" s="326"/>
+      <c r="V84" s="326"/>
+      <c r="W84" s="326"/>
+      <c r="X84" s="326"/>
+      <c r="Y84" s="326"/>
+      <c r="Z84" s="326"/>
+      <c r="AA84" s="326"/>
+      <c r="AB84" s="326"/>
+      <c r="AC84" s="326"/>
+      <c r="AD84" s="326"/>
+      <c r="AE84" s="326"/>
+      <c r="AF84" s="326"/>
+      <c r="AG84" s="326"/>
+      <c r="AH84" s="326"/>
+      <c r="AI84" s="326"/>
+      <c r="AJ84" s="326"/>
+      <c r="AK84" s="326"/>
+      <c r="AL84" s="326"/>
+      <c r="AM84" s="326"/>
+      <c r="AN84" s="327"/>
     </row>
     <row r="85" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A85" s="318"/>
-      <c r="B85" s="319"/>
-      <c r="C85" s="319"/>
-      <c r="D85" s="319"/>
-      <c r="E85" s="319"/>
-      <c r="F85" s="319"/>
-      <c r="G85" s="319"/>
-      <c r="H85" s="319"/>
-      <c r="I85" s="319"/>
-      <c r="J85" s="319"/>
-      <c r="K85" s="319"/>
-      <c r="L85" s="320"/>
-      <c r="M85" s="327"/>
-      <c r="N85" s="328"/>
-      <c r="O85" s="328"/>
-      <c r="P85" s="328"/>
-      <c r="Q85" s="328"/>
-      <c r="R85" s="328"/>
-      <c r="S85" s="328"/>
-      <c r="T85" s="328"/>
-      <c r="U85" s="328"/>
-      <c r="V85" s="328"/>
-      <c r="W85" s="328"/>
-      <c r="X85" s="328"/>
-      <c r="Y85" s="328"/>
-      <c r="Z85" s="328"/>
-      <c r="AA85" s="328"/>
-      <c r="AB85" s="328"/>
-      <c r="AC85" s="328"/>
-      <c r="AD85" s="328"/>
-      <c r="AE85" s="328"/>
-      <c r="AF85" s="328"/>
-      <c r="AG85" s="328"/>
-      <c r="AH85" s="328"/>
-      <c r="AI85" s="328"/>
-      <c r="AJ85" s="328"/>
-      <c r="AK85" s="328"/>
-      <c r="AL85" s="328"/>
-      <c r="AM85" s="328"/>
-      <c r="AN85" s="329"/>
+      <c r="A85" s="316"/>
+      <c r="B85" s="317"/>
+      <c r="C85" s="317"/>
+      <c r="D85" s="317"/>
+      <c r="E85" s="317"/>
+      <c r="F85" s="317"/>
+      <c r="G85" s="317"/>
+      <c r="H85" s="317"/>
+      <c r="I85" s="317"/>
+      <c r="J85" s="317"/>
+      <c r="K85" s="317"/>
+      <c r="L85" s="318"/>
+      <c r="M85" s="325"/>
+      <c r="N85" s="326"/>
+      <c r="O85" s="326"/>
+      <c r="P85" s="326"/>
+      <c r="Q85" s="326"/>
+      <c r="R85" s="326"/>
+      <c r="S85" s="326"/>
+      <c r="T85" s="326"/>
+      <c r="U85" s="326"/>
+      <c r="V85" s="326"/>
+      <c r="W85" s="326"/>
+      <c r="X85" s="326"/>
+      <c r="Y85" s="326"/>
+      <c r="Z85" s="326"/>
+      <c r="AA85" s="326"/>
+      <c r="AB85" s="326"/>
+      <c r="AC85" s="326"/>
+      <c r="AD85" s="326"/>
+      <c r="AE85" s="326"/>
+      <c r="AF85" s="326"/>
+      <c r="AG85" s="326"/>
+      <c r="AH85" s="326"/>
+      <c r="AI85" s="326"/>
+      <c r="AJ85" s="326"/>
+      <c r="AK85" s="326"/>
+      <c r="AL85" s="326"/>
+      <c r="AM85" s="326"/>
+      <c r="AN85" s="327"/>
     </row>
     <row r="86" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A86" s="318"/>
-      <c r="B86" s="319"/>
-      <c r="C86" s="319"/>
-      <c r="D86" s="319"/>
-      <c r="E86" s="319"/>
-      <c r="F86" s="319"/>
-      <c r="G86" s="319"/>
-      <c r="H86" s="319"/>
-      <c r="I86" s="319"/>
-      <c r="J86" s="319"/>
-      <c r="K86" s="319"/>
-      <c r="L86" s="320"/>
-      <c r="M86" s="327"/>
-      <c r="N86" s="328"/>
-      <c r="O86" s="328"/>
-      <c r="P86" s="328"/>
-      <c r="Q86" s="328"/>
-      <c r="R86" s="328"/>
-      <c r="S86" s="328"/>
-      <c r="T86" s="328"/>
-      <c r="U86" s="328"/>
-      <c r="V86" s="328"/>
-      <c r="W86" s="328"/>
-      <c r="X86" s="328"/>
-      <c r="Y86" s="328"/>
-      <c r="Z86" s="328"/>
-      <c r="AA86" s="328"/>
-      <c r="AB86" s="328"/>
-      <c r="AC86" s="328"/>
-      <c r="AD86" s="328"/>
-      <c r="AE86" s="328"/>
-      <c r="AF86" s="328"/>
-      <c r="AG86" s="328"/>
-      <c r="AH86" s="328"/>
-      <c r="AI86" s="328"/>
-      <c r="AJ86" s="328"/>
-      <c r="AK86" s="328"/>
-      <c r="AL86" s="328"/>
-      <c r="AM86" s="328"/>
-      <c r="AN86" s="329"/>
+      <c r="A86" s="316"/>
+      <c r="B86" s="317"/>
+      <c r="C86" s="317"/>
+      <c r="D86" s="317"/>
+      <c r="E86" s="317"/>
+      <c r="F86" s="317"/>
+      <c r="G86" s="317"/>
+      <c r="H86" s="317"/>
+      <c r="I86" s="317"/>
+      <c r="J86" s="317"/>
+      <c r="K86" s="317"/>
+      <c r="L86" s="318"/>
+      <c r="M86" s="325"/>
+      <c r="N86" s="326"/>
+      <c r="O86" s="326"/>
+      <c r="P86" s="326"/>
+      <c r="Q86" s="326"/>
+      <c r="R86" s="326"/>
+      <c r="S86" s="326"/>
+      <c r="T86" s="326"/>
+      <c r="U86" s="326"/>
+      <c r="V86" s="326"/>
+      <c r="W86" s="326"/>
+      <c r="X86" s="326"/>
+      <c r="Y86" s="326"/>
+      <c r="Z86" s="326"/>
+      <c r="AA86" s="326"/>
+      <c r="AB86" s="326"/>
+      <c r="AC86" s="326"/>
+      <c r="AD86" s="326"/>
+      <c r="AE86" s="326"/>
+      <c r="AF86" s="326"/>
+      <c r="AG86" s="326"/>
+      <c r="AH86" s="326"/>
+      <c r="AI86" s="326"/>
+      <c r="AJ86" s="326"/>
+      <c r="AK86" s="326"/>
+      <c r="AL86" s="326"/>
+      <c r="AM86" s="326"/>
+      <c r="AN86" s="327"/>
     </row>
     <row r="87" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A87" s="318"/>
-      <c r="B87" s="319"/>
-      <c r="C87" s="319"/>
-      <c r="D87" s="319"/>
-      <c r="E87" s="319"/>
-      <c r="F87" s="319"/>
-      <c r="G87" s="319"/>
-      <c r="H87" s="319"/>
-      <c r="I87" s="319"/>
-      <c r="J87" s="319"/>
-      <c r="K87" s="319"/>
-      <c r="L87" s="320"/>
-      <c r="M87" s="327"/>
-      <c r="N87" s="328"/>
-      <c r="O87" s="328"/>
-      <c r="P87" s="328"/>
-      <c r="Q87" s="328"/>
-      <c r="R87" s="328"/>
-      <c r="S87" s="328"/>
-      <c r="T87" s="328"/>
-      <c r="U87" s="328"/>
-      <c r="V87" s="328"/>
-      <c r="W87" s="328"/>
-      <c r="X87" s="328"/>
-      <c r="Y87" s="328"/>
-      <c r="Z87" s="328"/>
-      <c r="AA87" s="328"/>
-      <c r="AB87" s="328"/>
-      <c r="AC87" s="328"/>
-      <c r="AD87" s="328"/>
-      <c r="AE87" s="328"/>
-      <c r="AF87" s="328"/>
-      <c r="AG87" s="328"/>
-      <c r="AH87" s="328"/>
-      <c r="AI87" s="328"/>
-      <c r="AJ87" s="328"/>
-      <c r="AK87" s="328"/>
-      <c r="AL87" s="328"/>
-      <c r="AM87" s="328"/>
-      <c r="AN87" s="329"/>
+      <c r="A87" s="316"/>
+      <c r="B87" s="317"/>
+      <c r="C87" s="317"/>
+      <c r="D87" s="317"/>
+      <c r="E87" s="317"/>
+      <c r="F87" s="317"/>
+      <c r="G87" s="317"/>
+      <c r="H87" s="317"/>
+      <c r="I87" s="317"/>
+      <c r="J87" s="317"/>
+      <c r="K87" s="317"/>
+      <c r="L87" s="318"/>
+      <c r="M87" s="325"/>
+      <c r="N87" s="326"/>
+      <c r="O87" s="326"/>
+      <c r="P87" s="326"/>
+      <c r="Q87" s="326"/>
+      <c r="R87" s="326"/>
+      <c r="S87" s="326"/>
+      <c r="T87" s="326"/>
+      <c r="U87" s="326"/>
+      <c r="V87" s="326"/>
+      <c r="W87" s="326"/>
+      <c r="X87" s="326"/>
+      <c r="Y87" s="326"/>
+      <c r="Z87" s="326"/>
+      <c r="AA87" s="326"/>
+      <c r="AB87" s="326"/>
+      <c r="AC87" s="326"/>
+      <c r="AD87" s="326"/>
+      <c r="AE87" s="326"/>
+      <c r="AF87" s="326"/>
+      <c r="AG87" s="326"/>
+      <c r="AH87" s="326"/>
+      <c r="AI87" s="326"/>
+      <c r="AJ87" s="326"/>
+      <c r="AK87" s="326"/>
+      <c r="AL87" s="326"/>
+      <c r="AM87" s="326"/>
+      <c r="AN87" s="327"/>
     </row>
     <row r="88" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A88" s="318"/>
-      <c r="B88" s="319"/>
-      <c r="C88" s="319"/>
-      <c r="D88" s="319"/>
-      <c r="E88" s="319"/>
-      <c r="F88" s="319"/>
-      <c r="G88" s="319"/>
-      <c r="H88" s="319"/>
-      <c r="I88" s="319"/>
-      <c r="J88" s="319"/>
-      <c r="K88" s="319"/>
-      <c r="L88" s="320"/>
-      <c r="M88" s="327"/>
-      <c r="N88" s="328"/>
-      <c r="O88" s="328"/>
-      <c r="P88" s="328"/>
-      <c r="Q88" s="328"/>
-      <c r="R88" s="328"/>
-      <c r="S88" s="328"/>
-      <c r="T88" s="328"/>
-      <c r="U88" s="328"/>
-      <c r="V88" s="328"/>
-      <c r="W88" s="328"/>
-      <c r="X88" s="328"/>
-      <c r="Y88" s="328"/>
-      <c r="Z88" s="328"/>
-      <c r="AA88" s="328"/>
-      <c r="AB88" s="328"/>
-      <c r="AC88" s="328"/>
-      <c r="AD88" s="328"/>
-      <c r="AE88" s="328"/>
-      <c r="AF88" s="328"/>
-      <c r="AG88" s="328"/>
-      <c r="AH88" s="328"/>
-      <c r="AI88" s="328"/>
-      <c r="AJ88" s="328"/>
-      <c r="AK88" s="328"/>
-      <c r="AL88" s="328"/>
-      <c r="AM88" s="328"/>
-      <c r="AN88" s="329"/>
+      <c r="A88" s="316"/>
+      <c r="B88" s="317"/>
+      <c r="C88" s="317"/>
+      <c r="D88" s="317"/>
+      <c r="E88" s="317"/>
+      <c r="F88" s="317"/>
+      <c r="G88" s="317"/>
+      <c r="H88" s="317"/>
+      <c r="I88" s="317"/>
+      <c r="J88" s="317"/>
+      <c r="K88" s="317"/>
+      <c r="L88" s="318"/>
+      <c r="M88" s="325"/>
+      <c r="N88" s="326"/>
+      <c r="O88" s="326"/>
+      <c r="P88" s="326"/>
+      <c r="Q88" s="326"/>
+      <c r="R88" s="326"/>
+      <c r="S88" s="326"/>
+      <c r="T88" s="326"/>
+      <c r="U88" s="326"/>
+      <c r="V88" s="326"/>
+      <c r="W88" s="326"/>
+      <c r="X88" s="326"/>
+      <c r="Y88" s="326"/>
+      <c r="Z88" s="326"/>
+      <c r="AA88" s="326"/>
+      <c r="AB88" s="326"/>
+      <c r="AC88" s="326"/>
+      <c r="AD88" s="326"/>
+      <c r="AE88" s="326"/>
+      <c r="AF88" s="326"/>
+      <c r="AG88" s="326"/>
+      <c r="AH88" s="326"/>
+      <c r="AI88" s="326"/>
+      <c r="AJ88" s="326"/>
+      <c r="AK88" s="326"/>
+      <c r="AL88" s="326"/>
+      <c r="AM88" s="326"/>
+      <c r="AN88" s="327"/>
     </row>
     <row r="89" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A89" s="318"/>
-      <c r="B89" s="319"/>
-      <c r="C89" s="319"/>
-      <c r="D89" s="319"/>
-      <c r="E89" s="319"/>
-      <c r="F89" s="319"/>
-      <c r="G89" s="319"/>
-      <c r="H89" s="319"/>
-      <c r="I89" s="319"/>
-      <c r="J89" s="319"/>
-      <c r="K89" s="319"/>
-      <c r="L89" s="320"/>
-      <c r="M89" s="327"/>
-      <c r="N89" s="328"/>
-      <c r="O89" s="328"/>
-      <c r="P89" s="328"/>
-      <c r="Q89" s="328"/>
-      <c r="R89" s="328"/>
-      <c r="S89" s="328"/>
-      <c r="T89" s="328"/>
-      <c r="U89" s="328"/>
-      <c r="V89" s="328"/>
-      <c r="W89" s="328"/>
-      <c r="X89" s="328"/>
-      <c r="Y89" s="328"/>
-      <c r="Z89" s="328"/>
-      <c r="AA89" s="328"/>
-      <c r="AB89" s="328"/>
-      <c r="AC89" s="328"/>
-      <c r="AD89" s="328"/>
-      <c r="AE89" s="328"/>
-      <c r="AF89" s="328"/>
-      <c r="AG89" s="328"/>
-      <c r="AH89" s="328"/>
-      <c r="AI89" s="328"/>
-      <c r="AJ89" s="328"/>
-      <c r="AK89" s="328"/>
-      <c r="AL89" s="328"/>
-      <c r="AM89" s="328"/>
-      <c r="AN89" s="329"/>
+      <c r="A89" s="316"/>
+      <c r="B89" s="317"/>
+      <c r="C89" s="317"/>
+      <c r="D89" s="317"/>
+      <c r="E89" s="317"/>
+      <c r="F89" s="317"/>
+      <c r="G89" s="317"/>
+      <c r="H89" s="317"/>
+      <c r="I89" s="317"/>
+      <c r="J89" s="317"/>
+      <c r="K89" s="317"/>
+      <c r="L89" s="318"/>
+      <c r="M89" s="325"/>
+      <c r="N89" s="326"/>
+      <c r="O89" s="326"/>
+      <c r="P89" s="326"/>
+      <c r="Q89" s="326"/>
+      <c r="R89" s="326"/>
+      <c r="S89" s="326"/>
+      <c r="T89" s="326"/>
+      <c r="U89" s="326"/>
+      <c r="V89" s="326"/>
+      <c r="W89" s="326"/>
+      <c r="X89" s="326"/>
+      <c r="Y89" s="326"/>
+      <c r="Z89" s="326"/>
+      <c r="AA89" s="326"/>
+      <c r="AB89" s="326"/>
+      <c r="AC89" s="326"/>
+      <c r="AD89" s="326"/>
+      <c r="AE89" s="326"/>
+      <c r="AF89" s="326"/>
+      <c r="AG89" s="326"/>
+      <c r="AH89" s="326"/>
+      <c r="AI89" s="326"/>
+      <c r="AJ89" s="326"/>
+      <c r="AK89" s="326"/>
+      <c r="AL89" s="326"/>
+      <c r="AM89" s="326"/>
+      <c r="AN89" s="327"/>
     </row>
     <row r="90" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A90" s="318"/>
-      <c r="B90" s="319"/>
-      <c r="C90" s="319"/>
-      <c r="D90" s="319"/>
-      <c r="E90" s="319"/>
-      <c r="F90" s="319"/>
-      <c r="G90" s="319"/>
-      <c r="H90" s="319"/>
-      <c r="I90" s="319"/>
-      <c r="J90" s="319"/>
-      <c r="K90" s="319"/>
-      <c r="L90" s="320"/>
-      <c r="M90" s="327"/>
-      <c r="N90" s="328"/>
-      <c r="O90" s="328"/>
-      <c r="P90" s="328"/>
-      <c r="Q90" s="328"/>
-      <c r="R90" s="328"/>
-      <c r="S90" s="328"/>
-      <c r="T90" s="328"/>
-      <c r="U90" s="328"/>
-      <c r="V90" s="328"/>
-      <c r="W90" s="328"/>
-      <c r="X90" s="328"/>
-      <c r="Y90" s="328"/>
-      <c r="Z90" s="328"/>
-      <c r="AA90" s="328"/>
-      <c r="AB90" s="328"/>
-      <c r="AC90" s="328"/>
-      <c r="AD90" s="328"/>
-      <c r="AE90" s="328"/>
-      <c r="AF90" s="328"/>
-      <c r="AG90" s="328"/>
-      <c r="AH90" s="328"/>
-      <c r="AI90" s="328"/>
-      <c r="AJ90" s="328"/>
-      <c r="AK90" s="328"/>
-      <c r="AL90" s="328"/>
-      <c r="AM90" s="328"/>
-      <c r="AN90" s="329"/>
+      <c r="A90" s="316"/>
+      <c r="B90" s="317"/>
+      <c r="C90" s="317"/>
+      <c r="D90" s="317"/>
+      <c r="E90" s="317"/>
+      <c r="F90" s="317"/>
+      <c r="G90" s="317"/>
+      <c r="H90" s="317"/>
+      <c r="I90" s="317"/>
+      <c r="J90" s="317"/>
+      <c r="K90" s="317"/>
+      <c r="L90" s="318"/>
+      <c r="M90" s="325"/>
+      <c r="N90" s="326"/>
+      <c r="O90" s="326"/>
+      <c r="P90" s="326"/>
+      <c r="Q90" s="326"/>
+      <c r="R90" s="326"/>
+      <c r="S90" s="326"/>
+      <c r="T90" s="326"/>
+      <c r="U90" s="326"/>
+      <c r="V90" s="326"/>
+      <c r="W90" s="326"/>
+      <c r="X90" s="326"/>
+      <c r="Y90" s="326"/>
+      <c r="Z90" s="326"/>
+      <c r="AA90" s="326"/>
+      <c r="AB90" s="326"/>
+      <c r="AC90" s="326"/>
+      <c r="AD90" s="326"/>
+      <c r="AE90" s="326"/>
+      <c r="AF90" s="326"/>
+      <c r="AG90" s="326"/>
+      <c r="AH90" s="326"/>
+      <c r="AI90" s="326"/>
+      <c r="AJ90" s="326"/>
+      <c r="AK90" s="326"/>
+      <c r="AL90" s="326"/>
+      <c r="AM90" s="326"/>
+      <c r="AN90" s="327"/>
     </row>
     <row r="91" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A91" s="318"/>
-      <c r="B91" s="319"/>
-      <c r="C91" s="319"/>
-      <c r="D91" s="319"/>
-      <c r="E91" s="319"/>
-      <c r="F91" s="319"/>
-      <c r="G91" s="319"/>
-      <c r="H91" s="319"/>
-      <c r="I91" s="319"/>
-      <c r="J91" s="319"/>
-      <c r="K91" s="319"/>
-      <c r="L91" s="320"/>
-      <c r="M91" s="327"/>
-      <c r="N91" s="328"/>
-      <c r="O91" s="328"/>
-      <c r="P91" s="328"/>
-      <c r="Q91" s="328"/>
-      <c r="R91" s="328"/>
-      <c r="S91" s="328"/>
-      <c r="T91" s="328"/>
-      <c r="U91" s="328"/>
-      <c r="V91" s="328"/>
-      <c r="W91" s="328"/>
-      <c r="X91" s="328"/>
-      <c r="Y91" s="328"/>
-      <c r="Z91" s="328"/>
-      <c r="AA91" s="328"/>
-      <c r="AB91" s="328"/>
-      <c r="AC91" s="328"/>
-      <c r="AD91" s="328"/>
-      <c r="AE91" s="328"/>
-      <c r="AF91" s="328"/>
-      <c r="AG91" s="328"/>
-      <c r="AH91" s="328"/>
-      <c r="AI91" s="328"/>
-      <c r="AJ91" s="328"/>
-      <c r="AK91" s="328"/>
-      <c r="AL91" s="328"/>
-      <c r="AM91" s="328"/>
-      <c r="AN91" s="329"/>
+      <c r="A91" s="316"/>
+      <c r="B91" s="317"/>
+      <c r="C91" s="317"/>
+      <c r="D91" s="317"/>
+      <c r="E91" s="317"/>
+      <c r="F91" s="317"/>
+      <c r="G91" s="317"/>
+      <c r="H91" s="317"/>
+      <c r="I91" s="317"/>
+      <c r="J91" s="317"/>
+      <c r="K91" s="317"/>
+      <c r="L91" s="318"/>
+      <c r="M91" s="325"/>
+      <c r="N91" s="326"/>
+      <c r="O91" s="326"/>
+      <c r="P91" s="326"/>
+      <c r="Q91" s="326"/>
+      <c r="R91" s="326"/>
+      <c r="S91" s="326"/>
+      <c r="T91" s="326"/>
+      <c r="U91" s="326"/>
+      <c r="V91" s="326"/>
+      <c r="W91" s="326"/>
+      <c r="X91" s="326"/>
+      <c r="Y91" s="326"/>
+      <c r="Z91" s="326"/>
+      <c r="AA91" s="326"/>
+      <c r="AB91" s="326"/>
+      <c r="AC91" s="326"/>
+      <c r="AD91" s="326"/>
+      <c r="AE91" s="326"/>
+      <c r="AF91" s="326"/>
+      <c r="AG91" s="326"/>
+      <c r="AH91" s="326"/>
+      <c r="AI91" s="326"/>
+      <c r="AJ91" s="326"/>
+      <c r="AK91" s="326"/>
+      <c r="AL91" s="326"/>
+      <c r="AM91" s="326"/>
+      <c r="AN91" s="327"/>
     </row>
     <row r="92" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A92" s="318"/>
-      <c r="B92" s="319"/>
-      <c r="C92" s="319"/>
-      <c r="D92" s="319"/>
-      <c r="E92" s="319"/>
-      <c r="F92" s="319"/>
-      <c r="G92" s="319"/>
-      <c r="H92" s="319"/>
-      <c r="I92" s="319"/>
-      <c r="J92" s="319"/>
-      <c r="K92" s="319"/>
-      <c r="L92" s="320"/>
-      <c r="M92" s="327"/>
-      <c r="N92" s="328"/>
-      <c r="O92" s="328"/>
-      <c r="P92" s="328"/>
-      <c r="Q92" s="328"/>
-      <c r="R92" s="328"/>
-      <c r="S92" s="328"/>
-      <c r="T92" s="328"/>
-      <c r="U92" s="328"/>
-      <c r="V92" s="328"/>
-      <c r="W92" s="328"/>
-      <c r="X92" s="328"/>
-      <c r="Y92" s="328"/>
-      <c r="Z92" s="328"/>
-      <c r="AA92" s="328"/>
-      <c r="AB92" s="328"/>
-      <c r="AC92" s="328"/>
-      <c r="AD92" s="328"/>
-      <c r="AE92" s="328"/>
-      <c r="AF92" s="328"/>
-      <c r="AG92" s="328"/>
-      <c r="AH92" s="328"/>
-      <c r="AI92" s="328"/>
-      <c r="AJ92" s="328"/>
-      <c r="AK92" s="328"/>
-      <c r="AL92" s="328"/>
-      <c r="AM92" s="328"/>
-      <c r="AN92" s="329"/>
+      <c r="A92" s="316"/>
+      <c r="B92" s="317"/>
+      <c r="C92" s="317"/>
+      <c r="D92" s="317"/>
+      <c r="E92" s="317"/>
+      <c r="F92" s="317"/>
+      <c r="G92" s="317"/>
+      <c r="H92" s="317"/>
+      <c r="I92" s="317"/>
+      <c r="J92" s="317"/>
+      <c r="K92" s="317"/>
+      <c r="L92" s="318"/>
+      <c r="M92" s="325"/>
+      <c r="N92" s="326"/>
+      <c r="O92" s="326"/>
+      <c r="P92" s="326"/>
+      <c r="Q92" s="326"/>
+      <c r="R92" s="326"/>
+      <c r="S92" s="326"/>
+      <c r="T92" s="326"/>
+      <c r="U92" s="326"/>
+      <c r="V92" s="326"/>
+      <c r="W92" s="326"/>
+      <c r="X92" s="326"/>
+      <c r="Y92" s="326"/>
+      <c r="Z92" s="326"/>
+      <c r="AA92" s="326"/>
+      <c r="AB92" s="326"/>
+      <c r="AC92" s="326"/>
+      <c r="AD92" s="326"/>
+      <c r="AE92" s="326"/>
+      <c r="AF92" s="326"/>
+      <c r="AG92" s="326"/>
+      <c r="AH92" s="326"/>
+      <c r="AI92" s="326"/>
+      <c r="AJ92" s="326"/>
+      <c r="AK92" s="326"/>
+      <c r="AL92" s="326"/>
+      <c r="AM92" s="326"/>
+      <c r="AN92" s="327"/>
     </row>
     <row r="93" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A93" s="318"/>
-      <c r="B93" s="319"/>
-      <c r="C93" s="319"/>
-      <c r="D93" s="319"/>
-      <c r="E93" s="319"/>
-      <c r="F93" s="319"/>
-      <c r="G93" s="319"/>
-      <c r="H93" s="319"/>
-      <c r="I93" s="319"/>
-      <c r="J93" s="319"/>
-      <c r="K93" s="319"/>
-      <c r="L93" s="320"/>
-      <c r="M93" s="327"/>
-      <c r="N93" s="328"/>
-      <c r="O93" s="328"/>
-      <c r="P93" s="328"/>
-      <c r="Q93" s="328"/>
-      <c r="R93" s="328"/>
-      <c r="S93" s="328"/>
-      <c r="T93" s="328"/>
-      <c r="U93" s="328"/>
-      <c r="V93" s="328"/>
-      <c r="W93" s="328"/>
-      <c r="X93" s="328"/>
-      <c r="Y93" s="328"/>
-      <c r="Z93" s="328"/>
-      <c r="AA93" s="328"/>
-      <c r="AB93" s="328"/>
-      <c r="AC93" s="328"/>
-      <c r="AD93" s="328"/>
-      <c r="AE93" s="328"/>
-      <c r="AF93" s="328"/>
-      <c r="AG93" s="328"/>
-      <c r="AH93" s="328"/>
-      <c r="AI93" s="328"/>
-      <c r="AJ93" s="328"/>
-      <c r="AK93" s="328"/>
-      <c r="AL93" s="328"/>
-      <c r="AM93" s="328"/>
-      <c r="AN93" s="329"/>
+      <c r="A93" s="316"/>
+      <c r="B93" s="317"/>
+      <c r="C93" s="317"/>
+      <c r="D93" s="317"/>
+      <c r="E93" s="317"/>
+      <c r="F93" s="317"/>
+      <c r="G93" s="317"/>
+      <c r="H93" s="317"/>
+      <c r="I93" s="317"/>
+      <c r="J93" s="317"/>
+      <c r="K93" s="317"/>
+      <c r="L93" s="318"/>
+      <c r="M93" s="325"/>
+      <c r="N93" s="326"/>
+      <c r="O93" s="326"/>
+      <c r="P93" s="326"/>
+      <c r="Q93" s="326"/>
+      <c r="R93" s="326"/>
+      <c r="S93" s="326"/>
+      <c r="T93" s="326"/>
+      <c r="U93" s="326"/>
+      <c r="V93" s="326"/>
+      <c r="W93" s="326"/>
+      <c r="X93" s="326"/>
+      <c r="Y93" s="326"/>
+      <c r="Z93" s="326"/>
+      <c r="AA93" s="326"/>
+      <c r="AB93" s="326"/>
+      <c r="AC93" s="326"/>
+      <c r="AD93" s="326"/>
+      <c r="AE93" s="326"/>
+      <c r="AF93" s="326"/>
+      <c r="AG93" s="326"/>
+      <c r="AH93" s="326"/>
+      <c r="AI93" s="326"/>
+      <c r="AJ93" s="326"/>
+      <c r="AK93" s="326"/>
+      <c r="AL93" s="326"/>
+      <c r="AM93" s="326"/>
+      <c r="AN93" s="327"/>
     </row>
     <row r="94" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A94" s="318"/>
-      <c r="B94" s="319"/>
-      <c r="C94" s="319"/>
-      <c r="D94" s="319"/>
-      <c r="E94" s="319"/>
-      <c r="F94" s="319"/>
-      <c r="G94" s="319"/>
-      <c r="H94" s="319"/>
-      <c r="I94" s="319"/>
-      <c r="J94" s="319"/>
-      <c r="K94" s="319"/>
-      <c r="L94" s="320"/>
-      <c r="M94" s="327"/>
-      <c r="N94" s="328"/>
-      <c r="O94" s="328"/>
-      <c r="P94" s="328"/>
-      <c r="Q94" s="328"/>
-      <c r="R94" s="328"/>
-      <c r="S94" s="328"/>
-      <c r="T94" s="328"/>
-      <c r="U94" s="328"/>
-      <c r="V94" s="328"/>
-      <c r="W94" s="328"/>
-      <c r="X94" s="328"/>
-      <c r="Y94" s="328"/>
-      <c r="Z94" s="328"/>
-      <c r="AA94" s="328"/>
-      <c r="AB94" s="328"/>
-      <c r="AC94" s="328"/>
-      <c r="AD94" s="328"/>
-      <c r="AE94" s="328"/>
-      <c r="AF94" s="328"/>
-      <c r="AG94" s="328"/>
-      <c r="AH94" s="328"/>
-      <c r="AI94" s="328"/>
-      <c r="AJ94" s="328"/>
-      <c r="AK94" s="328"/>
-      <c r="AL94" s="328"/>
-      <c r="AM94" s="328"/>
-      <c r="AN94" s="329"/>
+      <c r="A94" s="316"/>
+      <c r="B94" s="317"/>
+      <c r="C94" s="317"/>
+      <c r="D94" s="317"/>
+      <c r="E94" s="317"/>
+      <c r="F94" s="317"/>
+      <c r="G94" s="317"/>
+      <c r="H94" s="317"/>
+      <c r="I94" s="317"/>
+      <c r="J94" s="317"/>
+      <c r="K94" s="317"/>
+      <c r="L94" s="318"/>
+      <c r="M94" s="325"/>
+      <c r="N94" s="326"/>
+      <c r="O94" s="326"/>
+      <c r="P94" s="326"/>
+      <c r="Q94" s="326"/>
+      <c r="R94" s="326"/>
+      <c r="S94" s="326"/>
+      <c r="T94" s="326"/>
+      <c r="U94" s="326"/>
+      <c r="V94" s="326"/>
+      <c r="W94" s="326"/>
+      <c r="X94" s="326"/>
+      <c r="Y94" s="326"/>
+      <c r="Z94" s="326"/>
+      <c r="AA94" s="326"/>
+      <c r="AB94" s="326"/>
+      <c r="AC94" s="326"/>
+      <c r="AD94" s="326"/>
+      <c r="AE94" s="326"/>
+      <c r="AF94" s="326"/>
+      <c r="AG94" s="326"/>
+      <c r="AH94" s="326"/>
+      <c r="AI94" s="326"/>
+      <c r="AJ94" s="326"/>
+      <c r="AK94" s="326"/>
+      <c r="AL94" s="326"/>
+      <c r="AM94" s="326"/>
+      <c r="AN94" s="327"/>
     </row>
     <row r="95" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A95" s="318"/>
-      <c r="B95" s="319"/>
-      <c r="C95" s="319"/>
-      <c r="D95" s="319"/>
-      <c r="E95" s="319"/>
-      <c r="F95" s="319"/>
-      <c r="G95" s="319"/>
-      <c r="H95" s="319"/>
-      <c r="I95" s="319"/>
-      <c r="J95" s="319"/>
-      <c r="K95" s="319"/>
-      <c r="L95" s="320"/>
-      <c r="M95" s="327"/>
-      <c r="N95" s="328"/>
-      <c r="O95" s="328"/>
-      <c r="P95" s="328"/>
-      <c r="Q95" s="328"/>
-      <c r="R95" s="328"/>
-      <c r="S95" s="328"/>
-      <c r="T95" s="328"/>
-      <c r="U95" s="328"/>
-      <c r="V95" s="328"/>
-      <c r="W95" s="328"/>
-      <c r="X95" s="328"/>
-      <c r="Y95" s="328"/>
-      <c r="Z95" s="328"/>
-      <c r="AA95" s="328"/>
-      <c r="AB95" s="328"/>
-      <c r="AC95" s="328"/>
-      <c r="AD95" s="328"/>
-      <c r="AE95" s="328"/>
-      <c r="AF95" s="328"/>
-      <c r="AG95" s="328"/>
-      <c r="AH95" s="328"/>
-      <c r="AI95" s="328"/>
-      <c r="AJ95" s="328"/>
-      <c r="AK95" s="328"/>
-      <c r="AL95" s="328"/>
-      <c r="AM95" s="328"/>
-      <c r="AN95" s="329"/>
+      <c r="A95" s="316"/>
+      <c r="B95" s="317"/>
+      <c r="C95" s="317"/>
+      <c r="D95" s="317"/>
+      <c r="E95" s="317"/>
+      <c r="F95" s="317"/>
+      <c r="G95" s="317"/>
+      <c r="H95" s="317"/>
+      <c r="I95" s="317"/>
+      <c r="J95" s="317"/>
+      <c r="K95" s="317"/>
+      <c r="L95" s="318"/>
+      <c r="M95" s="325"/>
+      <c r="N95" s="326"/>
+      <c r="O95" s="326"/>
+      <c r="P95" s="326"/>
+      <c r="Q95" s="326"/>
+      <c r="R95" s="326"/>
+      <c r="S95" s="326"/>
+      <c r="T95" s="326"/>
+      <c r="U95" s="326"/>
+      <c r="V95" s="326"/>
+      <c r="W95" s="326"/>
+      <c r="X95" s="326"/>
+      <c r="Y95" s="326"/>
+      <c r="Z95" s="326"/>
+      <c r="AA95" s="326"/>
+      <c r="AB95" s="326"/>
+      <c r="AC95" s="326"/>
+      <c r="AD95" s="326"/>
+      <c r="AE95" s="326"/>
+      <c r="AF95" s="326"/>
+      <c r="AG95" s="326"/>
+      <c r="AH95" s="326"/>
+      <c r="AI95" s="326"/>
+      <c r="AJ95" s="326"/>
+      <c r="AK95" s="326"/>
+      <c r="AL95" s="326"/>
+      <c r="AM95" s="326"/>
+      <c r="AN95" s="327"/>
     </row>
     <row r="96" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A96" s="318"/>
-      <c r="B96" s="319"/>
-      <c r="C96" s="319"/>
-      <c r="D96" s="319"/>
-      <c r="E96" s="319"/>
-      <c r="F96" s="319"/>
-      <c r="G96" s="319"/>
-      <c r="H96" s="319"/>
-      <c r="I96" s="319"/>
-      <c r="J96" s="319"/>
-      <c r="K96" s="319"/>
-      <c r="L96" s="320"/>
-      <c r="M96" s="327"/>
-      <c r="N96" s="328"/>
-      <c r="O96" s="328"/>
-      <c r="P96" s="328"/>
-      <c r="Q96" s="328"/>
-      <c r="R96" s="328"/>
-      <c r="S96" s="328"/>
-      <c r="T96" s="328"/>
-      <c r="U96" s="328"/>
-      <c r="V96" s="328"/>
-      <c r="W96" s="328"/>
-      <c r="X96" s="328"/>
-      <c r="Y96" s="328"/>
-      <c r="Z96" s="328"/>
-      <c r="AA96" s="328"/>
-      <c r="AB96" s="328"/>
-      <c r="AC96" s="328"/>
-      <c r="AD96" s="328"/>
-      <c r="AE96" s="328"/>
-      <c r="AF96" s="328"/>
-      <c r="AG96" s="328"/>
-      <c r="AH96" s="328"/>
-      <c r="AI96" s="328"/>
-      <c r="AJ96" s="328"/>
-      <c r="AK96" s="328"/>
-      <c r="AL96" s="328"/>
-      <c r="AM96" s="328"/>
-      <c r="AN96" s="329"/>
+      <c r="A96" s="316"/>
+      <c r="B96" s="317"/>
+      <c r="C96" s="317"/>
+      <c r="D96" s="317"/>
+      <c r="E96" s="317"/>
+      <c r="F96" s="317"/>
+      <c r="G96" s="317"/>
+      <c r="H96" s="317"/>
+      <c r="I96" s="317"/>
+      <c r="J96" s="317"/>
+      <c r="K96" s="317"/>
+      <c r="L96" s="318"/>
+      <c r="M96" s="325"/>
+      <c r="N96" s="326"/>
+      <c r="O96" s="326"/>
+      <c r="P96" s="326"/>
+      <c r="Q96" s="326"/>
+      <c r="R96" s="326"/>
+      <c r="S96" s="326"/>
+      <c r="T96" s="326"/>
+      <c r="U96" s="326"/>
+      <c r="V96" s="326"/>
+      <c r="W96" s="326"/>
+      <c r="X96" s="326"/>
+      <c r="Y96" s="326"/>
+      <c r="Z96" s="326"/>
+      <c r="AA96" s="326"/>
+      <c r="AB96" s="326"/>
+      <c r="AC96" s="326"/>
+      <c r="AD96" s="326"/>
+      <c r="AE96" s="326"/>
+      <c r="AF96" s="326"/>
+      <c r="AG96" s="326"/>
+      <c r="AH96" s="326"/>
+      <c r="AI96" s="326"/>
+      <c r="AJ96" s="326"/>
+      <c r="AK96" s="326"/>
+      <c r="AL96" s="326"/>
+      <c r="AM96" s="326"/>
+      <c r="AN96" s="327"/>
     </row>
     <row r="97" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A97" s="318"/>
-      <c r="B97" s="319"/>
-      <c r="C97" s="319"/>
-      <c r="D97" s="319"/>
-      <c r="E97" s="319"/>
-      <c r="F97" s="319"/>
-      <c r="G97" s="319"/>
-      <c r="H97" s="319"/>
-      <c r="I97" s="319"/>
-      <c r="J97" s="319"/>
-      <c r="K97" s="319"/>
-      <c r="L97" s="320"/>
-      <c r="M97" s="327"/>
-      <c r="N97" s="328"/>
-      <c r="O97" s="328"/>
-      <c r="P97" s="328"/>
-      <c r="Q97" s="328"/>
-      <c r="R97" s="328"/>
-      <c r="S97" s="328"/>
-      <c r="T97" s="328"/>
-      <c r="U97" s="328"/>
-      <c r="V97" s="328"/>
-      <c r="W97" s="328"/>
-      <c r="X97" s="328"/>
-      <c r="Y97" s="328"/>
-      <c r="Z97" s="328"/>
-      <c r="AA97" s="328"/>
-      <c r="AB97" s="328"/>
-      <c r="AC97" s="328"/>
-      <c r="AD97" s="328"/>
-      <c r="AE97" s="328"/>
-      <c r="AF97" s="328"/>
-      <c r="AG97" s="328"/>
-      <c r="AH97" s="328"/>
-      <c r="AI97" s="328"/>
-      <c r="AJ97" s="328"/>
-      <c r="AK97" s="328"/>
-      <c r="AL97" s="328"/>
-      <c r="AM97" s="328"/>
-      <c r="AN97" s="329"/>
+      <c r="A97" s="316"/>
+      <c r="B97" s="317"/>
+      <c r="C97" s="317"/>
+      <c r="D97" s="317"/>
+      <c r="E97" s="317"/>
+      <c r="F97" s="317"/>
+      <c r="G97" s="317"/>
+      <c r="H97" s="317"/>
+      <c r="I97" s="317"/>
+      <c r="J97" s="317"/>
+      <c r="K97" s="317"/>
+      <c r="L97" s="318"/>
+      <c r="M97" s="325"/>
+      <c r="N97" s="326"/>
+      <c r="O97" s="326"/>
+      <c r="P97" s="326"/>
+      <c r="Q97" s="326"/>
+      <c r="R97" s="326"/>
+      <c r="S97" s="326"/>
+      <c r="T97" s="326"/>
+      <c r="U97" s="326"/>
+      <c r="V97" s="326"/>
+      <c r="W97" s="326"/>
+      <c r="X97" s="326"/>
+      <c r="Y97" s="326"/>
+      <c r="Z97" s="326"/>
+      <c r="AA97" s="326"/>
+      <c r="AB97" s="326"/>
+      <c r="AC97" s="326"/>
+      <c r="AD97" s="326"/>
+      <c r="AE97" s="326"/>
+      <c r="AF97" s="326"/>
+      <c r="AG97" s="326"/>
+      <c r="AH97" s="326"/>
+      <c r="AI97" s="326"/>
+      <c r="AJ97" s="326"/>
+      <c r="AK97" s="326"/>
+      <c r="AL97" s="326"/>
+      <c r="AM97" s="326"/>
+      <c r="AN97" s="327"/>
     </row>
     <row r="98" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A98" s="318"/>
-      <c r="B98" s="319"/>
-      <c r="C98" s="319"/>
-      <c r="D98" s="319"/>
-      <c r="E98" s="319"/>
-      <c r="F98" s="319"/>
-      <c r="G98" s="319"/>
-      <c r="H98" s="319"/>
-      <c r="I98" s="319"/>
-      <c r="J98" s="319"/>
-      <c r="K98" s="319"/>
-      <c r="L98" s="320"/>
-      <c r="M98" s="327"/>
-      <c r="N98" s="328"/>
-      <c r="O98" s="328"/>
-      <c r="P98" s="328"/>
-      <c r="Q98" s="328"/>
-      <c r="R98" s="328"/>
-      <c r="S98" s="328"/>
-      <c r="T98" s="328"/>
-      <c r="U98" s="328"/>
-      <c r="V98" s="328"/>
-      <c r="W98" s="328"/>
-      <c r="X98" s="328"/>
-      <c r="Y98" s="328"/>
-      <c r="Z98" s="328"/>
-      <c r="AA98" s="328"/>
-      <c r="AB98" s="328"/>
-      <c r="AC98" s="328"/>
-      <c r="AD98" s="328"/>
-      <c r="AE98" s="328"/>
-      <c r="AF98" s="328"/>
-      <c r="AG98" s="328"/>
-      <c r="AH98" s="328"/>
-      <c r="AI98" s="328"/>
-      <c r="AJ98" s="328"/>
-      <c r="AK98" s="328"/>
-      <c r="AL98" s="328"/>
-      <c r="AM98" s="328"/>
-      <c r="AN98" s="329"/>
+      <c r="A98" s="316"/>
+      <c r="B98" s="317"/>
+      <c r="C98" s="317"/>
+      <c r="D98" s="317"/>
+      <c r="E98" s="317"/>
+      <c r="F98" s="317"/>
+      <c r="G98" s="317"/>
+      <c r="H98" s="317"/>
+      <c r="I98" s="317"/>
+      <c r="J98" s="317"/>
+      <c r="K98" s="317"/>
+      <c r="L98" s="318"/>
+      <c r="M98" s="325"/>
+      <c r="N98" s="326"/>
+      <c r="O98" s="326"/>
+      <c r="P98" s="326"/>
+      <c r="Q98" s="326"/>
+      <c r="R98" s="326"/>
+      <c r="S98" s="326"/>
+      <c r="T98" s="326"/>
+      <c r="U98" s="326"/>
+      <c r="V98" s="326"/>
+      <c r="W98" s="326"/>
+      <c r="X98" s="326"/>
+      <c r="Y98" s="326"/>
+      <c r="Z98" s="326"/>
+      <c r="AA98" s="326"/>
+      <c r="AB98" s="326"/>
+      <c r="AC98" s="326"/>
+      <c r="AD98" s="326"/>
+      <c r="AE98" s="326"/>
+      <c r="AF98" s="326"/>
+      <c r="AG98" s="326"/>
+      <c r="AH98" s="326"/>
+      <c r="AI98" s="326"/>
+      <c r="AJ98" s="326"/>
+      <c r="AK98" s="326"/>
+      <c r="AL98" s="326"/>
+      <c r="AM98" s="326"/>
+      <c r="AN98" s="327"/>
     </row>
     <row r="99" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A99" s="318"/>
-      <c r="B99" s="319"/>
-      <c r="C99" s="319"/>
-      <c r="D99" s="319"/>
-      <c r="E99" s="319"/>
-      <c r="F99" s="319"/>
-      <c r="G99" s="319"/>
-      <c r="H99" s="319"/>
-      <c r="I99" s="319"/>
-      <c r="J99" s="319"/>
-      <c r="K99" s="319"/>
-      <c r="L99" s="320"/>
-      <c r="M99" s="327"/>
-      <c r="N99" s="328"/>
-      <c r="O99" s="328"/>
-      <c r="P99" s="328"/>
-      <c r="Q99" s="328"/>
-      <c r="R99" s="328"/>
-      <c r="S99" s="328"/>
-      <c r="T99" s="328"/>
-      <c r="U99" s="328"/>
-      <c r="V99" s="328"/>
-      <c r="W99" s="328"/>
-      <c r="X99" s="328"/>
-      <c r="Y99" s="328"/>
-      <c r="Z99" s="328"/>
-      <c r="AA99" s="328"/>
-      <c r="AB99" s="328"/>
-      <c r="AC99" s="328"/>
-      <c r="AD99" s="328"/>
-      <c r="AE99" s="328"/>
-      <c r="AF99" s="328"/>
-      <c r="AG99" s="328"/>
-      <c r="AH99" s="328"/>
-      <c r="AI99" s="328"/>
-      <c r="AJ99" s="328"/>
-      <c r="AK99" s="328"/>
-      <c r="AL99" s="328"/>
-      <c r="AM99" s="328"/>
-      <c r="AN99" s="329"/>
+      <c r="A99" s="316"/>
+      <c r="B99" s="317"/>
+      <c r="C99" s="317"/>
+      <c r="D99" s="317"/>
+      <c r="E99" s="317"/>
+      <c r="F99" s="317"/>
+      <c r="G99" s="317"/>
+      <c r="H99" s="317"/>
+      <c r="I99" s="317"/>
+      <c r="J99" s="317"/>
+      <c r="K99" s="317"/>
+      <c r="L99" s="318"/>
+      <c r="M99" s="325"/>
+      <c r="N99" s="326"/>
+      <c r="O99" s="326"/>
+      <c r="P99" s="326"/>
+      <c r="Q99" s="326"/>
+      <c r="R99" s="326"/>
+      <c r="S99" s="326"/>
+      <c r="T99" s="326"/>
+      <c r="U99" s="326"/>
+      <c r="V99" s="326"/>
+      <c r="W99" s="326"/>
+      <c r="X99" s="326"/>
+      <c r="Y99" s="326"/>
+      <c r="Z99" s="326"/>
+      <c r="AA99" s="326"/>
+      <c r="AB99" s="326"/>
+      <c r="AC99" s="326"/>
+      <c r="AD99" s="326"/>
+      <c r="AE99" s="326"/>
+      <c r="AF99" s="326"/>
+      <c r="AG99" s="326"/>
+      <c r="AH99" s="326"/>
+      <c r="AI99" s="326"/>
+      <c r="AJ99" s="326"/>
+      <c r="AK99" s="326"/>
+      <c r="AL99" s="326"/>
+      <c r="AM99" s="326"/>
+      <c r="AN99" s="327"/>
     </row>
     <row r="100" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A100" s="318"/>
-      <c r="B100" s="319"/>
-      <c r="C100" s="319"/>
-      <c r="D100" s="319"/>
-      <c r="E100" s="319"/>
-      <c r="F100" s="319"/>
-      <c r="G100" s="319"/>
-      <c r="H100" s="319"/>
-      <c r="I100" s="319"/>
-      <c r="J100" s="319"/>
-      <c r="K100" s="319"/>
-      <c r="L100" s="320"/>
-      <c r="M100" s="327"/>
-      <c r="N100" s="328"/>
-      <c r="O100" s="328"/>
-      <c r="P100" s="328"/>
-      <c r="Q100" s="328"/>
-      <c r="R100" s="328"/>
-      <c r="S100" s="328"/>
-      <c r="T100" s="328"/>
-      <c r="U100" s="328"/>
-      <c r="V100" s="328"/>
-      <c r="W100" s="328"/>
-      <c r="X100" s="328"/>
-      <c r="Y100" s="328"/>
-      <c r="Z100" s="328"/>
-      <c r="AA100" s="328"/>
-      <c r="AB100" s="328"/>
-      <c r="AC100" s="328"/>
-      <c r="AD100" s="328"/>
-      <c r="AE100" s="328"/>
-      <c r="AF100" s="328"/>
-      <c r="AG100" s="328"/>
-      <c r="AH100" s="328"/>
-      <c r="AI100" s="328"/>
-      <c r="AJ100" s="328"/>
-      <c r="AK100" s="328"/>
-      <c r="AL100" s="328"/>
-      <c r="AM100" s="328"/>
-      <c r="AN100" s="329"/>
+      <c r="A100" s="316"/>
+      <c r="B100" s="317"/>
+      <c r="C100" s="317"/>
+      <c r="D100" s="317"/>
+      <c r="E100" s="317"/>
+      <c r="F100" s="317"/>
+      <c r="G100" s="317"/>
+      <c r="H100" s="317"/>
+      <c r="I100" s="317"/>
+      <c r="J100" s="317"/>
+      <c r="K100" s="317"/>
+      <c r="L100" s="318"/>
+      <c r="M100" s="325"/>
+      <c r="N100" s="326"/>
+      <c r="O100" s="326"/>
+      <c r="P100" s="326"/>
+      <c r="Q100" s="326"/>
+      <c r="R100" s="326"/>
+      <c r="S100" s="326"/>
+      <c r="T100" s="326"/>
+      <c r="U100" s="326"/>
+      <c r="V100" s="326"/>
+      <c r="W100" s="326"/>
+      <c r="X100" s="326"/>
+      <c r="Y100" s="326"/>
+      <c r="Z100" s="326"/>
+      <c r="AA100" s="326"/>
+      <c r="AB100" s="326"/>
+      <c r="AC100" s="326"/>
+      <c r="AD100" s="326"/>
+      <c r="AE100" s="326"/>
+      <c r="AF100" s="326"/>
+      <c r="AG100" s="326"/>
+      <c r="AH100" s="326"/>
+      <c r="AI100" s="326"/>
+      <c r="AJ100" s="326"/>
+      <c r="AK100" s="326"/>
+      <c r="AL100" s="326"/>
+      <c r="AM100" s="326"/>
+      <c r="AN100" s="327"/>
     </row>
     <row r="101" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A101" s="318"/>
-      <c r="B101" s="319"/>
-      <c r="C101" s="319"/>
-      <c r="D101" s="319"/>
-      <c r="E101" s="319"/>
-      <c r="F101" s="319"/>
-      <c r="G101" s="319"/>
-      <c r="H101" s="319"/>
-      <c r="I101" s="319"/>
-      <c r="J101" s="319"/>
-      <c r="K101" s="319"/>
-      <c r="L101" s="320"/>
-      <c r="M101" s="327"/>
-      <c r="N101" s="328"/>
-      <c r="O101" s="328"/>
-      <c r="P101" s="328"/>
-      <c r="Q101" s="328"/>
-      <c r="R101" s="328"/>
-      <c r="S101" s="328"/>
-      <c r="T101" s="328"/>
-      <c r="U101" s="328"/>
-      <c r="V101" s="328"/>
-      <c r="W101" s="328"/>
-      <c r="X101" s="328"/>
-      <c r="Y101" s="328"/>
-      <c r="Z101" s="328"/>
-      <c r="AA101" s="328"/>
-      <c r="AB101" s="328"/>
-      <c r="AC101" s="328"/>
-      <c r="AD101" s="328"/>
-      <c r="AE101" s="328"/>
-      <c r="AF101" s="328"/>
-      <c r="AG101" s="328"/>
-      <c r="AH101" s="328"/>
-      <c r="AI101" s="328"/>
-      <c r="AJ101" s="328"/>
-      <c r="AK101" s="328"/>
-      <c r="AL101" s="328"/>
-      <c r="AM101" s="328"/>
-      <c r="AN101" s="329"/>
+      <c r="A101" s="316"/>
+      <c r="B101" s="317"/>
+      <c r="C101" s="317"/>
+      <c r="D101" s="317"/>
+      <c r="E101" s="317"/>
+      <c r="F101" s="317"/>
+      <c r="G101" s="317"/>
+      <c r="H101" s="317"/>
+      <c r="I101" s="317"/>
+      <c r="J101" s="317"/>
+      <c r="K101" s="317"/>
+      <c r="L101" s="318"/>
+      <c r="M101" s="325"/>
+      <c r="N101" s="326"/>
+      <c r="O101" s="326"/>
+      <c r="P101" s="326"/>
+      <c r="Q101" s="326"/>
+      <c r="R101" s="326"/>
+      <c r="S101" s="326"/>
+      <c r="T101" s="326"/>
+      <c r="U101" s="326"/>
+      <c r="V101" s="326"/>
+      <c r="W101" s="326"/>
+      <c r="X101" s="326"/>
+      <c r="Y101" s="326"/>
+      <c r="Z101" s="326"/>
+      <c r="AA101" s="326"/>
+      <c r="AB101" s="326"/>
+      <c r="AC101" s="326"/>
+      <c r="AD101" s="326"/>
+      <c r="AE101" s="326"/>
+      <c r="AF101" s="326"/>
+      <c r="AG101" s="326"/>
+      <c r="AH101" s="326"/>
+      <c r="AI101" s="326"/>
+      <c r="AJ101" s="326"/>
+      <c r="AK101" s="326"/>
+      <c r="AL101" s="326"/>
+      <c r="AM101" s="326"/>
+      <c r="AN101" s="327"/>
     </row>
     <row r="102" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A102" s="318"/>
-      <c r="B102" s="319"/>
-      <c r="C102" s="319"/>
-      <c r="D102" s="319"/>
-      <c r="E102" s="319"/>
-      <c r="F102" s="319"/>
-      <c r="G102" s="319"/>
-      <c r="H102" s="319"/>
-      <c r="I102" s="319"/>
-      <c r="J102" s="319"/>
-      <c r="K102" s="319"/>
-      <c r="L102" s="320"/>
-      <c r="M102" s="327"/>
-      <c r="N102" s="328"/>
-      <c r="O102" s="328"/>
-      <c r="P102" s="328"/>
-      <c r="Q102" s="328"/>
-      <c r="R102" s="328"/>
-      <c r="S102" s="328"/>
-      <c r="T102" s="328"/>
-      <c r="U102" s="328"/>
-      <c r="V102" s="328"/>
-      <c r="W102" s="328"/>
-      <c r="X102" s="328"/>
-      <c r="Y102" s="328"/>
-      <c r="Z102" s="328"/>
-      <c r="AA102" s="328"/>
-      <c r="AB102" s="328"/>
-      <c r="AC102" s="328"/>
-      <c r="AD102" s="328"/>
-      <c r="AE102" s="328"/>
-      <c r="AF102" s="328"/>
-      <c r="AG102" s="328"/>
-      <c r="AH102" s="328"/>
-      <c r="AI102" s="328"/>
-      <c r="AJ102" s="328"/>
-      <c r="AK102" s="328"/>
-      <c r="AL102" s="328"/>
-      <c r="AM102" s="328"/>
-      <c r="AN102" s="329"/>
+      <c r="A102" s="316"/>
+      <c r="B102" s="317"/>
+      <c r="C102" s="317"/>
+      <c r="D102" s="317"/>
+      <c r="E102" s="317"/>
+      <c r="F102" s="317"/>
+      <c r="G102" s="317"/>
+      <c r="H102" s="317"/>
+      <c r="I102" s="317"/>
+      <c r="J102" s="317"/>
+      <c r="K102" s="317"/>
+      <c r="L102" s="318"/>
+      <c r="M102" s="325"/>
+      <c r="N102" s="326"/>
+      <c r="O102" s="326"/>
+      <c r="P102" s="326"/>
+      <c r="Q102" s="326"/>
+      <c r="R102" s="326"/>
+      <c r="S102" s="326"/>
+      <c r="T102" s="326"/>
+      <c r="U102" s="326"/>
+      <c r="V102" s="326"/>
+      <c r="W102" s="326"/>
+      <c r="X102" s="326"/>
+      <c r="Y102" s="326"/>
+      <c r="Z102" s="326"/>
+      <c r="AA102" s="326"/>
+      <c r="AB102" s="326"/>
+      <c r="AC102" s="326"/>
+      <c r="AD102" s="326"/>
+      <c r="AE102" s="326"/>
+      <c r="AF102" s="326"/>
+      <c r="AG102" s="326"/>
+      <c r="AH102" s="326"/>
+      <c r="AI102" s="326"/>
+      <c r="AJ102" s="326"/>
+      <c r="AK102" s="326"/>
+      <c r="AL102" s="326"/>
+      <c r="AM102" s="326"/>
+      <c r="AN102" s="327"/>
     </row>
     <row r="103" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A103" s="318"/>
-      <c r="B103" s="319"/>
-      <c r="C103" s="319"/>
-      <c r="D103" s="319"/>
-      <c r="E103" s="319"/>
-      <c r="F103" s="319"/>
-      <c r="G103" s="319"/>
-      <c r="H103" s="319"/>
-      <c r="I103" s="319"/>
-      <c r="J103" s="319"/>
-      <c r="K103" s="319"/>
-      <c r="L103" s="320"/>
-      <c r="M103" s="327"/>
-      <c r="N103" s="328"/>
-      <c r="O103" s="328"/>
-      <c r="P103" s="328"/>
-      <c r="Q103" s="328"/>
-      <c r="R103" s="328"/>
-      <c r="S103" s="328"/>
-      <c r="T103" s="328"/>
-      <c r="U103" s="328"/>
-      <c r="V103" s="328"/>
-      <c r="W103" s="328"/>
-      <c r="X103" s="328"/>
-      <c r="Y103" s="328"/>
-      <c r="Z103" s="328"/>
-      <c r="AA103" s="328"/>
-      <c r="AB103" s="328"/>
-      <c r="AC103" s="328"/>
-      <c r="AD103" s="328"/>
-      <c r="AE103" s="328"/>
-      <c r="AF103" s="328"/>
-      <c r="AG103" s="328"/>
-      <c r="AH103" s="328"/>
-      <c r="AI103" s="328"/>
-      <c r="AJ103" s="328"/>
-      <c r="AK103" s="328"/>
-      <c r="AL103" s="328"/>
-      <c r="AM103" s="328"/>
-      <c r="AN103" s="329"/>
+      <c r="A103" s="316"/>
+      <c r="B103" s="317"/>
+      <c r="C103" s="317"/>
+      <c r="D103" s="317"/>
+      <c r="E103" s="317"/>
+      <c r="F103" s="317"/>
+      <c r="G103" s="317"/>
+      <c r="H103" s="317"/>
+      <c r="I103" s="317"/>
+      <c r="J103" s="317"/>
+      <c r="K103" s="317"/>
+      <c r="L103" s="318"/>
+      <c r="M103" s="325"/>
+      <c r="N103" s="326"/>
+      <c r="O103" s="326"/>
+      <c r="P103" s="326"/>
+      <c r="Q103" s="326"/>
+      <c r="R103" s="326"/>
+      <c r="S103" s="326"/>
+      <c r="T103" s="326"/>
+      <c r="U103" s="326"/>
+      <c r="V103" s="326"/>
+      <c r="W103" s="326"/>
+      <c r="X103" s="326"/>
+      <c r="Y103" s="326"/>
+      <c r="Z103" s="326"/>
+      <c r="AA103" s="326"/>
+      <c r="AB103" s="326"/>
+      <c r="AC103" s="326"/>
+      <c r="AD103" s="326"/>
+      <c r="AE103" s="326"/>
+      <c r="AF103" s="326"/>
+      <c r="AG103" s="326"/>
+      <c r="AH103" s="326"/>
+      <c r="AI103" s="326"/>
+      <c r="AJ103" s="326"/>
+      <c r="AK103" s="326"/>
+      <c r="AL103" s="326"/>
+      <c r="AM103" s="326"/>
+      <c r="AN103" s="327"/>
     </row>
     <row r="104" spans="1:40" ht="30.75" customHeight="1">
-      <c r="A104" s="318"/>
-      <c r="B104" s="319"/>
-      <c r="C104" s="319"/>
-      <c r="D104" s="319"/>
-      <c r="E104" s="319"/>
-      <c r="F104" s="319"/>
-      <c r="G104" s="319"/>
-      <c r="H104" s="319"/>
-      <c r="I104" s="319"/>
-      <c r="J104" s="319"/>
-      <c r="K104" s="319"/>
-      <c r="L104" s="320"/>
-      <c r="M104" s="327"/>
-      <c r="N104" s="328"/>
-      <c r="O104" s="328"/>
-      <c r="P104" s="328"/>
-      <c r="Q104" s="328"/>
-      <c r="R104" s="328"/>
-      <c r="S104" s="328"/>
-      <c r="T104" s="328"/>
-      <c r="U104" s="328"/>
-      <c r="V104" s="328"/>
-      <c r="W104" s="328"/>
-      <c r="X104" s="328"/>
-      <c r="Y104" s="328"/>
-      <c r="Z104" s="328"/>
-      <c r="AA104" s="328"/>
-      <c r="AB104" s="328"/>
-      <c r="AC104" s="328"/>
-      <c r="AD104" s="328"/>
-      <c r="AE104" s="328"/>
-      <c r="AF104" s="328"/>
-      <c r="AG104" s="328"/>
-      <c r="AH104" s="328"/>
-      <c r="AI104" s="328"/>
-      <c r="AJ104" s="328"/>
-      <c r="AK104" s="328"/>
-      <c r="AL104" s="328"/>
-      <c r="AM104" s="328"/>
-      <c r="AN104" s="329"/>
+      <c r="A104" s="316"/>
+      <c r="B104" s="317"/>
+      <c r="C104" s="317"/>
+      <c r="D104" s="317"/>
+      <c r="E104" s="317"/>
+      <c r="F104" s="317"/>
+      <c r="G104" s="317"/>
+      <c r="H104" s="317"/>
+      <c r="I104" s="317"/>
+      <c r="J104" s="317"/>
+      <c r="K104" s="317"/>
+      <c r="L104" s="318"/>
+      <c r="M104" s="325"/>
+      <c r="N104" s="326"/>
+      <c r="O104" s="326"/>
+      <c r="P104" s="326"/>
+      <c r="Q104" s="326"/>
+      <c r="R104" s="326"/>
+      <c r="S104" s="326"/>
+      <c r="T104" s="326"/>
+      <c r="U104" s="326"/>
+      <c r="V104" s="326"/>
+      <c r="W104" s="326"/>
+      <c r="X104" s="326"/>
+      <c r="Y104" s="326"/>
+      <c r="Z104" s="326"/>
+      <c r="AA104" s="326"/>
+      <c r="AB104" s="326"/>
+      <c r="AC104" s="326"/>
+      <c r="AD104" s="326"/>
+      <c r="AE104" s="326"/>
+      <c r="AF104" s="326"/>
+      <c r="AG104" s="326"/>
+      <c r="AH104" s="326"/>
+      <c r="AI104" s="326"/>
+      <c r="AJ104" s="326"/>
+      <c r="AK104" s="326"/>
+      <c r="AL104" s="326"/>
+      <c r="AM104" s="326"/>
+      <c r="AN104" s="327"/>
     </row>
     <row r="105" spans="1:40" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A105" s="321"/>
-      <c r="B105" s="322"/>
-      <c r="C105" s="322"/>
-      <c r="D105" s="322"/>
-      <c r="E105" s="322"/>
-      <c r="F105" s="322"/>
-      <c r="G105" s="322"/>
-      <c r="H105" s="322"/>
-      <c r="I105" s="322"/>
-      <c r="J105" s="322"/>
-      <c r="K105" s="322"/>
-      <c r="L105" s="323"/>
-      <c r="M105" s="330"/>
-      <c r="N105" s="331"/>
-      <c r="O105" s="331"/>
-      <c r="P105" s="331"/>
-      <c r="Q105" s="331"/>
-      <c r="R105" s="331"/>
-      <c r="S105" s="331"/>
-      <c r="T105" s="331"/>
-      <c r="U105" s="331"/>
-      <c r="V105" s="331"/>
-      <c r="W105" s="331"/>
-      <c r="X105" s="331"/>
-      <c r="Y105" s="331"/>
-      <c r="Z105" s="331"/>
-      <c r="AA105" s="331"/>
-      <c r="AB105" s="331"/>
-      <c r="AC105" s="331"/>
-      <c r="AD105" s="331"/>
-      <c r="AE105" s="331"/>
-      <c r="AF105" s="331"/>
-      <c r="AG105" s="331"/>
-      <c r="AH105" s="331"/>
-      <c r="AI105" s="331"/>
-      <c r="AJ105" s="331"/>
-      <c r="AK105" s="331"/>
-      <c r="AL105" s="331"/>
-      <c r="AM105" s="331"/>
-      <c r="AN105" s="332"/>
+      <c r="A105" s="319"/>
+      <c r="B105" s="320"/>
+      <c r="C105" s="320"/>
+      <c r="D105" s="320"/>
+      <c r="E105" s="320"/>
+      <c r="F105" s="320"/>
+      <c r="G105" s="320"/>
+      <c r="H105" s="320"/>
+      <c r="I105" s="320"/>
+      <c r="J105" s="320"/>
+      <c r="K105" s="320"/>
+      <c r="L105" s="321"/>
+      <c r="M105" s="328"/>
+      <c r="N105" s="329"/>
+      <c r="O105" s="329"/>
+      <c r="P105" s="329"/>
+      <c r="Q105" s="329"/>
+      <c r="R105" s="329"/>
+      <c r="S105" s="329"/>
+      <c r="T105" s="329"/>
+      <c r="U105" s="329"/>
+      <c r="V105" s="329"/>
+      <c r="W105" s="329"/>
+      <c r="X105" s="329"/>
+      <c r="Y105" s="329"/>
+      <c r="Z105" s="329"/>
+      <c r="AA105" s="329"/>
+      <c r="AB105" s="329"/>
+      <c r="AC105" s="329"/>
+      <c r="AD105" s="329"/>
+      <c r="AE105" s="329"/>
+      <c r="AF105" s="329"/>
+      <c r="AG105" s="329"/>
+      <c r="AH105" s="329"/>
+      <c r="AI105" s="329"/>
+      <c r="AJ105" s="329"/>
+      <c r="AK105" s="329"/>
+      <c r="AL105" s="329"/>
+      <c r="AM105" s="329"/>
+      <c r="AN105" s="330"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1vovxCHf1q5ojzbN6CIC7eWjYUiNqGG7tRV6kzRfNmLE/WPnmhlJ0whRWExm3RYsdh172QIx4Hxo5B+ZSX9G/A==" saltValue="sdkbzDJxKfoIKIgYup93+Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="75">
+    <mergeCell ref="AK1:AN1"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AA1:AJ1"/>
+    <mergeCell ref="W4:AN4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D4:V4"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AN10:AN49"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="A7:AN7"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A76:L105"/>
+    <mergeCell ref="M76:AN105"/>
+    <mergeCell ref="A75:L75"/>
+    <mergeCell ref="M75:AN75"/>
+    <mergeCell ref="A54:L74"/>
+    <mergeCell ref="M54:AN74"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A35:AJ35"/>
+    <mergeCell ref="AL10:AL49"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="A26:AJ26"/>
+    <mergeCell ref="A36:A42"/>
+    <mergeCell ref="A21:A25"/>
     <mergeCell ref="AB5:AC5"/>
     <mergeCell ref="AD5:AE5"/>
     <mergeCell ref="AF5:AG5"/>
@@ -12278,65 +12340,6 @@
     <mergeCell ref="R8:S8"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A35:AJ35"/>
-    <mergeCell ref="AL10:AL49"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="A26:AJ26"/>
-    <mergeCell ref="A36:A42"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A76:L105"/>
-    <mergeCell ref="M76:AN105"/>
-    <mergeCell ref="A75:L75"/>
-    <mergeCell ref="M75:AN75"/>
-    <mergeCell ref="A54:L74"/>
-    <mergeCell ref="M54:AN74"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A43:A49"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AN10:AN49"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="A7:AN7"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D4:V4"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="AK1:AN1"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AA1:AJ1"/>
-    <mergeCell ref="W4:AN4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="AK28:AK32">
@@ -12690,15 +12693,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA9366B03F6EC145B189534E5AC3D6E6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ffc27aaa6afa60559960f746ac0a40ab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="dac3fa0a-9923-49c3-b4ba-df6390fa58ea" xmlns:ns4="1ed6e237-7a44-4d6d-bfbc-e270d277b5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6816e770e34b85fcdcbb3032b3d95e9" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12932,6 +12926,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F27D016-ED29-4335-8911-6427F4BFA81E}">
   <ds:schemaRefs>
@@ -12941,24 +12944,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9757ECA-E322-4B4F-A80B-F429838D8BF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1ed6e237-7a44-4d6d-bfbc-e270d277b5ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="dac3fa0a-9923-49c3-b4ba-df6390fa58ea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4331761-FFFE-4F11-AA2E-B35F1517E21B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12976,4 +12961,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9757ECA-E322-4B4F-A80B-F429838D8BF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1ed6e237-7a44-4d6d-bfbc-e270d277b5ad"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="dac3fa0a-9923-49c3-b4ba-df6390fa58ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>